--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -548,8 +548,8 @@
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="3" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
@@ -600,12 +600,12 @@
           <t>6</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
           <t>8</t>
@@ -1014,13 +1014,13 @@
 &amp;mo BLUETOOTH</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr"/>
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>mo中央R
 &amp;mo BLUETOOTH</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr"/>
       <c r="J10" s="7" t="inlineStr">
         <is>
           <t>N
@@ -1088,12 +1088,12 @@
           <t>L7</t>
         </is>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="H11" s="9" t="inlineStr"/>
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>L7</t>
         </is>
       </c>
-      <c r="I11" s="9" t="inlineStr"/>
       <c r="J11" s="9" t="inlineStr">
         <is>
           <t>N</t>
@@ -1156,12 +1156,12 @@
           <t>〃</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="I12" s="9" t="inlineStr"/>
+      <c r="H12" s="9" t="inlineStr"/>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J12" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -1230,13 +1230,13 @@
 &amp;mo SYMBOL</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr"/>
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>mo2 (center)
 &amp;mo VIM_NORMAL_1</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr"/>
       <c r="J13" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
@@ -1289,12 +1289,12 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="H14" s="9" t="inlineStr"/>
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr"/>
       <c r="J14" s="9" t="inlineStr">
         <is>
           <t>ENTER</t>
@@ -1345,12 +1345,12 @@
           <t>〃</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr"/>
+      <c r="H15" s="9" t="inlineStr"/>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
           <t>L1</t>
@@ -1747,13 +1747,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>mo中央R
 &amp;none</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr"/>
       <c r="J22" s="7" t="inlineStr">
         <is>
           <t>N
@@ -1907,13 +1907,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr"/>
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>mo2 (center)
 &amp;mo VIM_NORMAL_2</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr"/>
       <c r="J25" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
@@ -1958,12 +1958,12 @@
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr"/>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="H26" s="9" t="inlineStr"/>
+      <c r="I26" s="9" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="I26" s="9" t="inlineStr"/>
       <c r="J26" s="9" t="inlineStr"/>
       <c r="K26" s="9" t="inlineStr"/>
       <c r="L26" s="9" t="inlineStr"/>
@@ -1998,12 +1998,12 @@
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr"/>
-      <c r="H27" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="I27" s="9" t="inlineStr"/>
+      <c r="H27" s="9" t="inlineStr"/>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J27" s="9" t="inlineStr"/>
       <c r="K27" s="9" t="inlineStr"/>
       <c r="L27" s="9" t="inlineStr"/>
@@ -2591,13 +2591,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr"/>
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>mo中央R
 &amp;none</t>
         </is>
       </c>
-      <c r="I39" s="7" t="inlineStr"/>
       <c r="J39" s="7" t="inlineStr">
         <is>
           <t>N
@@ -2761,13 +2761,13 @@
 &amp;mo VIM_NORMAL_2</t>
         </is>
       </c>
-      <c r="H42" s="7" t="inlineStr">
+      <c r="H42" s="7" t="inlineStr"/>
+      <c r="I42" s="7" t="inlineStr">
         <is>
           <t>mo2 (center)
 &amp;none</t>
         </is>
       </c>
-      <c r="I42" s="7" t="inlineStr"/>
       <c r="J42" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
@@ -3146,13 +3146,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="H51" s="7" t="inlineStr">
+      <c r="H51" s="7" t="inlineStr"/>
+      <c r="I51" s="7" t="inlineStr">
         <is>
           <t>mo中央R
 &amp;none</t>
         </is>
       </c>
-      <c r="I51" s="7" t="inlineStr"/>
       <c r="J51" s="7" t="inlineStr">
         <is>
           <t>N
@@ -3254,13 +3254,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="H53" s="7" t="inlineStr">
+      <c r="H53" s="7" t="inlineStr"/>
+      <c r="I53" s="7" t="inlineStr">
         <is>
           <t>mo2 (center)
 &amp;none</t>
         </is>
       </c>
-      <c r="I53" s="7" t="inlineStr"/>
       <c r="J53" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
@@ -3551,13 +3551,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="H60" s="7" t="inlineStr">
+      <c r="H60" s="7" t="inlineStr"/>
+      <c r="I60" s="7" t="inlineStr">
         <is>
           <t>mo中央R
 &amp;none</t>
         </is>
       </c>
-      <c r="I60" s="7" t="inlineStr"/>
       <c r="J60" s="7" t="inlineStr">
         <is>
           <t>N
@@ -3651,13 +3651,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="H62" s="7" t="inlineStr">
+      <c r="H62" s="7" t="inlineStr"/>
+      <c r="I62" s="7" t="inlineStr">
         <is>
           <t>mo2 (center)
 &amp;none</t>
         </is>
       </c>
-      <c r="I62" s="7" t="inlineStr"/>
       <c r="J62" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
@@ -3936,13 +3936,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="H69" s="7" t="inlineStr">
+      <c r="H69" s="7" t="inlineStr"/>
+      <c r="I69" s="7" t="inlineStr">
         <is>
           <t>mo中央R
 &amp;none</t>
         </is>
       </c>
-      <c r="I69" s="7" t="inlineStr"/>
       <c r="J69" s="7" t="inlineStr">
         <is>
           <t>N
@@ -4036,13 +4036,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="H71" s="7" t="inlineStr">
+      <c r="H71" s="7" t="inlineStr"/>
+      <c r="I71" s="7" t="inlineStr">
         <is>
           <t>mo2 (center)
 &amp;none</t>
         </is>
       </c>
-      <c r="I71" s="7" t="inlineStr"/>
       <c r="J71" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
@@ -4361,13 +4361,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="H78" s="7" t="inlineStr">
+      <c r="H78" s="7" t="inlineStr"/>
+      <c r="I78" s="7" t="inlineStr">
         <is>
           <t>mo中央R
 &amp;none</t>
         </is>
       </c>
-      <c r="I78" s="7" t="inlineStr"/>
       <c r="J78" s="7" t="inlineStr">
         <is>
           <t>N
@@ -4461,13 +4461,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="H80" s="7" t="inlineStr">
+      <c r="H80" s="7" t="inlineStr"/>
+      <c r="I80" s="7" t="inlineStr">
         <is>
           <t>mo2 (center)
 &amp;none</t>
         </is>
       </c>
-      <c r="I80" s="7" t="inlineStr"/>
       <c r="J80" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
@@ -4746,13 +4746,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="H87" s="7" t="inlineStr">
+      <c r="H87" s="7" t="inlineStr"/>
+      <c r="I87" s="7" t="inlineStr">
         <is>
           <t>mo中央R
 &amp;none</t>
         </is>
       </c>
-      <c r="I87" s="7" t="inlineStr"/>
       <c r="J87" s="7" t="inlineStr">
         <is>
           <t>N
@@ -4846,13 +4846,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="H89" s="7" t="inlineStr">
+      <c r="H89" s="7" t="inlineStr"/>
+      <c r="I89" s="7" t="inlineStr">
         <is>
           <t>mo2 (center)
 &amp;none</t>
         </is>
       </c>
-      <c r="I89" s="7" t="inlineStr"/>
       <c r="J89" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
@@ -5289,13 +5289,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="H98" s="7" t="inlineStr">
+      <c r="H98" s="7" t="inlineStr"/>
+      <c r="I98" s="7" t="inlineStr">
         <is>
           <t>mo中央R
 &amp;none</t>
         </is>
       </c>
-      <c r="I98" s="7" t="inlineStr"/>
       <c r="J98" s="7" t="inlineStr">
         <is>
           <t>N
@@ -5419,13 +5419,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="H100" s="7" t="inlineStr">
+      <c r="H100" s="7" t="inlineStr"/>
+      <c r="I100" s="7" t="inlineStr">
         <is>
           <t>mo2 (center)
 &amp;none</t>
         </is>
       </c>
-      <c r="I100" s="7" t="inlineStr"/>
       <c r="J100" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
@@ -5494,8 +5494,8 @@
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="3" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
@@ -5546,12 +5546,12 @@
           <t>6</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
           <t>8</t>
@@ -5960,13 +5960,13 @@
 &amp;mo BLUETOOTH</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr"/>
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>mo中央R
 &amp;mo BLUETOOTH</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr"/>
       <c r="J10" s="7" t="inlineStr">
         <is>
           <t>N
@@ -6034,12 +6034,12 @@
           <t>&amp;mo BLUETOOTH</t>
         </is>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="H11" s="9" t="inlineStr"/>
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>&amp;mo BLUETOOTH</t>
         </is>
       </c>
-      <c r="I11" s="9" t="inlineStr"/>
       <c r="J11" s="9" t="inlineStr">
         <is>
           <t>&amp;kp N</t>
@@ -6102,12 +6102,12 @@
           <t>〃</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="I12" s="9" t="inlineStr"/>
+      <c r="H12" s="9" t="inlineStr"/>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J12" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -6176,13 +6176,13 @@
 &amp;mo SYMBOL</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr"/>
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>mo2 (center)
 &amp;mo VIM_NORMAL_1</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr"/>
       <c r="J13" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
@@ -6235,12 +6235,12 @@
           <t>&amp;mo SYMBOL</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="H14" s="9" t="inlineStr"/>
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>&amp;mo VIM_NORMAL_1</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr"/>
       <c r="J14" s="9" t="inlineStr">
         <is>
           <t>&amp;lt SYMBOL ENTER</t>
@@ -6291,12 +6291,12 @@
           <t>〃</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr"/>
+      <c r="H15" s="9" t="inlineStr"/>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
           <t>&amp;lt SYMBOL ENTER</t>
@@ -6693,13 +6693,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>mo中央R
 &amp;none</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr"/>
       <c r="J22" s="7" t="inlineStr">
         <is>
           <t>N
@@ -6853,13 +6853,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr"/>
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>mo2 (center)
 &amp;mo VIM_NORMAL_2</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr"/>
       <c r="J25" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
@@ -6904,12 +6904,12 @@
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr"/>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="H26" s="9" t="inlineStr"/>
+      <c r="I26" s="9" t="inlineStr">
         <is>
           <t>&amp;mo VIM_NORMAL_2</t>
         </is>
       </c>
-      <c r="I26" s="9" t="inlineStr"/>
       <c r="J26" s="9" t="inlineStr"/>
       <c r="K26" s="9" t="inlineStr"/>
       <c r="L26" s="9" t="inlineStr"/>
@@ -6944,12 +6944,12 @@
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr"/>
-      <c r="H27" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="I27" s="9" t="inlineStr"/>
+      <c r="H27" s="9" t="inlineStr"/>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J27" s="9" t="inlineStr"/>
       <c r="K27" s="9" t="inlineStr"/>
       <c r="L27" s="9" t="inlineStr"/>
@@ -7571,13 +7571,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr"/>
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>mo中央R
 &amp;none</t>
         </is>
       </c>
-      <c r="I39" s="7" t="inlineStr"/>
       <c r="J39" s="7" t="inlineStr">
         <is>
           <t>N
@@ -7742,13 +7742,13 @@
 &amp;mo VIM_NORMAL_2</t>
         </is>
       </c>
-      <c r="H42" s="7" t="inlineStr">
+      <c r="H42" s="7" t="inlineStr"/>
+      <c r="I42" s="7" t="inlineStr">
         <is>
           <t>mo2 (center)
 &amp;none</t>
         </is>
       </c>
-      <c r="I42" s="7" t="inlineStr"/>
       <c r="J42" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
@@ -8139,13 +8139,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="H51" s="7" t="inlineStr">
+      <c r="H51" s="7" t="inlineStr"/>
+      <c r="I51" s="7" t="inlineStr">
         <is>
           <t>mo中央R
 &amp;none</t>
         </is>
       </c>
-      <c r="I51" s="7" t="inlineStr"/>
       <c r="J51" s="7" t="inlineStr">
         <is>
           <t>N
@@ -8247,13 +8247,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="H53" s="7" t="inlineStr">
+      <c r="H53" s="7" t="inlineStr"/>
+      <c r="I53" s="7" t="inlineStr">
         <is>
           <t>mo2 (center)
 &amp;none</t>
         </is>
       </c>
-      <c r="I53" s="7" t="inlineStr"/>
       <c r="J53" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
@@ -8544,13 +8544,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="H60" s="7" t="inlineStr">
+      <c r="H60" s="7" t="inlineStr"/>
+      <c r="I60" s="7" t="inlineStr">
         <is>
           <t>mo中央R
 &amp;none</t>
         </is>
       </c>
-      <c r="I60" s="7" t="inlineStr"/>
       <c r="J60" s="7" t="inlineStr">
         <is>
           <t>N
@@ -8644,13 +8644,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="H62" s="7" t="inlineStr">
+      <c r="H62" s="7" t="inlineStr"/>
+      <c r="I62" s="7" t="inlineStr">
         <is>
           <t>mo2 (center)
 &amp;none</t>
         </is>
       </c>
-      <c r="I62" s="7" t="inlineStr"/>
       <c r="J62" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
@@ -8937,13 +8937,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="H69" s="7" t="inlineStr">
+      <c r="H69" s="7" t="inlineStr"/>
+      <c r="I69" s="7" t="inlineStr">
         <is>
           <t>mo中央R
 &amp;none</t>
         </is>
       </c>
-      <c r="I69" s="7" t="inlineStr"/>
       <c r="J69" s="7" t="inlineStr">
         <is>
           <t>N
@@ -9045,13 +9045,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="H71" s="7" t="inlineStr">
+      <c r="H71" s="7" t="inlineStr"/>
+      <c r="I71" s="7" t="inlineStr">
         <is>
           <t>mo2 (center)
 &amp;none</t>
         </is>
       </c>
-      <c r="I71" s="7" t="inlineStr"/>
       <c r="J71" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
@@ -9378,13 +9378,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="H78" s="7" t="inlineStr">
+      <c r="H78" s="7" t="inlineStr"/>
+      <c r="I78" s="7" t="inlineStr">
         <is>
           <t>mo中央R
 &amp;none</t>
         </is>
       </c>
-      <c r="I78" s="7" t="inlineStr"/>
       <c r="J78" s="7" t="inlineStr">
         <is>
           <t>N
@@ -9486,13 +9486,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="H80" s="7" t="inlineStr">
+      <c r="H80" s="7" t="inlineStr"/>
+      <c r="I80" s="7" t="inlineStr">
         <is>
           <t>mo2 (center)
 &amp;none</t>
         </is>
       </c>
-      <c r="I80" s="7" t="inlineStr"/>
       <c r="J80" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
@@ -9799,13 +9799,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="H87" s="7" t="inlineStr">
+      <c r="H87" s="7" t="inlineStr"/>
+      <c r="I87" s="7" t="inlineStr">
         <is>
           <t>mo中央R
 &amp;none</t>
         </is>
       </c>
-      <c r="I87" s="7" t="inlineStr"/>
       <c r="J87" s="7" t="inlineStr">
         <is>
           <t>N
@@ -9907,13 +9907,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="H89" s="7" t="inlineStr">
+      <c r="H89" s="7" t="inlineStr"/>
+      <c r="I89" s="7" t="inlineStr">
         <is>
           <t>mo2 (center)
 &amp;none</t>
         </is>
       </c>
-      <c r="I89" s="7" t="inlineStr"/>
       <c r="J89" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
@@ -10349,13 +10349,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="H98" s="7" t="inlineStr">
+      <c r="H98" s="7" t="inlineStr"/>
+      <c r="I98" s="7" t="inlineStr">
         <is>
           <t>mo中央R
 &amp;none</t>
         </is>
       </c>
-      <c r="I98" s="7" t="inlineStr"/>
       <c r="J98" s="7" t="inlineStr">
         <is>
           <t>N
@@ -10473,13 +10473,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="H100" s="7" t="inlineStr">
+      <c r="H100" s="7" t="inlineStr"/>
+      <c r="I100" s="7" t="inlineStr">
         <is>
           <t>mo2 (center)
 &amp;none</t>
         </is>
       </c>
-      <c r="I100" s="7" t="inlineStr"/>
       <c r="J100" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -545,12 +545,12 @@
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="3" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
@@ -635,7 +635,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>DEFAULT レイヤー</t>
+          <t>BASE_QWERTY レイヤー</t>
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
@@ -818,9 +818,19 @@
 &amp;kp G</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H7" s="7" t="inlineStr"/>
-      <c r="I7" s="7" t="inlineStr"/>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
           <t>H
@@ -1215,32 +1225,32 @@
       <c r="E13" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt VIM_NORMAL_1 SPACE</t>
+&amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt VIM_NORMAL_1 SPACE</t>
+&amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
           <t>mo1 (L center)
-&amp;mo SYMBOL</t>
+&amp;mo NUM_SYMBOL</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="7" t="inlineStr">
         <is>
           <t>mo2 (center)
-&amp;mo VIM_NORMAL_1</t>
+&amp;mo VIM_NORMAL_BASE</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
-&amp;lt SYMBOL ENTER</t>
+&amp;lt NUM_SYMBOL ENTER</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr"/>
@@ -1368,7 +1378,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>SYMBOL レイヤー</t>
+          <t>NUM_SYMBOL レイヤー</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -1551,9 +1561,19 @@
 &amp;kp DELETE</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr"/>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="7" t="inlineStr"/>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
           <t>H
@@ -1892,13 +1912,13 @@
       <c r="E25" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt VIM_NORMAL_2 SPACE</t>
+&amp;lt VIM_NORMAL_SYM SPACE</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt VIM_NORMAL_2 SPACE</t>
+&amp;lt VIM_NORMAL_SYM SPACE</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -1911,7 +1931,7 @@
       <c r="I25" s="7" t="inlineStr">
         <is>
           <t>mo2 (center)
-&amp;mo VIM_NORMAL_2</t>
+&amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
@@ -2013,7 +2033,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>VIM_NORMAL_1 レイヤー</t>
+          <t>VIM_NORMAL_BASE レイヤー</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -2314,9 +2334,19 @@
 &amp;mm_vim_g</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr"/>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H34" s="7" t="inlineStr"/>
-      <c r="I34" s="7" t="inlineStr"/>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
           <t>H
@@ -2648,7 +2678,7 @@
       <c r="D40" s="9" t="inlineStr"/>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>⇒VIM_VISUAL</t>
+          <t>⇒VIM_VISUAL_BASE</t>
         </is>
       </c>
       <c r="F40" s="9" t="inlineStr">
@@ -2694,7 +2724,7 @@
         <is>
           <t>HOME
 ▸ ⇧↓
-▸ ⇒VIM_VISUAL</t>
+▸ ⇒VIM_VISUAL_BASE</t>
         </is>
       </c>
       <c r="F41" s="9" t="inlineStr">
@@ -2758,7 +2788,7 @@
       <c r="G42" s="7" t="inlineStr">
         <is>
           <t>mo1 (L center)
-&amp;mo VIM_NORMAL_2</t>
+&amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr"/>
@@ -2771,7 +2801,7 @@
       <c r="J42" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
-&amp;lt VIM_NORMAL_2 ENTER</t>
+&amp;lt VIM_NORMAL_SYM ENTER</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr"/>
@@ -2859,7 +2889,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>VIM_NORMAL_2 レイヤー</t>
+          <t>VIM_NORMAL_SYM レイヤー</t>
         </is>
       </c>
       <c r="B45" s="4" t="n"/>
@@ -3038,9 +3068,19 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G49" s="7" t="inlineStr"/>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H49" s="7" t="inlineStr"/>
-      <c r="I49" s="7" t="inlineStr"/>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
           <t>H
@@ -3308,7 +3348,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>MOUSE レイヤー</t>
+          <t>MOUSE_MOVE レイヤー</t>
         </is>
       </c>
       <c r="B55" s="4" t="n"/>
@@ -3451,9 +3491,19 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G58" s="7" t="inlineStr"/>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H58" s="7" t="inlineStr"/>
-      <c r="I58" s="7" t="inlineStr"/>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
           <t>H
@@ -3469,7 +3519,7 @@
       <c r="L58" s="7" t="inlineStr">
         <is>
           <t>K
-&amp;mo SCROLL</t>
+&amp;mo MOUSE_SCROLL</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
@@ -3697,7 +3747,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>SCROLL レイヤー</t>
+          <t>MOUSE_SCROLL レイヤー</t>
         </is>
       </c>
       <c r="B64" s="4" t="n"/>
@@ -3840,9 +3890,19 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G67" s="7" t="inlineStr"/>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H67" s="7" t="inlineStr"/>
-      <c r="I67" s="7" t="inlineStr"/>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
           <t>H
@@ -4265,9 +4325,19 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G76" s="7" t="inlineStr"/>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H76" s="7" t="inlineStr"/>
-      <c r="I76" s="7" t="inlineStr"/>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="J76" s="7" t="inlineStr">
         <is>
           <t>H
@@ -4650,9 +4720,19 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G85" s="7" t="inlineStr"/>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H85" s="7" t="inlineStr"/>
-      <c r="I85" s="7" t="inlineStr"/>
+      <c r="I85" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
           <t>H
@@ -4892,7 +4972,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>VIM_VISUAL レイヤー</t>
+          <t>VIM_VISUAL_BASE レイヤー</t>
         </is>
       </c>
       <c r="B91" s="4" t="n"/>
@@ -5007,7 +5087,7 @@
 ▸ RShift
 ▸ ⌃C
 ▸ →
-▸ ⇒DEFAULT</t>
+▸ ⇒BASE_QWERTY</t>
         </is>
       </c>
       <c r="K93" s="9" t="inlineStr"/>
@@ -5018,7 +5098,7 @@
           <t>LShift
 ▸ RShift
 ▸ ⌃V
-▸ ⇒DEFAULT</t>
+▸ ⇒BASE_QWERTY</t>
         </is>
       </c>
     </row>
@@ -5058,9 +5138,19 @@
 &amp;mm_vim_visual_g</t>
         </is>
       </c>
-      <c r="G94" s="7" t="inlineStr"/>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H94" s="7" t="inlineStr"/>
-      <c r="I94" s="7" t="inlineStr"/>
+      <c r="I94" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="J94" s="7" t="inlineStr">
         <is>
           <t>H
@@ -5109,7 +5199,7 @@
           <t>LShift
 ▸ RShift
 ▸ ⌃X
-▸ ⇒DEFAULT</t>
+▸ ⇒BASE_QWERTY</t>
         </is>
       </c>
       <c r="E95" s="9" t="inlineStr"/>
@@ -5343,7 +5433,7 @@
           <t>LShift
 ▸ RShift
 ▸ ⌃X
-▸ ⇒DEFAULT</t>
+▸ ⇒BASE_QWERTY</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr"/>
@@ -5352,7 +5442,7 @@
           <t>LShift
 ▸ RShift
 ▸ →
-▸ ⇒DEFAULT</t>
+▸ ⇒BASE_QWERTY</t>
         </is>
       </c>
       <c r="F99" s="9" t="inlineStr">
@@ -5491,12 +5581,12 @@
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="3" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
@@ -5581,7 +5671,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>DEFAULT レイヤー</t>
+          <t>BASE_QWERTY レイヤー</t>
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
@@ -5764,9 +5854,19 @@
 &amp;kp G</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H7" s="7" t="inlineStr"/>
-      <c r="I7" s="7" t="inlineStr"/>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
           <t>H
@@ -6161,32 +6261,32 @@
       <c r="E13" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt VIM_NORMAL_1 SPACE</t>
+&amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt VIM_NORMAL_1 SPACE</t>
+&amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
           <t>mo1 (L center)
-&amp;mo SYMBOL</t>
+&amp;mo NUM_SYMBOL</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="7" t="inlineStr">
         <is>
           <t>mo2 (center)
-&amp;mo VIM_NORMAL_1</t>
+&amp;mo VIM_NORMAL_BASE</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
-&amp;lt SYMBOL ENTER</t>
+&amp;lt NUM_SYMBOL ENTER</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr"/>
@@ -6222,28 +6322,28 @@
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt VIM_NORMAL_1 SPACE</t>
+          <t>&amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt VIM_NORMAL_1 SPACE</t>
+          <t>&amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>&amp;mo SYMBOL</t>
+          <t>&amp;mo NUM_SYMBOL</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr"/>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>&amp;mo VIM_NORMAL_1</t>
+          <t>&amp;mo VIM_NORMAL_BASE</t>
         </is>
       </c>
       <c r="J14" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt SYMBOL ENTER</t>
+          <t>&amp;lt NUM_SYMBOL ENTER</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr"/>
@@ -6278,12 +6378,12 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt VIM_NORMAL_1 SPACE</t>
+          <t>&amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt VIM_NORMAL_1 SPACE</t>
+          <t>&amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
@@ -6299,7 +6399,7 @@
       </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt SYMBOL ENTER</t>
+          <t>&amp;lt NUM_SYMBOL ENTER</t>
         </is>
       </c>
       <c r="K15" s="9" t="inlineStr"/>
@@ -6314,7 +6414,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>SYMBOL レイヤー</t>
+          <t>NUM_SYMBOL レイヤー</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -6497,9 +6597,19 @@
 &amp;kp DELETE</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr"/>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="7" t="inlineStr"/>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
           <t>H
@@ -6838,13 +6948,13 @@
       <c r="E25" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt VIM_NORMAL_2 SPACE</t>
+&amp;lt VIM_NORMAL_SYM SPACE</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
           <t>SPACE
-&amp;lt VIM_NORMAL_2 SPACE</t>
+&amp;lt VIM_NORMAL_SYM SPACE</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -6857,7 +6967,7 @@
       <c r="I25" s="7" t="inlineStr">
         <is>
           <t>mo2 (center)
-&amp;mo VIM_NORMAL_2</t>
+&amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
@@ -6895,19 +7005,19 @@
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt VIM_NORMAL_2 SPACE</t>
+          <t>&amp;lt VIM_NORMAL_SYM SPACE</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt VIM_NORMAL_2 SPACE</t>
+          <t>&amp;lt VIM_NORMAL_SYM SPACE</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr"/>
       <c r="H26" s="9" t="inlineStr"/>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>&amp;mo VIM_NORMAL_2</t>
+          <t>&amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
       <c r="J26" s="9" t="inlineStr"/>
@@ -6935,12 +7045,12 @@
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt VIM_NORMAL_2 SPACE</t>
+          <t>&amp;lt VIM_NORMAL_SYM SPACE</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt VIM_NORMAL_2 SPACE</t>
+          <t>&amp;lt VIM_NORMAL_SYM SPACE</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr"/>
@@ -6959,7 +7069,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>VIM_NORMAL_1 レイヤー</t>
+          <t>VIM_NORMAL_BASE レイヤー</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -7275,9 +7385,19 @@
 &amp;mm_vim_g</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr"/>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H34" s="7" t="inlineStr"/>
-      <c r="I34" s="7" t="inlineStr"/>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
           <t>H
@@ -7629,7 +7749,7 @@
       <c r="E40" s="10" t="inlineStr">
         <is>
           <t>mm_vim_v[0]
-▸ &amp;to VIM_VISUAL</t>
+▸ &amp;to VIM_VISUAL_BASE</t>
         </is>
       </c>
       <c r="F40" s="9" t="inlineStr">
@@ -7739,7 +7859,7 @@
       <c r="G42" s="7" t="inlineStr">
         <is>
           <t>mo1 (L center)
-&amp;mo VIM_NORMAL_2</t>
+&amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr"/>
@@ -7752,7 +7872,7 @@
       <c r="J42" s="7" t="inlineStr">
         <is>
           <t>lt1 ENTER
-&amp;lt VIM_NORMAL_2 ENTER</t>
+&amp;lt VIM_NORMAL_SYM ENTER</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr"/>
@@ -7786,14 +7906,14 @@
       <c r="F43" s="9" t="inlineStr"/>
       <c r="G43" s="9" t="inlineStr">
         <is>
-          <t>&amp;mo VIM_NORMAL_2</t>
+          <t>&amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
       <c r="H43" s="9" t="inlineStr"/>
       <c r="I43" s="9" t="inlineStr"/>
       <c r="J43" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt VIM_NORMAL_2 ENTER</t>
+          <t>&amp;lt VIM_NORMAL_SYM ENTER</t>
         </is>
       </c>
       <c r="K43" s="9" t="inlineStr"/>
@@ -7829,7 +7949,7 @@
       <c r="I44" s="9" t="inlineStr"/>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>&amp;lt VIM_NORMAL_2 ENTER</t>
+          <t>&amp;lt VIM_NORMAL_SYM ENTER</t>
         </is>
       </c>
       <c r="K44" s="9" t="inlineStr"/>
@@ -7840,7 +7960,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>VIM_NORMAL_2 レイヤー</t>
+          <t>VIM_NORMAL_SYM レイヤー</t>
         </is>
       </c>
       <c r="B45" s="4" t="n"/>
@@ -8031,9 +8151,19 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G49" s="7" t="inlineStr"/>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H49" s="7" t="inlineStr"/>
-      <c r="I49" s="7" t="inlineStr"/>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
           <t>H
@@ -8301,7 +8431,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>MOUSE レイヤー</t>
+          <t>MOUSE_MOVE レイヤー</t>
         </is>
       </c>
       <c r="B55" s="4" t="n"/>
@@ -8444,9 +8574,19 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G58" s="7" t="inlineStr"/>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H58" s="7" t="inlineStr"/>
-      <c r="I58" s="7" t="inlineStr"/>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
           <t>H
@@ -8462,7 +8602,7 @@
       <c r="L58" s="7" t="inlineStr">
         <is>
           <t>K
-&amp;mo SCROLL</t>
+&amp;mo MOUSE_SCROLL</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
@@ -8496,7 +8636,7 @@
       <c r="K59" s="9" t="inlineStr"/>
       <c r="L59" s="9" t="inlineStr">
         <is>
-          <t>&amp;mo SCROLL</t>
+          <t>&amp;mo MOUSE_SCROLL</t>
         </is>
       </c>
       <c r="M59" s="9" t="inlineStr"/>
@@ -8690,7 +8830,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>SCROLL レイヤー</t>
+          <t>MOUSE_SCROLL レイヤー</t>
         </is>
       </c>
       <c r="B64" s="4" t="n"/>
@@ -8833,9 +8973,19 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G67" s="7" t="inlineStr"/>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H67" s="7" t="inlineStr"/>
-      <c r="I67" s="7" t="inlineStr"/>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
           <t>H
@@ -9274,9 +9424,19 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G76" s="7" t="inlineStr"/>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H76" s="7" t="inlineStr"/>
-      <c r="I76" s="7" t="inlineStr"/>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="J76" s="7" t="inlineStr">
         <is>
           <t>H
@@ -9699,9 +9859,19 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G85" s="7" t="inlineStr"/>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H85" s="7" t="inlineStr"/>
-      <c r="I85" s="7" t="inlineStr"/>
+      <c r="I85" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
           <t>H
@@ -9953,7 +10123,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>VIM_VISUAL レイヤー</t>
+          <t>VIM_VISUAL_BASE レイヤー</t>
         </is>
       </c>
       <c r="B91" s="4" t="n"/>
@@ -10112,9 +10282,19 @@
 &amp;mm_vim_visual_g</t>
         </is>
       </c>
-      <c r="G94" s="7" t="inlineStr"/>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="H94" s="7" t="inlineStr"/>
-      <c r="I94" s="7" t="inlineStr"/>
+      <c r="I94" s="7" t="inlineStr">
+        <is>
+          <t>中央
+&amp;none</t>
+        </is>
+      </c>
       <c r="J94" s="7" t="inlineStr">
         <is>
           <t>H

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -660,31 +660,31 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;kp Q</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;kp W</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;kp E</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;kp R</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;kp T</t>
         </is>
       </c>
@@ -693,31 +693,31 @@
       <c r="I5" s="7" t="inlineStr"/>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;kp Y</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;kp U</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;kp I</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;kp O</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;kp P</t>
         </is>
       </c>
@@ -790,74 +790,74 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;mt LEFT_CONTROL A</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;kp S</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;kp D</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;kp F</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;kp G</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 15
 &amp;none</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr"/>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 17
 &amp;kp H</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 18
 &amp;kp J</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 19
 &amp;kp K</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 20
 &amp;kp L</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 21
 &amp;mt RCTRL MINUS</t>
         </is>
       </c>
@@ -990,74 +990,74 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 22
 &amp;mt LEFT_SHIFT Z</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 23
 &amp;kp X</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 24
 &amp;kp C</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 25
 &amp;kp V</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 26
 &amp;kp B</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>mo中央L
+          <t>pos 27
 &amp;mo BLUETOOTH</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr"/>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>mo中央R
+          <t>pos 28
 &amp;mo BLUETOOTH</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 29
 &amp;kp N</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 30
 &amp;kp M</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 31
 &amp;kp COMMA</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 32
 &amp;kp PERIOD</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 33
 &amp;mt RIGHT_SHIFT SLASH</t>
         </is>
       </c>
@@ -1206,50 +1206,50 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 34
 &amp;mo FUNCTION</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 35
 &amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 36
 &amp;kp LEFT_ALT</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 37
 &amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 38
 &amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 39
 &amp;mo NUM_SYMBOL</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>mo2 (center)
+          <t>pos 40
 &amp;mo VIM_NORMAL_BASE</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 41
 &amp;lt NUM_SYMBOL ENTER</t>
         </is>
       </c>
@@ -1258,7 +1258,7 @@
       <c r="M13" s="7" t="inlineStr"/>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 42
 &amp;mo FUNCTION</t>
         </is>
       </c>
@@ -1403,31 +1403,31 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;kp N1</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;kp N2</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;kp N3</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;kp N4</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;kp N5</t>
         </is>
       </c>
@@ -1436,31 +1436,31 @@
       <c r="I17" s="7" t="inlineStr"/>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;kp N6</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;kp N7</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;kp N8</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;kp N9</t>
         </is>
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;kp N0</t>
         </is>
       </c>
@@ -1533,74 +1533,74 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;mt LCTRL TAB</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;kp GRAVE</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;kp LEFT_BRACKET</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;kp RIGHT_BRACKET</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;kp DELETE</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 15
 &amp;none</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr"/>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 17
 &amp;kp BACKSPACE</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 18
 &amp;kp SEMICOLON</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 19
 &amp;kp SINGLE_QUOTE</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 20
 &amp;kp BACKSLASH</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 21
 &amp;trans</t>
         </is>
       </c>
@@ -1733,74 +1733,74 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 22
 &amp;mt LEFT_SHIFT ESCAPE</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>mo中央L
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr"/>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>mo中央R
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 30
 &amp;kp EQUAL</t>
         </is>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 31
 &amp;trans</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 32
 &amp;trans</t>
         </is>
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 33
 &amp;trans</t>
         </is>
       </c>
@@ -1893,50 +1893,50 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 35
 &amp;trans</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 36
 &amp;trans</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 37
 &amp;lt VIM_NORMAL_SYM SPACE</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 38
 &amp;lt VIM_NORMAL_SYM SPACE</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr"/>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>mo2 (center)
+          <t>pos 40
 &amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -1945,7 +1945,7 @@
       <c r="M25" s="7" t="inlineStr"/>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 42
 &amp;none</t>
         </is>
       </c>
@@ -2058,31 +2058,31 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;mm_vim_w</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;kp LC(RIGHT)</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;mm_vim_ctrl_r</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
@@ -2091,31 +2091,31 @@
       <c r="I29" s="7" t="inlineStr"/>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;mm_vim_y</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;mm_vim_u</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;mm_vim_o</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;kp LC(V)</t>
         </is>
       </c>
@@ -2306,74 +2306,74 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;mm_vim_d</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;mm_vim_g</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 15
 &amp;none</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr"/>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 17
 &amp;kp LEFT</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 18
 &amp;mm_vim_j</t>
         </is>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 19
 &amp;kp UP_ARROW</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 20
 &amp;kp RIGHT</t>
         </is>
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 21
 &amp;kp RCTRL</t>
         </is>
       </c>
@@ -2587,74 +2587,74 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 22
 &amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 23
 &amp;kp DELETE</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 25
 &amp;mm_vim_v</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 26
 &amp;kp LC(LEFT)</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>mo中央L
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr"/>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>mo中央R
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 29
 &amp;mm_vim_n</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 30
 &amp;none</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 33
 &amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
@@ -2757,50 +2757,50 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 35
 &amp;trans</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 36
 &amp;trans</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 39
 &amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr"/>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>mo2 (center)
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 41
 &amp;lt VIM_NORMAL_SYM ENTER</t>
         </is>
       </c>
@@ -2809,7 +2809,7 @@
       <c r="M42" s="7" t="inlineStr"/>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 42
 &amp;none</t>
         </is>
       </c>
@@ -2914,31 +2914,31 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;none</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;none</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;mm_vim_shift_4</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
@@ -2947,31 +2947,31 @@
       <c r="I46" s="7" t="inlineStr"/>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;mm_vim_shift_6</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;none</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;kp HOME</t>
         </is>
       </c>
@@ -3040,74 +3040,74 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;none</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;none</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 15
 &amp;none</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr"/>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 17
 &amp;kp LEFT</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 18
 &amp;none</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 19
 &amp;none</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 20
 &amp;none</t>
         </is>
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 21
 &amp;kp RCTRL</t>
         </is>
       </c>
@@ -3152,74 +3152,74 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 22
 &amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>mo中央L
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr"/>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>mo中央R
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 30
 &amp;none</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 33
 &amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
@@ -3260,50 +3260,50 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 35
 &amp;trans</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 36
 &amp;trans</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr"/>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>mo2 (center)
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -3312,7 +3312,7 @@
       <c r="M53" s="7" t="inlineStr"/>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 42
 &amp;none</t>
         </is>
       </c>
@@ -3373,31 +3373,31 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;none</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;none</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;none</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
@@ -3406,31 +3406,31 @@
       <c r="I56" s="7" t="inlineStr"/>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;none</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;none</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;none</t>
         </is>
       </c>
@@ -3463,74 +3463,74 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;none</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;none</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;none</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 15
 &amp;none</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr"/>
       <c r="I58" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 17
 &amp;none</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 18
 &amp;none</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 19
 &amp;mo MOUSE_SCROLL</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 20
 &amp;none</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
@@ -3567,74 +3567,74 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>mo中央L
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr"/>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>mo中央R
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 30
 &amp;none</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 33
 &amp;none</t>
         </is>
       </c>
@@ -3667,50 +3667,50 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr"/>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>mo2 (center)
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -3719,7 +3719,7 @@
       <c r="M62" s="7" t="inlineStr"/>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 42
 &amp;none</t>
         </is>
       </c>
@@ -3772,31 +3772,31 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;none</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;none</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;none</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
@@ -3805,31 +3805,31 @@
       <c r="I65" s="7" t="inlineStr"/>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;none</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;none</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;none</t>
         </is>
       </c>
@@ -3862,74 +3862,74 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;none</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;none</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;none</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 15
 &amp;none</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr"/>
       <c r="I67" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 17
 &amp;none</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 18
 &amp;mkp MB1</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 19
 &amp;none</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 20
 &amp;mkp MB2</t>
         </is>
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
@@ -3962,74 +3962,74 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>mo中央L
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr"/>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>mo中央R
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 30
 &amp;mkp MB4</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 32
 &amp;mkp MB5</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 33
 &amp;none</t>
         </is>
       </c>
@@ -4062,50 +4062,50 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr"/>
       <c r="I71" s="7" t="inlineStr">
         <is>
-          <t>mo2 (center)
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -4114,7 +4114,7 @@
       <c r="M71" s="7" t="inlineStr"/>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 42
 &amp;none</t>
         </is>
       </c>
@@ -4167,31 +4167,31 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;kp F1</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;kp F2</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;kp F3</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;kp F4</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;kp F5</t>
         </is>
       </c>
@@ -4200,31 +4200,31 @@
       <c r="I74" s="7" t="inlineStr"/>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;kp F6</t>
         </is>
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;kp F7</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;kp F8</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;kp F9</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;kp F10</t>
         </is>
       </c>
@@ -4297,74 +4297,74 @@
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;none</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;sys_reset</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;none</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;none</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 15
 &amp;none</t>
         </is>
       </c>
       <c r="H76" s="7" t="inlineStr"/>
       <c r="I76" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="J76" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 17
 &amp;none</t>
         </is>
       </c>
       <c r="K76" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 18
 &amp;none</t>
         </is>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 19
 &amp;none</t>
         </is>
       </c>
       <c r="M76" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 20
 &amp;sys_reset</t>
         </is>
       </c>
       <c r="N76" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
@@ -4397,74 +4397,74 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 26
 &amp;bootloader</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>mo中央L
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr"/>
       <c r="I78" s="7" t="inlineStr">
         <is>
-          <t>mo中央R
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="J78" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 29
 &amp;bootloader</t>
         </is>
       </c>
       <c r="K78" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 30
 &amp;none</t>
         </is>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="M78" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="N78" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 33
 &amp;none</t>
         </is>
       </c>
@@ -4497,50 +4497,50 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr"/>
       <c r="I80" s="7" t="inlineStr">
         <is>
-          <t>mo2 (center)
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="J80" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -4549,7 +4549,7 @@
       <c r="M80" s="7" t="inlineStr"/>
       <c r="N80" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 42
 &amp;none</t>
         </is>
       </c>
@@ -4602,31 +4602,31 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;bt BT_SEL 0</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;bt BT_SEL 1</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;bt BT_SEL 2</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;bt BT_SEL 3</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;bt BT_SEL 4</t>
         </is>
       </c>
@@ -4635,31 +4635,31 @@
       <c r="I83" s="7" t="inlineStr"/>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;none</t>
         </is>
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;out OUT_USB</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="N83" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;none</t>
         </is>
       </c>
@@ -4692,74 +4692,74 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;bt BT_CLR_ALL</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;none</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;none</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 15
 &amp;none</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr"/>
       <c r="I85" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 17
 &amp;none</t>
         </is>
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 18
 &amp;none</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 19
 &amp;none</t>
         </is>
       </c>
       <c r="M85" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 20
 &amp;none</t>
         </is>
       </c>
       <c r="N85" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
@@ -4792,74 +4792,74 @@
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 24
 &amp;bt BT_CLR</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 26
 &amp;out OUT_BLE</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>mo中央L
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr"/>
       <c r="I87" s="7" t="inlineStr">
         <is>
-          <t>mo中央R
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 30
 &amp;none</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="N87" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 33
 &amp;none</t>
         </is>
       </c>
@@ -4892,50 +4892,50 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr"/>
       <c r="I89" s="7" t="inlineStr">
         <is>
-          <t>mo2 (center)
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -4944,7 +4944,7 @@
       <c r="M89" s="7" t="inlineStr"/>
       <c r="N89" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 42
 &amp;none</t>
         </is>
       </c>
@@ -4997,31 +4997,31 @@
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;kp LS(LC(RIGHT))</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;kp LS(LC(RIGHT))</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;none</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
@@ -5030,31 +5030,31 @@
       <c r="I92" s="7" t="inlineStr"/>
       <c r="J92" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;macro_vim_visual_y</t>
         </is>
       </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;none</t>
         </is>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="M92" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="N92" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;macro_vim_visual_p</t>
         </is>
       </c>
@@ -5110,74 +5110,74 @@
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;macro_vim_visual_cut</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;mm_vim_visual_g</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 15
 &amp;none</t>
         </is>
       </c>
       <c r="H94" s="7" t="inlineStr"/>
       <c r="I94" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="J94" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 17
 &amp;kp LS(LEFT)</t>
         </is>
       </c>
       <c r="K94" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 18
 &amp;kp LS(DOWN)</t>
         </is>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 19
 &amp;kp LS(UP)</t>
         </is>
       </c>
       <c r="M94" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 20
 &amp;kp LS(RIGHT)</t>
         </is>
       </c>
       <c r="N94" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 21
 &amp;kp RCTRL</t>
         </is>
       </c>
@@ -5345,74 +5345,74 @@
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 22
 &amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 23
 &amp;macro_vim_visual_cut</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 25
 &amp;macro_vim_visual_exit</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 26
 &amp;kp LS(LC(LEFT))</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>mo中央L
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="H98" s="7" t="inlineStr"/>
       <c r="I98" s="7" t="inlineStr">
         <is>
-          <t>mo中央R
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="J98" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 29
 &amp;kp F3</t>
         </is>
       </c>
       <c r="K98" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 30
 &amp;none</t>
         </is>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="M98" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="N98" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 33
 &amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
@@ -5475,50 +5475,50 @@
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr"/>
       <c r="I100" s="7" t="inlineStr">
         <is>
-          <t>mo2 (center)
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="J100" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -5527,7 +5527,7 @@
       <c r="M100" s="7" t="inlineStr"/>
       <c r="N100" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 42
 &amp;none</t>
         </is>
       </c>
@@ -5696,31 +5696,31 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;kp Q</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;kp W</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;kp E</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;kp R</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;kp T</t>
         </is>
       </c>
@@ -5729,31 +5729,31 @@
       <c r="I5" s="7" t="inlineStr"/>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;kp Y</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;kp U</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;kp I</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;kp O</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;kp P</t>
         </is>
       </c>
@@ -5826,74 +5826,74 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;mt LEFT_CONTROL A</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;kp S</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;kp D</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;kp F</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;kp G</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 15
 &amp;none</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr"/>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 17
 &amp;kp H</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 18
 &amp;kp J</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 19
 &amp;kp K</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 20
 &amp;kp L</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 21
 &amp;mt RCTRL MINUS</t>
         </is>
       </c>
@@ -6026,74 +6026,74 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 22
 &amp;mt LEFT_SHIFT Z</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 23
 &amp;kp X</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 24
 &amp;kp C</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 25
 &amp;kp V</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 26
 &amp;kp B</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>mo中央L
+          <t>pos 27
 &amp;mo BLUETOOTH</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr"/>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>mo中央R
+          <t>pos 28
 &amp;mo BLUETOOTH</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 29
 &amp;kp N</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 30
 &amp;kp M</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 31
 &amp;kp COMMA</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 32
 &amp;kp PERIOD</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 33
 &amp;mt RIGHT_SHIFT SLASH</t>
         </is>
       </c>
@@ -6242,50 +6242,50 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 34
 &amp;mo FUNCTION</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 35
 &amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 36
 &amp;kp LEFT_ALT</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 37
 &amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 38
 &amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 39
 &amp;mo NUM_SYMBOL</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>mo2 (center)
+          <t>pos 40
 &amp;mo VIM_NORMAL_BASE</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 41
 &amp;lt NUM_SYMBOL ENTER</t>
         </is>
       </c>
@@ -6294,7 +6294,7 @@
       <c r="M13" s="7" t="inlineStr"/>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 42
 &amp;mo FUNCTION</t>
         </is>
       </c>
@@ -6439,31 +6439,31 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;kp N1</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;kp N2</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;kp N3</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;kp N4</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;kp N5</t>
         </is>
       </c>
@@ -6472,31 +6472,31 @@
       <c r="I17" s="7" t="inlineStr"/>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;kp N6</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;kp N7</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;kp N8</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;kp N9</t>
         </is>
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;kp N0</t>
         </is>
       </c>
@@ -6569,74 +6569,74 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;mt LCTRL TAB</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;kp GRAVE</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;kp LEFT_BRACKET</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;kp RIGHT_BRACKET</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;kp DELETE</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 15
 &amp;none</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr"/>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 17
 &amp;kp BACKSPACE</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 18
 &amp;kp SEMICOLON</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 19
 &amp;kp SINGLE_QUOTE</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 20
 &amp;kp BACKSLASH</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 21
 &amp;trans</t>
         </is>
       </c>
@@ -6769,74 +6769,74 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 22
 &amp;mt LEFT_SHIFT ESCAPE</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>mo中央L
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr"/>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>mo中央R
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 30
 &amp;kp EQUAL</t>
         </is>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 31
 &amp;trans</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 32
 &amp;trans</t>
         </is>
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 33
 &amp;trans</t>
         </is>
       </c>
@@ -6929,50 +6929,50 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 35
 &amp;trans</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 36
 &amp;trans</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 37
 &amp;lt VIM_NORMAL_SYM SPACE</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 38
 &amp;lt VIM_NORMAL_SYM SPACE</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr"/>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>mo2 (center)
+          <t>pos 40
 &amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -6981,7 +6981,7 @@
       <c r="M25" s="7" t="inlineStr"/>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 42
 &amp;none</t>
         </is>
       </c>
@@ -7094,31 +7094,31 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;mm_vim_w</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;kp LC(RIGHT)</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;mm_vim_ctrl_r</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
@@ -7127,31 +7127,31 @@
       <c r="I29" s="7" t="inlineStr"/>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;mm_vim_y</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;mm_vim_u</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;mm_vim_o</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;kp LC(V)</t>
         </is>
       </c>
@@ -7357,74 +7357,74 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;mm_vim_d</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;mm_vim_g</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 15
 &amp;none</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr"/>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 17
 &amp;kp LEFT</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 18
 &amp;mm_vim_j</t>
         </is>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 19
 &amp;kp UP_ARROW</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 20
 &amp;kp RIGHT</t>
         </is>
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 21
 &amp;kp RCTRL</t>
         </is>
       </c>
@@ -7657,74 +7657,74 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 22
 &amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 23
 &amp;kp DELETE</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 25
 &amp;mm_vim_v</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 26
 &amp;kp LC(LEFT)</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>mo中央L
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr"/>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>mo中央R
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 29
 &amp;mm_vim_n</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 30
 &amp;none</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 33
 &amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
@@ -7828,50 +7828,50 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 35
 &amp;trans</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 36
 &amp;trans</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 39
 &amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr"/>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>mo2 (center)
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 41
 &amp;lt VIM_NORMAL_SYM ENTER</t>
         </is>
       </c>
@@ -7880,7 +7880,7 @@
       <c r="M42" s="7" t="inlineStr"/>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 42
 &amp;none</t>
         </is>
       </c>
@@ -7985,31 +7985,31 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;none</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;none</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;mm_vim_shift_4</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
@@ -8018,31 +8018,31 @@
       <c r="I46" s="7" t="inlineStr"/>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;mm_vim_shift_6</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;none</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;kp HOME</t>
         </is>
       </c>
@@ -8123,74 +8123,74 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;none</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;none</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 15
 &amp;none</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr"/>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 17
 &amp;kp LEFT</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 18
 &amp;none</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 19
 &amp;none</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 20
 &amp;none</t>
         </is>
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 21
 &amp;kp RCTRL</t>
         </is>
       </c>
@@ -8235,74 +8235,74 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 22
 &amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>mo中央L
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr"/>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>mo中央R
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 30
 &amp;none</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 33
 &amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
@@ -8343,50 +8343,50 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 35
 &amp;trans</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 36
 &amp;trans</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr"/>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>mo2 (center)
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -8395,7 +8395,7 @@
       <c r="M53" s="7" t="inlineStr"/>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 42
 &amp;none</t>
         </is>
       </c>
@@ -8456,31 +8456,31 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;none</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;none</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;none</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
@@ -8489,31 +8489,31 @@
       <c r="I56" s="7" t="inlineStr"/>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;none</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;none</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;none</t>
         </is>
       </c>
@@ -8546,74 +8546,74 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;none</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;none</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;none</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 15
 &amp;none</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr"/>
       <c r="I58" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 17
 &amp;none</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 18
 &amp;none</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 19
 &amp;mo MOUSE_SCROLL</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 20
 &amp;none</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
@@ -8650,74 +8650,74 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>mo中央L
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr"/>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>mo中央R
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 30
 &amp;none</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 33
 &amp;none</t>
         </is>
       </c>
@@ -8750,50 +8750,50 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr"/>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>mo2 (center)
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -8802,7 +8802,7 @@
       <c r="M62" s="7" t="inlineStr"/>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 42
 &amp;none</t>
         </is>
       </c>
@@ -8855,31 +8855,31 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;none</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;none</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;none</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
@@ -8888,31 +8888,31 @@
       <c r="I65" s="7" t="inlineStr"/>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;none</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;none</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;none</t>
         </is>
       </c>
@@ -8945,74 +8945,74 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;none</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;none</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;none</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 15
 &amp;none</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr"/>
       <c r="I67" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 17
 &amp;none</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 18
 &amp;mkp MB1</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 19
 &amp;none</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 20
 &amp;mkp MB2</t>
         </is>
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
@@ -9053,74 +9053,74 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 26
 &amp;none</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>mo中央L
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr"/>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>mo中央R
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 30
 &amp;mkp MB4</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 32
 &amp;mkp MB5</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 33
 &amp;none</t>
         </is>
       </c>
@@ -9161,50 +9161,50 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr"/>
       <c r="I71" s="7" t="inlineStr">
         <is>
-          <t>mo2 (center)
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -9213,7 +9213,7 @@
       <c r="M71" s="7" t="inlineStr"/>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 42
 &amp;none</t>
         </is>
       </c>
@@ -9266,31 +9266,31 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;kp F1</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;kp F2</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;kp F3</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;kp F4</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;kp F5</t>
         </is>
       </c>
@@ -9299,31 +9299,31 @@
       <c r="I74" s="7" t="inlineStr"/>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;kp F6</t>
         </is>
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;kp F7</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;kp F8</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;kp F9</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;kp F10</t>
         </is>
       </c>
@@ -9396,74 +9396,74 @@
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;none</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;sys_reset</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;none</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;none</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 15
 &amp;none</t>
         </is>
       </c>
       <c r="H76" s="7" t="inlineStr"/>
       <c r="I76" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="J76" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 17
 &amp;none</t>
         </is>
       </c>
       <c r="K76" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 18
 &amp;none</t>
         </is>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 19
 &amp;none</t>
         </is>
       </c>
       <c r="M76" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 20
 &amp;sys_reset</t>
         </is>
       </c>
       <c r="N76" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
@@ -9504,74 +9504,74 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 26
 &amp;bootloader</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>mo中央L
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr"/>
       <c r="I78" s="7" t="inlineStr">
         <is>
-          <t>mo中央R
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="J78" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 29
 &amp;bootloader</t>
         </is>
       </c>
       <c r="K78" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 30
 &amp;none</t>
         </is>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="M78" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="N78" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 33
 &amp;none</t>
         </is>
       </c>
@@ -9612,50 +9612,50 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr"/>
       <c r="I80" s="7" t="inlineStr">
         <is>
-          <t>mo2 (center)
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="J80" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -9664,7 +9664,7 @@
       <c r="M80" s="7" t="inlineStr"/>
       <c r="N80" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 42
 &amp;none</t>
         </is>
       </c>
@@ -9717,31 +9717,31 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;bt BT_SEL 0</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;bt BT_SEL 1</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;bt BT_SEL 2</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;bt BT_SEL 3</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;bt BT_SEL 4</t>
         </is>
       </c>
@@ -9750,31 +9750,31 @@
       <c r="I83" s="7" t="inlineStr"/>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;none</t>
         </is>
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;out OUT_USB</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="N83" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;none</t>
         </is>
       </c>
@@ -9831,74 +9831,74 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;bt BT_CLR_ALL</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;none</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;none</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 15
 &amp;none</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr"/>
       <c r="I85" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 17
 &amp;none</t>
         </is>
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 18
 &amp;none</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 19
 &amp;none</t>
         </is>
       </c>
       <c r="M85" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 20
 &amp;none</t>
         </is>
       </c>
       <c r="N85" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 21
 &amp;none</t>
         </is>
       </c>
@@ -9935,74 +9935,74 @@
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 22
 &amp;none</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 23
 &amp;none</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 24
 &amp;bt BT_CLR</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 25
 &amp;none</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 26
 &amp;out OUT_BLE</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>mo中央L
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr"/>
       <c r="I87" s="7" t="inlineStr">
         <is>
-          <t>mo中央R
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 29
 &amp;none</t>
         </is>
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 30
 &amp;none</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="N87" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 33
 &amp;none</t>
         </is>
       </c>
@@ -10043,50 +10043,50 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr"/>
       <c r="I89" s="7" t="inlineStr">
         <is>
-          <t>mo2 (center)
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -10095,7 +10095,7 @@
       <c r="M89" s="7" t="inlineStr"/>
       <c r="N89" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 42
 &amp;none</t>
         </is>
       </c>
@@ -10148,31 +10148,31 @@
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>Q
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>W
+          <t>pos 1
 &amp;kp LS(LC(RIGHT))</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>E
+          <t>pos 2
 &amp;kp LS(LC(RIGHT))</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>R
+          <t>pos 3
 &amp;none</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>T
+          <t>pos 4
 &amp;none</t>
         </is>
       </c>
@@ -10181,31 +10181,31 @@
       <c r="I92" s="7" t="inlineStr"/>
       <c r="J92" s="7" t="inlineStr">
         <is>
-          <t>Y
+          <t>pos 5
 &amp;macro_vim_visual_y</t>
         </is>
       </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
-          <t>U
+          <t>pos 6
 &amp;none</t>
         </is>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
-          <t>I
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="M92" s="7" t="inlineStr">
         <is>
-          <t>O
+          <t>pos 8
 &amp;none</t>
         </is>
       </c>
       <c r="N92" s="7" t="inlineStr">
         <is>
-          <t>P
+          <t>pos 9
 &amp;macro_vim_visual_p</t>
         </is>
       </c>
@@ -10254,74 +10254,74 @@
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>A
+          <t>pos 10
 &amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>S
+          <t>pos 11
 &amp;none</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>D
+          <t>pos 12
 &amp;macro_vim_visual_cut</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>F
+          <t>pos 13
 &amp;none</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>G
+          <t>pos 14
 &amp;mm_vim_visual_g</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 15
 &amp;none</t>
         </is>
       </c>
       <c r="H94" s="7" t="inlineStr"/>
       <c r="I94" s="7" t="inlineStr">
         <is>
-          <t>中央
+          <t>pos 16
 &amp;none</t>
         </is>
       </c>
       <c r="J94" s="7" t="inlineStr">
         <is>
-          <t>H
+          <t>pos 17
 &amp;kp LS(LEFT)</t>
         </is>
       </c>
       <c r="K94" s="7" t="inlineStr">
         <is>
-          <t>J
+          <t>pos 18
 &amp;kp LS(DOWN)</t>
         </is>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
-          <t>K
+          <t>pos 19
 &amp;kp LS(UP)</t>
         </is>
       </c>
       <c r="M94" s="7" t="inlineStr">
         <is>
-          <t>L
+          <t>pos 20
 &amp;kp LS(RIGHT)</t>
         </is>
       </c>
       <c r="N94" s="7" t="inlineStr">
         <is>
-          <t>-
+          <t>pos 21
 &amp;kp RCTRL</t>
         </is>
       </c>
@@ -10495,74 +10495,74 @@
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>Z
+          <t>pos 22
 &amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>X
+          <t>pos 23
 &amp;macro_vim_visual_cut</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>C
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>V
+          <t>pos 25
 &amp;macro_vim_visual_exit</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>B
+          <t>pos 26
 &amp;kp LS(LC(LEFT))</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>mo中央L
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="H98" s="7" t="inlineStr"/>
       <c r="I98" s="7" t="inlineStr">
         <is>
-          <t>mo中央R
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="J98" s="7" t="inlineStr">
         <is>
-          <t>N
+          <t>pos 29
 &amp;kp F3</t>
         </is>
       </c>
       <c r="K98" s="7" t="inlineStr">
         <is>
-          <t>M
+          <t>pos 30
 &amp;none</t>
         </is>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
-          <t>,
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
       <c r="M98" s="7" t="inlineStr">
         <is>
-          <t>.
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="N98" s="7" t="inlineStr">
         <is>
-          <t>/
+          <t>pos 33
 &amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
@@ -10619,50 +10619,50 @@
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>mo6 (L outer)
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>LWin
+          <t>pos 35
 &amp;none</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>LAlt
+          <t>pos 36
 &amp;none</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>SPACE
+          <t>pos 38
 &amp;none</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>mo1 (L center)
+          <t>pos 39
 &amp;none</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr"/>
       <c r="I100" s="7" t="inlineStr">
         <is>
-          <t>mo2 (center)
+          <t>pos 40
 &amp;none</t>
         </is>
       </c>
       <c r="J100" s="7" t="inlineStr">
         <is>
-          <t>lt1 ENTER
+          <t>pos 41
 &amp;none</t>
         </is>
       </c>
@@ -10671,7 +10671,7 @@
       <c r="M100" s="7" t="inlineStr"/>
       <c r="N100" s="7" t="inlineStr">
         <is>
-          <t>mo6 (R outer)
+          <t>pos 42
 &amp;none</t>
         </is>
       </c>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -3949,9 +3949,17 @@
       <c r="H68" s="9" t="inlineStr"/>
       <c r="I68" s="9" t="inlineStr"/>
       <c r="J68" s="9" t="inlineStr"/>
-      <c r="K68" s="9" t="inlineStr"/>
+      <c r="K68" s="9" t="inlineStr">
+        <is>
+          <t>🖱左</t>
+        </is>
+      </c>
       <c r="L68" s="9" t="inlineStr"/>
-      <c r="M68" s="9" t="inlineStr"/>
+      <c r="M68" s="9" t="inlineStr">
+        <is>
+          <t>🖱右</t>
+        </is>
+      </c>
       <c r="N68" s="9" t="inlineStr"/>
     </row>
     <row r="69" ht="30" customHeight="1">
@@ -4049,9 +4057,17 @@
       <c r="H70" s="9" t="inlineStr"/>
       <c r="I70" s="9" t="inlineStr"/>
       <c r="J70" s="9" t="inlineStr"/>
-      <c r="K70" s="9" t="inlineStr"/>
+      <c r="K70" s="9" t="inlineStr">
+        <is>
+          <t>🖱戻</t>
+        </is>
+      </c>
       <c r="L70" s="9" t="inlineStr"/>
-      <c r="M70" s="9" t="inlineStr"/>
+      <c r="M70" s="9" t="inlineStr">
+        <is>
+          <t>🖱進</t>
+        </is>
+      </c>
       <c r="N70" s="9" t="inlineStr"/>
     </row>
     <row r="71" ht="30" customHeight="1">
@@ -4670,16 +4686,40 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B84" s="9" t="inlineStr"/>
-      <c r="C84" s="9" t="inlineStr"/>
-      <c r="D84" s="9" t="inlineStr"/>
-      <c r="E84" s="9" t="inlineStr"/>
-      <c r="F84" s="9" t="inlineStr"/>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>BT0</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>BT1</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>BT2</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>BT3</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>BT4</t>
+        </is>
+      </c>
       <c r="G84" s="9" t="inlineStr"/>
       <c r="H84" s="9" t="inlineStr"/>
       <c r="I84" s="9" t="inlineStr"/>
       <c r="J84" s="9" t="inlineStr"/>
-      <c r="K84" s="9" t="inlineStr"/>
+      <c r="K84" s="9" t="inlineStr">
+        <is>
+          <t>USB出力</t>
+        </is>
+      </c>
       <c r="L84" s="9" t="inlineStr"/>
       <c r="M84" s="9" t="inlineStr"/>
       <c r="N84" s="9" t="inlineStr"/>
@@ -4770,7 +4810,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B86" s="9" t="inlineStr"/>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>BT全解除</t>
+        </is>
+      </c>
       <c r="C86" s="9" t="inlineStr"/>
       <c r="D86" s="9" t="inlineStr"/>
       <c r="E86" s="9" t="inlineStr"/>
@@ -4872,9 +4916,17 @@
       </c>
       <c r="B88" s="9" t="inlineStr"/>
       <c r="C88" s="9" t="inlineStr"/>
-      <c r="D88" s="9" t="inlineStr"/>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>BT解除</t>
+        </is>
+      </c>
       <c r="E88" s="9" t="inlineStr"/>
-      <c r="F88" s="9" t="inlineStr"/>
+      <c r="F88" s="9" t="inlineStr">
+        <is>
+          <t>BLE出力</t>
+        </is>
+      </c>
       <c r="G88" s="9" t="inlineStr"/>
       <c r="H88" s="9" t="inlineStr"/>
       <c r="I88" s="9" t="inlineStr"/>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -4392,7 +4392,11 @@
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr"/>
-      <c r="C77" s="9" t="inlineStr"/>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>リセット</t>
+        </is>
+      </c>
       <c r="D77" s="9" t="inlineStr"/>
       <c r="E77" s="9" t="inlineStr"/>
       <c r="F77" s="9" t="inlineStr"/>
@@ -4402,7 +4406,11 @@
       <c r="J77" s="9" t="inlineStr"/>
       <c r="K77" s="9" t="inlineStr"/>
       <c r="L77" s="9" t="inlineStr"/>
-      <c r="M77" s="9" t="inlineStr"/>
+      <c r="M77" s="9" t="inlineStr">
+        <is>
+          <t>リセット</t>
+        </is>
+      </c>
       <c r="N77" s="9" t="inlineStr"/>
     </row>
     <row r="78" ht="30" customHeight="1">
@@ -4495,11 +4503,19 @@
       <c r="C79" s="9" t="inlineStr"/>
       <c r="D79" s="9" t="inlineStr"/>
       <c r="E79" s="9" t="inlineStr"/>
-      <c r="F79" s="9" t="inlineStr"/>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>ブートローダ</t>
+        </is>
+      </c>
       <c r="G79" s="9" t="inlineStr"/>
       <c r="H79" s="9" t="inlineStr"/>
       <c r="I79" s="9" t="inlineStr"/>
-      <c r="J79" s="9" t="inlineStr"/>
+      <c r="J79" s="9" t="inlineStr">
+        <is>
+          <t>ブートローダ</t>
+        </is>
+      </c>
       <c r="K79" s="9" t="inlineStr"/>
       <c r="L79" s="9" t="inlineStr"/>
       <c r="M79" s="9" t="inlineStr"/>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -3949,9 +3949,17 @@
       <c r="H68" s="9" t="inlineStr"/>
       <c r="I68" s="9" t="inlineStr"/>
       <c r="J68" s="9" t="inlineStr"/>
-      <c r="K68" s="9" t="inlineStr"/>
+      <c r="K68" s="9" t="inlineStr">
+        <is>
+          <t>🖱左</t>
+        </is>
+      </c>
       <c r="L68" s="9" t="inlineStr"/>
-      <c r="M68" s="9" t="inlineStr"/>
+      <c r="M68" s="9" t="inlineStr">
+        <is>
+          <t>🖱右</t>
+        </is>
+      </c>
       <c r="N68" s="9" t="inlineStr"/>
     </row>
     <row r="69" ht="30" customHeight="1">
@@ -4049,9 +4057,17 @@
       <c r="H70" s="9" t="inlineStr"/>
       <c r="I70" s="9" t="inlineStr"/>
       <c r="J70" s="9" t="inlineStr"/>
-      <c r="K70" s="9" t="inlineStr"/>
+      <c r="K70" s="9" t="inlineStr">
+        <is>
+          <t>🖱戻</t>
+        </is>
+      </c>
       <c r="L70" s="9" t="inlineStr"/>
-      <c r="M70" s="9" t="inlineStr"/>
+      <c r="M70" s="9" t="inlineStr">
+        <is>
+          <t>🖱進</t>
+        </is>
+      </c>
       <c r="N70" s="9" t="inlineStr"/>
     </row>
     <row r="71" ht="30" customHeight="1">
@@ -4376,7 +4392,11 @@
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr"/>
-      <c r="C77" s="9" t="inlineStr"/>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>リセット</t>
+        </is>
+      </c>
       <c r="D77" s="9" t="inlineStr"/>
       <c r="E77" s="9" t="inlineStr"/>
       <c r="F77" s="9" t="inlineStr"/>
@@ -4386,7 +4406,11 @@
       <c r="J77" s="9" t="inlineStr"/>
       <c r="K77" s="9" t="inlineStr"/>
       <c r="L77" s="9" t="inlineStr"/>
-      <c r="M77" s="9" t="inlineStr"/>
+      <c r="M77" s="9" t="inlineStr">
+        <is>
+          <t>リセット</t>
+        </is>
+      </c>
       <c r="N77" s="9" t="inlineStr"/>
     </row>
     <row r="78" ht="30" customHeight="1">
@@ -4479,11 +4503,19 @@
       <c r="C79" s="9" t="inlineStr"/>
       <c r="D79" s="9" t="inlineStr"/>
       <c r="E79" s="9" t="inlineStr"/>
-      <c r="F79" s="9" t="inlineStr"/>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>ブートローダ</t>
+        </is>
+      </c>
       <c r="G79" s="9" t="inlineStr"/>
       <c r="H79" s="9" t="inlineStr"/>
       <c r="I79" s="9" t="inlineStr"/>
-      <c r="J79" s="9" t="inlineStr"/>
+      <c r="J79" s="9" t="inlineStr">
+        <is>
+          <t>ブートローダ</t>
+        </is>
+      </c>
       <c r="K79" s="9" t="inlineStr"/>
       <c r="L79" s="9" t="inlineStr"/>
       <c r="M79" s="9" t="inlineStr"/>
@@ -4670,16 +4702,40 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B84" s="9" t="inlineStr"/>
-      <c r="C84" s="9" t="inlineStr"/>
-      <c r="D84" s="9" t="inlineStr"/>
-      <c r="E84" s="9" t="inlineStr"/>
-      <c r="F84" s="9" t="inlineStr"/>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>BT0</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>BT1</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>BT2</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>BT3</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>BT4</t>
+        </is>
+      </c>
       <c r="G84" s="9" t="inlineStr"/>
       <c r="H84" s="9" t="inlineStr"/>
       <c r="I84" s="9" t="inlineStr"/>
       <c r="J84" s="9" t="inlineStr"/>
-      <c r="K84" s="9" t="inlineStr"/>
+      <c r="K84" s="9" t="inlineStr">
+        <is>
+          <t>USB出力</t>
+        </is>
+      </c>
       <c r="L84" s="9" t="inlineStr"/>
       <c r="M84" s="9" t="inlineStr"/>
       <c r="N84" s="9" t="inlineStr"/>
@@ -4770,7 +4826,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B86" s="9" t="inlineStr"/>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>BT全解除</t>
+        </is>
+      </c>
       <c r="C86" s="9" t="inlineStr"/>
       <c r="D86" s="9" t="inlineStr"/>
       <c r="E86" s="9" t="inlineStr"/>
@@ -4872,9 +4932,17 @@
       </c>
       <c r="B88" s="9" t="inlineStr"/>
       <c r="C88" s="9" t="inlineStr"/>
-      <c r="D88" s="9" t="inlineStr"/>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>BT解除</t>
+        </is>
+      </c>
       <c r="E88" s="9" t="inlineStr"/>
-      <c r="F88" s="9" t="inlineStr"/>
+      <c r="F88" s="9" t="inlineStr">
+        <is>
+          <t>BLE出力</t>
+        </is>
+      </c>
       <c r="G88" s="9" t="inlineStr"/>
       <c r="H88" s="9" t="inlineStr"/>
       <c r="I88" s="9" t="inlineStr"/>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N101"/>
+  <dimension ref="A1:N111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5574,7 +5574,7 @@
       <c r="G100" s="7" t="inlineStr">
         <is>
           <t>pos 39
-&amp;none</t>
+&amp;mo VIM_VISUAL_SYM</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr"/>
@@ -5587,7 +5587,7 @@
       <c r="J100" s="7" t="inlineStr">
         <is>
           <t>pos 41
-&amp;none</t>
+&amp;mo VIM_VISUAL_SYM</t>
         </is>
       </c>
       <c r="K100" s="7" t="inlineStr"/>
@@ -5611,17 +5611,476 @@
       <c r="D101" s="9" t="inlineStr"/>
       <c r="E101" s="9" t="inlineStr"/>
       <c r="F101" s="9" t="inlineStr"/>
-      <c r="G101" s="9" t="inlineStr"/>
+      <c r="G101" s="9" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
       <c r="H101" s="9" t="inlineStr"/>
       <c r="I101" s="9" t="inlineStr"/>
-      <c r="J101" s="9" t="inlineStr"/>
+      <c r="J101" s="9" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
       <c r="K101" s="9" t="inlineStr"/>
       <c r="L101" s="9" t="inlineStr"/>
       <c r="M101" s="9" t="inlineStr"/>
       <c r="N101" s="9" t="inlineStr"/>
     </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>VIM_VISUAL_SYM レイヤー</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="n"/>
+      <c r="C102" s="4" t="n"/>
+      <c r="D102" s="4" t="n"/>
+      <c r="E102" s="4" t="n"/>
+      <c r="F102" s="4" t="n"/>
+      <c r="G102" s="4" t="n"/>
+      <c r="H102" s="4" t="n"/>
+      <c r="I102" s="4" t="n"/>
+      <c r="J102" s="4" t="n"/>
+      <c r="K102" s="4" t="n"/>
+      <c r="L102" s="4" t="n"/>
+      <c r="M102" s="4" t="n"/>
+      <c r="N102" s="5" t="n"/>
+    </row>
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>Row 1</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>pos 0
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>pos 1
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>pos 2
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>pos 3
+&amp;mm_vim_visual_shift_4</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>pos 4
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="inlineStr"/>
+      <c r="H103" s="7" t="inlineStr"/>
+      <c r="I103" s="7" t="inlineStr"/>
+      <c r="J103" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;mm_vim_visual_shift_6</t>
+        </is>
+      </c>
+      <c r="K103" s="7" t="inlineStr">
+        <is>
+          <t>pos 6
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L103" s="7" t="inlineStr">
+        <is>
+          <t>pos 7
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M103" s="7" t="inlineStr">
+        <is>
+          <t>pos 8
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N103" s="7" t="inlineStr">
+        <is>
+          <t>pos 9
+&amp;kp LS(HOME)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="inlineStr"/>
+      <c r="C104" s="9" t="inlineStr"/>
+      <c r="D104" s="9" t="inlineStr"/>
+      <c r="E104" s="9" t="inlineStr"/>
+      <c r="F104" s="9" t="inlineStr"/>
+      <c r="G104" s="9" t="inlineStr"/>
+      <c r="H104" s="9" t="inlineStr"/>
+      <c r="I104" s="9" t="inlineStr"/>
+      <c r="J104" s="9" t="inlineStr"/>
+      <c r="K104" s="9" t="inlineStr"/>
+      <c r="L104" s="9" t="inlineStr"/>
+      <c r="M104" s="9" t="inlineStr"/>
+      <c r="N104" s="9" t="inlineStr">
+        <is>
+          <t>⇧HOME</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>Shift+</t>
+        </is>
+      </c>
+      <c r="B105" s="9" t="inlineStr"/>
+      <c r="C105" s="9" t="inlineStr"/>
+      <c r="D105" s="9" t="inlineStr"/>
+      <c r="E105" s="9" t="inlineStr">
+        <is>
+          <t>⇧END</t>
+        </is>
+      </c>
+      <c r="F105" s="9" t="inlineStr"/>
+      <c r="G105" s="9" t="inlineStr"/>
+      <c r="H105" s="9" t="inlineStr"/>
+      <c r="I105" s="9" t="inlineStr"/>
+      <c r="J105" s="9" t="inlineStr">
+        <is>
+          <t>⇧HOME</t>
+        </is>
+      </c>
+      <c r="K105" s="9" t="inlineStr"/>
+      <c r="L105" s="9" t="inlineStr"/>
+      <c r="M105" s="9" t="inlineStr"/>
+      <c r="N105" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="30" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>Row 2</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>pos 10
+&amp;kp LCTRL</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>pos 11
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>pos 12
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>pos 13
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>pos 14
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;none</t>
+        </is>
+      </c>
+      <c r="H106" s="7" t="inlineStr"/>
+      <c r="I106" s="7" t="inlineStr">
+        <is>
+          <t>pos 16
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J106" s="7" t="inlineStr">
+        <is>
+          <t>pos 17
+&amp;kp LS(LEFT)</t>
+        </is>
+      </c>
+      <c r="K106" s="7" t="inlineStr">
+        <is>
+          <t>pos 18
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L106" s="7" t="inlineStr">
+        <is>
+          <t>pos 19
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M106" s="7" t="inlineStr">
+        <is>
+          <t>pos 20
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N106" s="7" t="inlineStr">
+        <is>
+          <t>pos 21
+&amp;kp RCTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>LCtrl</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr"/>
+      <c r="D107" s="9" t="inlineStr"/>
+      <c r="E107" s="9" t="inlineStr"/>
+      <c r="F107" s="9" t="inlineStr"/>
+      <c r="G107" s="9" t="inlineStr"/>
+      <c r="H107" s="9" t="inlineStr"/>
+      <c r="I107" s="9" t="inlineStr"/>
+      <c r="J107" s="9" t="inlineStr">
+        <is>
+          <t>⇧←</t>
+        </is>
+      </c>
+      <c r="K107" s="9" t="inlineStr"/>
+      <c r="L107" s="9" t="inlineStr"/>
+      <c r="M107" s="9" t="inlineStr"/>
+      <c r="N107" s="9" t="inlineStr">
+        <is>
+          <t>RCtrl</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="30" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>Row 3</t>
+        </is>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>pos 22
+&amp;kp LEFT_SHIFT</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>pos 23
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>pos 24
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>pos 25
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>pos 26
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>pos 27
+&amp;none</t>
+        </is>
+      </c>
+      <c r="H108" s="7" t="inlineStr"/>
+      <c r="I108" s="7" t="inlineStr">
+        <is>
+          <t>pos 28
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J108" s="7" t="inlineStr">
+        <is>
+          <t>pos 29
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K108" s="7" t="inlineStr">
+        <is>
+          <t>pos 30
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L108" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M108" s="7" t="inlineStr">
+        <is>
+          <t>pos 32
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N108" s="7" t="inlineStr">
+        <is>
+          <t>pos 33
+&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>LShift</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="inlineStr"/>
+      <c r="D109" s="9" t="inlineStr"/>
+      <c r="E109" s="9" t="inlineStr"/>
+      <c r="F109" s="9" t="inlineStr"/>
+      <c r="G109" s="9" t="inlineStr"/>
+      <c r="H109" s="9" t="inlineStr"/>
+      <c r="I109" s="9" t="inlineStr"/>
+      <c r="J109" s="9" t="inlineStr"/>
+      <c r="K109" s="9" t="inlineStr"/>
+      <c r="L109" s="9" t="inlineStr"/>
+      <c r="M109" s="9" t="inlineStr"/>
+      <c r="N109" s="9" t="inlineStr">
+        <is>
+          <t>RShift</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="30" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>Row 4</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>pos 34
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>pos 35
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>pos 36
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>pos 37
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F110" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G110" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="H110" s="7" t="inlineStr"/>
+      <c r="I110" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J110" s="7" t="inlineStr">
+        <is>
+          <t>pos 41
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K110" s="7" t="inlineStr"/>
+      <c r="L110" s="7" t="inlineStr"/>
+      <c r="M110" s="7" t="inlineStr"/>
+      <c r="N110" s="7" t="inlineStr">
+        <is>
+          <t>pos 42
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B111" s="9" t="inlineStr"/>
+      <c r="C111" s="9" t="inlineStr"/>
+      <c r="D111" s="9" t="inlineStr"/>
+      <c r="E111" s="9" t="inlineStr"/>
+      <c r="F111" s="9" t="inlineStr"/>
+      <c r="G111" s="9" t="inlineStr"/>
+      <c r="H111" s="9" t="inlineStr"/>
+      <c r="I111" s="9" t="inlineStr"/>
+      <c r="J111" s="9" t="inlineStr"/>
+      <c r="K111" s="9" t="inlineStr"/>
+      <c r="L111" s="9" t="inlineStr"/>
+      <c r="M111" s="9" t="inlineStr"/>
+      <c r="N111" s="9" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A91:N91"/>
     <mergeCell ref="A55:N55"/>
     <mergeCell ref="A4:N4"/>
@@ -5631,6 +6090,7 @@
     <mergeCell ref="A82:N82"/>
     <mergeCell ref="A73:N73"/>
     <mergeCell ref="A28:N28"/>
+    <mergeCell ref="A102:N102"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5642,7 +6102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N101"/>
+  <dimension ref="A1:N111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10718,7 +11178,7 @@
       <c r="G100" s="7" t="inlineStr">
         <is>
           <t>pos 39
-&amp;none</t>
+&amp;mo VIM_VISUAL_SYM</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr"/>
@@ -10731,7 +11191,7 @@
       <c r="J100" s="7" t="inlineStr">
         <is>
           <t>pos 41
-&amp;none</t>
+&amp;mo VIM_VISUAL_SYM</t>
         </is>
       </c>
       <c r="K100" s="7" t="inlineStr"/>
@@ -10755,17 +11215,488 @@
       <c r="D101" s="9" t="inlineStr"/>
       <c r="E101" s="9" t="inlineStr"/>
       <c r="F101" s="9" t="inlineStr"/>
-      <c r="G101" s="9" t="inlineStr"/>
+      <c r="G101" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mo VIM_VISUAL_SYM</t>
+        </is>
+      </c>
       <c r="H101" s="9" t="inlineStr"/>
       <c r="I101" s="9" t="inlineStr"/>
-      <c r="J101" s="9" t="inlineStr"/>
+      <c r="J101" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mo VIM_VISUAL_SYM</t>
+        </is>
+      </c>
       <c r="K101" s="9" t="inlineStr"/>
       <c r="L101" s="9" t="inlineStr"/>
       <c r="M101" s="9" t="inlineStr"/>
       <c r="N101" s="9" t="inlineStr"/>
     </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>VIM_VISUAL_SYM レイヤー</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="n"/>
+      <c r="C102" s="4" t="n"/>
+      <c r="D102" s="4" t="n"/>
+      <c r="E102" s="4" t="n"/>
+      <c r="F102" s="4" t="n"/>
+      <c r="G102" s="4" t="n"/>
+      <c r="H102" s="4" t="n"/>
+      <c r="I102" s="4" t="n"/>
+      <c r="J102" s="4" t="n"/>
+      <c r="K102" s="4" t="n"/>
+      <c r="L102" s="4" t="n"/>
+      <c r="M102" s="4" t="n"/>
+      <c r="N102" s="5" t="n"/>
+    </row>
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>Row 1</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>pos 0
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>pos 1
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>pos 2
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>pos 3
+&amp;mm_vim_visual_shift_4</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>pos 4
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="inlineStr"/>
+      <c r="H103" s="7" t="inlineStr"/>
+      <c r="I103" s="7" t="inlineStr"/>
+      <c r="J103" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;mm_vim_visual_shift_6</t>
+        </is>
+      </c>
+      <c r="K103" s="7" t="inlineStr">
+        <is>
+          <t>pos 6
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L103" s="7" t="inlineStr">
+        <is>
+          <t>pos 7
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M103" s="7" t="inlineStr">
+        <is>
+          <t>pos 8
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N103" s="7" t="inlineStr">
+        <is>
+          <t>pos 9
+&amp;kp LS(HOME)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="30" customHeight="1">
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="inlineStr"/>
+      <c r="C104" s="9" t="inlineStr"/>
+      <c r="D104" s="9" t="inlineStr"/>
+      <c r="E104" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_shift_4[0]
+▸ &amp;none</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="inlineStr"/>
+      <c r="G104" s="9" t="inlineStr"/>
+      <c r="H104" s="9" t="inlineStr"/>
+      <c r="I104" s="9" t="inlineStr"/>
+      <c r="J104" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_shift_6[0]
+▸ &amp;none</t>
+        </is>
+      </c>
+      <c r="K104" s="9" t="inlineStr"/>
+      <c r="L104" s="9" t="inlineStr"/>
+      <c r="M104" s="9" t="inlineStr"/>
+      <c r="N104" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LS(HOME)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="30" customHeight="1">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>Shift+</t>
+        </is>
+      </c>
+      <c r="B105" s="9" t="inlineStr"/>
+      <c r="C105" s="9" t="inlineStr"/>
+      <c r="D105" s="9" t="inlineStr"/>
+      <c r="E105" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_shift_4[1]
+▸ &amp;kp LS(END)</t>
+        </is>
+      </c>
+      <c r="F105" s="9" t="inlineStr"/>
+      <c r="G105" s="9" t="inlineStr"/>
+      <c r="H105" s="9" t="inlineStr"/>
+      <c r="I105" s="9" t="inlineStr"/>
+      <c r="J105" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_shift_6[1]
+▸ &amp;kp LS(HOME)</t>
+        </is>
+      </c>
+      <c r="K105" s="9" t="inlineStr"/>
+      <c r="L105" s="9" t="inlineStr"/>
+      <c r="M105" s="9" t="inlineStr"/>
+      <c r="N105" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="30" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>Row 2</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>pos 10
+&amp;kp LCTRL</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>pos 11
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>pos 12
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>pos 13
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>pos 14
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;none</t>
+        </is>
+      </c>
+      <c r="H106" s="7" t="inlineStr"/>
+      <c r="I106" s="7" t="inlineStr">
+        <is>
+          <t>pos 16
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J106" s="7" t="inlineStr">
+        <is>
+          <t>pos 17
+&amp;kp LS(LEFT)</t>
+        </is>
+      </c>
+      <c r="K106" s="7" t="inlineStr">
+        <is>
+          <t>pos 18
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L106" s="7" t="inlineStr">
+        <is>
+          <t>pos 19
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M106" s="7" t="inlineStr">
+        <is>
+          <t>pos 20
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N106" s="7" t="inlineStr">
+        <is>
+          <t>pos 21
+&amp;kp RCTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LCTRL</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr"/>
+      <c r="D107" s="9" t="inlineStr"/>
+      <c r="E107" s="9" t="inlineStr"/>
+      <c r="F107" s="9" t="inlineStr"/>
+      <c r="G107" s="9" t="inlineStr"/>
+      <c r="H107" s="9" t="inlineStr"/>
+      <c r="I107" s="9" t="inlineStr"/>
+      <c r="J107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LS(LEFT)</t>
+        </is>
+      </c>
+      <c r="K107" s="9" t="inlineStr"/>
+      <c r="L107" s="9" t="inlineStr"/>
+      <c r="M107" s="9" t="inlineStr"/>
+      <c r="N107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RCTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="30" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>Row 3</t>
+        </is>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>pos 22
+&amp;kp LEFT_SHIFT</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>pos 23
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>pos 24
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>pos 25
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>pos 26
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>pos 27
+&amp;none</t>
+        </is>
+      </c>
+      <c r="H108" s="7" t="inlineStr"/>
+      <c r="I108" s="7" t="inlineStr">
+        <is>
+          <t>pos 28
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J108" s="7" t="inlineStr">
+        <is>
+          <t>pos 29
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K108" s="7" t="inlineStr">
+        <is>
+          <t>pos 30
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L108" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M108" s="7" t="inlineStr">
+        <is>
+          <t>pos 32
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N108" s="7" t="inlineStr">
+        <is>
+          <t>pos 33
+&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_SHIFT</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="inlineStr"/>
+      <c r="D109" s="9" t="inlineStr"/>
+      <c r="E109" s="9" t="inlineStr"/>
+      <c r="F109" s="9" t="inlineStr"/>
+      <c r="G109" s="9" t="inlineStr"/>
+      <c r="H109" s="9" t="inlineStr"/>
+      <c r="I109" s="9" t="inlineStr"/>
+      <c r="J109" s="9" t="inlineStr"/>
+      <c r="K109" s="9" t="inlineStr"/>
+      <c r="L109" s="9" t="inlineStr"/>
+      <c r="M109" s="9" t="inlineStr"/>
+      <c r="N109" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="30" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>Row 4</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>pos 34
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>pos 35
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>pos 36
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>pos 37
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F110" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G110" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="H110" s="7" t="inlineStr"/>
+      <c r="I110" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J110" s="7" t="inlineStr">
+        <is>
+          <t>pos 41
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K110" s="7" t="inlineStr"/>
+      <c r="L110" s="7" t="inlineStr"/>
+      <c r="M110" s="7" t="inlineStr"/>
+      <c r="N110" s="7" t="inlineStr">
+        <is>
+          <t>pos 42
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B111" s="9" t="inlineStr"/>
+      <c r="C111" s="9" t="inlineStr"/>
+      <c r="D111" s="9" t="inlineStr"/>
+      <c r="E111" s="9" t="inlineStr"/>
+      <c r="F111" s="9" t="inlineStr"/>
+      <c r="G111" s="9" t="inlineStr"/>
+      <c r="H111" s="9" t="inlineStr"/>
+      <c r="I111" s="9" t="inlineStr"/>
+      <c r="J111" s="9" t="inlineStr"/>
+      <c r="K111" s="9" t="inlineStr"/>
+      <c r="L111" s="9" t="inlineStr"/>
+      <c r="M111" s="9" t="inlineStr"/>
+      <c r="N111" s="9" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A91:N91"/>
     <mergeCell ref="A55:N55"/>
     <mergeCell ref="A4:N4"/>
@@ -10775,6 +11706,7 @@
     <mergeCell ref="A82:N82"/>
     <mergeCell ref="A73:N73"/>
     <mergeCell ref="A28:N28"/>
+    <mergeCell ref="A102:N102"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -3348,7 +3348,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>MOUSE_MOVE レイヤー</t>
+          <t>VIM_VISUAL_BASE レイヤー</t>
         </is>
       </c>
       <c r="B55" s="4" t="n"/>
@@ -3380,13 +3380,13 @@
       <c r="C56" s="7" t="inlineStr">
         <is>
           <t>pos 1
-&amp;none</t>
+&amp;kp LS(LC(RIGHT))</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
           <t>pos 2
-&amp;none</t>
+&amp;kp LS(LC(RIGHT))</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
@@ -3407,7 +3407,7 @@
       <c r="J56" s="7" t="inlineStr">
         <is>
           <t>pos 5
-&amp;none</t>
+&amp;macro_vim_visual_y</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
@@ -3431,29 +3431,52 @@
       <c r="N56" s="7" t="inlineStr">
         <is>
           <t>pos 9
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
+&amp;macro_vim_visual_p</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="75" customHeight="1">
       <c r="A57" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr"/>
-      <c r="C57" s="9" t="inlineStr"/>
-      <c r="D57" s="9" t="inlineStr"/>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>⇧⌃→</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>⇧⌃→</t>
+        </is>
+      </c>
       <c r="E57" s="9" t="inlineStr"/>
       <c r="F57" s="9" t="inlineStr"/>
       <c r="G57" s="9" t="inlineStr"/>
       <c r="H57" s="9" t="inlineStr"/>
       <c r="I57" s="9" t="inlineStr"/>
-      <c r="J57" s="9" t="inlineStr"/>
+      <c r="J57" s="10" t="inlineStr">
+        <is>
+          <t>LShift
+▸ RShift
+▸ ⌃C
+▸ →
+▸ ⇒BASE_QWERTY</t>
+        </is>
+      </c>
       <c r="K57" s="9" t="inlineStr"/>
       <c r="L57" s="9" t="inlineStr"/>
       <c r="M57" s="9" t="inlineStr"/>
-      <c r="N57" s="9" t="inlineStr"/>
+      <c r="N57" s="10" t="inlineStr">
+        <is>
+          <t>LShift
+▸ RShift
+▸ ⌃V
+▸ ⇒BASE_QWERTY</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
@@ -3464,7 +3487,7 @@
       <c r="B58" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
@@ -3476,7 +3499,7 @@
       <c r="D58" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;macro_vim_visual_cut</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
@@ -3488,7 +3511,7 @@
       <c r="F58" s="7" t="inlineStr">
         <is>
           <t>pos 14
-&amp;none</t>
+&amp;mm_vim_visual_g</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
@@ -3507,430 +3530,499 @@
       <c r="J58" s="7" t="inlineStr">
         <is>
           <t>pos 17
-&amp;none</t>
+&amp;kp LS(LEFT)</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
           <t>pos 18
-&amp;none</t>
+&amp;kp LS(DOWN)</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;mo MOUSE_SCROLL</t>
+&amp;kp LS(UP)</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
+&amp;kp LS(RIGHT)</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
           <t>pos 21
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
+&amp;kp RCTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="60" customHeight="1">
       <c r="A59" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B59" s="9" t="inlineStr"/>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>LCtrl</t>
+        </is>
+      </c>
       <c r="C59" s="9" t="inlineStr"/>
-      <c r="D59" s="9" t="inlineStr"/>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>LShift
+▸ RShift
+▸ ⌃X
+▸ ⇒BASE_QWERTY</t>
+        </is>
+      </c>
       <c r="E59" s="9" t="inlineStr"/>
       <c r="F59" s="9" t="inlineStr"/>
       <c r="G59" s="9" t="inlineStr"/>
       <c r="H59" s="9" t="inlineStr"/>
       <c r="I59" s="9" t="inlineStr"/>
-      <c r="J59" s="9" t="inlineStr"/>
-      <c r="K59" s="9" t="inlineStr"/>
+      <c r="J59" s="9" t="inlineStr">
+        <is>
+          <t>⇧←</t>
+        </is>
+      </c>
+      <c r="K59" s="9" t="inlineStr">
+        <is>
+          <t>⇧↓</t>
+        </is>
+      </c>
       <c r="L59" s="9" t="inlineStr">
         <is>
-          <t>L5</t>
-        </is>
-      </c>
-      <c r="M59" s="9" t="inlineStr"/>
-      <c r="N59" s="9" t="inlineStr"/>
-    </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>Row 3</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>pos 22
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>pos 23
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>pos 24
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>pos 25
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>pos 26
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G60" s="7" t="inlineStr">
-        <is>
-          <t>pos 27
-&amp;none</t>
-        </is>
-      </c>
-      <c r="H60" s="7" t="inlineStr"/>
-      <c r="I60" s="7" t="inlineStr">
-        <is>
-          <t>pos 28
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J60" s="7" t="inlineStr">
-        <is>
-          <t>pos 29
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K60" s="7" t="inlineStr">
-        <is>
-          <t>pos 30
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L60" s="7" t="inlineStr">
-        <is>
-          <t>pos 31
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M60" s="7" t="inlineStr">
-        <is>
-          <t>pos 32
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N60" s="7" t="inlineStr">
-        <is>
-          <t>pos 33
-&amp;none</t>
+          <t>⇧↑</t>
+        </is>
+      </c>
+      <c r="M59" s="9" t="inlineStr">
+        <is>
+          <t>⇧→</t>
+        </is>
+      </c>
+      <c r="N59" s="9" t="inlineStr">
+        <is>
+          <t>RCtrl</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>ダブルタップ</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr"/>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr"/>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>⇧⌃HOME</t>
+        </is>
+      </c>
+      <c r="G60" s="9" t="inlineStr"/>
+      <c r="H60" s="9" t="inlineStr"/>
+      <c r="I60" s="9" t="inlineStr"/>
+      <c r="J60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="K60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="L60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B61" s="9" t="inlineStr"/>
+          <t>Shift+</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="C61" s="9" t="inlineStr"/>
-      <c r="D61" s="9" t="inlineStr"/>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="E61" s="9" t="inlineStr"/>
-      <c r="F61" s="9" t="inlineStr"/>
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t>⇧⌃END</t>
+        </is>
+      </c>
       <c r="G61" s="9" t="inlineStr"/>
       <c r="H61" s="9" t="inlineStr"/>
       <c r="I61" s="9" t="inlineStr"/>
-      <c r="J61" s="9" t="inlineStr"/>
-      <c r="K61" s="9" t="inlineStr"/>
-      <c r="L61" s="9" t="inlineStr"/>
-      <c r="M61" s="9" t="inlineStr"/>
-      <c r="N61" s="9" t="inlineStr"/>
+      <c r="J61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="K61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="L61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>Row 4</t>
+          <t>Row 3</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>pos 34
-&amp;none</t>
+          <t>pos 22
+&amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>pos 35
-&amp;none</t>
+          <t>pos 23
+&amp;macro_vim_visual_cut</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>pos 36
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>pos 37
-&amp;none</t>
+          <t>pos 25
+&amp;macro_vim_visual_exit</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>pos 38
-&amp;none</t>
+          <t>pos 26
+&amp;kp LS(LC(LEFT))</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>pos 39
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr"/>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>pos 40
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>pos 41
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K62" s="7" t="inlineStr"/>
-      <c r="L62" s="7" t="inlineStr"/>
-      <c r="M62" s="7" t="inlineStr"/>
+          <t>pos 29
+&amp;kp F3</t>
+        </is>
+      </c>
+      <c r="K62" s="7" t="inlineStr">
+        <is>
+          <t>pos 30
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M62" s="7" t="inlineStr">
+        <is>
+          <t>pos 32
+&amp;none</t>
+        </is>
+      </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>pos 42
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
+          <t>pos 33
+&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="60" customHeight="1">
       <c r="A63" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B63" s="9" t="inlineStr"/>
-      <c r="C63" s="9" t="inlineStr"/>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>LShift</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>LShift
+▸ RShift
+▸ ⌃X
+▸ ⇒BASE_QWERTY</t>
+        </is>
+      </c>
       <c r="D63" s="9" t="inlineStr"/>
-      <c r="E63" s="9" t="inlineStr"/>
-      <c r="F63" s="9" t="inlineStr"/>
+      <c r="E63" s="10" t="inlineStr">
+        <is>
+          <t>LShift
+▸ RShift
+▸ →
+▸ ⇒BASE_QWERTY</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>⇧⌃←</t>
+        </is>
+      </c>
       <c r="G63" s="9" t="inlineStr"/>
       <c r="H63" s="9" t="inlineStr"/>
       <c r="I63" s="9" t="inlineStr"/>
-      <c r="J63" s="9" t="inlineStr"/>
+      <c r="J63" s="9" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
       <c r="K63" s="9" t="inlineStr"/>
       <c r="L63" s="9" t="inlineStr"/>
       <c r="M63" s="9" t="inlineStr"/>
-      <c r="N63" s="9" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>MOUSE_SCROLL レイヤー</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="n"/>
-      <c r="C64" s="4" t="n"/>
-      <c r="D64" s="4" t="n"/>
-      <c r="E64" s="4" t="n"/>
-      <c r="F64" s="4" t="n"/>
-      <c r="G64" s="4" t="n"/>
-      <c r="H64" s="4" t="n"/>
-      <c r="I64" s="4" t="n"/>
-      <c r="J64" s="4" t="n"/>
-      <c r="K64" s="4" t="n"/>
-      <c r="L64" s="4" t="n"/>
-      <c r="M64" s="4" t="n"/>
-      <c r="N64" s="5" t="n"/>
-    </row>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>Row 1</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>pos 0
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>pos 1
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>pos 2
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t>pos 3
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F65" s="7" t="inlineStr">
-        <is>
-          <t>pos 4
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G65" s="7" t="inlineStr"/>
-      <c r="H65" s="7" t="inlineStr"/>
-      <c r="I65" s="7" t="inlineStr"/>
-      <c r="J65" s="7" t="inlineStr">
-        <is>
-          <t>pos 5
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K65" s="7" t="inlineStr">
-        <is>
-          <t>pos 6
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L65" s="7" t="inlineStr">
-        <is>
-          <t>pos 7
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M65" s="7" t="inlineStr">
-        <is>
-          <t>pos 8
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N65" s="7" t="inlineStr">
-        <is>
-          <t>pos 9
-&amp;none</t>
-        </is>
-      </c>
+      <c r="N63" s="9" t="inlineStr">
+        <is>
+          <t>RShift</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Row 4</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>pos 34
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>pos 35
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>pos 36
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>pos 37
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;mo VIM_VISUAL_SYM</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="inlineStr"/>
+      <c r="I64" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J64" s="7" t="inlineStr">
+        <is>
+          <t>pos 41
+&amp;mo VIM_VISUAL_SYM</t>
+        </is>
+      </c>
+      <c r="K64" s="7" t="inlineStr"/>
+      <c r="L64" s="7" t="inlineStr"/>
+      <c r="M64" s="7" t="inlineStr"/>
+      <c r="N64" s="7" t="inlineStr">
+        <is>
+          <t>pos 42
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr"/>
+      <c r="C65" s="9" t="inlineStr"/>
+      <c r="D65" s="9" t="inlineStr"/>
+      <c r="E65" s="9" t="inlineStr"/>
+      <c r="F65" s="9" t="inlineStr"/>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="inlineStr"/>
+      <c r="I65" s="9" t="inlineStr"/>
+      <c r="J65" s="9" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="K65" s="9" t="inlineStr"/>
+      <c r="L65" s="9" t="inlineStr"/>
+      <c r="M65" s="9" t="inlineStr"/>
+      <c r="N65" s="9" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B66" s="9" t="inlineStr"/>
-      <c r="C66" s="9" t="inlineStr"/>
-      <c r="D66" s="9" t="inlineStr"/>
-      <c r="E66" s="9" t="inlineStr"/>
-      <c r="F66" s="9" t="inlineStr"/>
-      <c r="G66" s="9" t="inlineStr"/>
-      <c r="H66" s="9" t="inlineStr"/>
-      <c r="I66" s="9" t="inlineStr"/>
-      <c r="J66" s="9" t="inlineStr"/>
-      <c r="K66" s="9" t="inlineStr"/>
-      <c r="L66" s="9" t="inlineStr"/>
-      <c r="M66" s="9" t="inlineStr"/>
-      <c r="N66" s="9" t="inlineStr"/>
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>VIM_VISUAL_SYM レイヤー</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="n"/>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n"/>
+      <c r="F66" s="4" t="n"/>
+      <c r="G66" s="4" t="n"/>
+      <c r="H66" s="4" t="n"/>
+      <c r="I66" s="4" t="n"/>
+      <c r="J66" s="4" t="n"/>
+      <c r="K66" s="4" t="n"/>
+      <c r="L66" s="4" t="n"/>
+      <c r="M66" s="4" t="n"/>
+      <c r="N66" s="5" t="n"/>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>Row 2</t>
+          <t>Row 1</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>pos 10
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>pos 11
+          <t>pos 1
 &amp;none</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>pos 12
+          <t>pos 2
 &amp;none</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>pos 13
-&amp;none</t>
+          <t>pos 3
+&amp;mm_vim_visual_shift_4</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>pos 14
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G67" s="7" t="inlineStr">
-        <is>
-          <t>pos 15
-&amp;none</t>
-        </is>
-      </c>
+          <t>pos 4
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr"/>
       <c r="H67" s="7" t="inlineStr"/>
-      <c r="I67" s="7" t="inlineStr">
-        <is>
-          <t>pos 16
-&amp;none</t>
-        </is>
-      </c>
+      <c r="I67" s="7" t="inlineStr"/>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>pos 17
-&amp;none</t>
+          <t>pos 5
+&amp;mm_vim_visual_shift_6</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>pos 18
-&amp;mkp MB1</t>
+          <t>pos 6
+&amp;none</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>pos 19
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>pos 20
-&amp;mkp MB2</t>
+          <t>pos 8
+&amp;none</t>
         </is>
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>pos 21
-&amp;none</t>
+          <t>pos 9
+&amp;kp LS(HOME)</t>
         </is>
       </c>
     </row>
@@ -3949,299 +4041,329 @@
       <c r="H68" s="9" t="inlineStr"/>
       <c r="I68" s="9" t="inlineStr"/>
       <c r="J68" s="9" t="inlineStr"/>
-      <c r="K68" s="9" t="inlineStr">
-        <is>
-          <t>🖱左</t>
-        </is>
-      </c>
+      <c r="K68" s="9" t="inlineStr"/>
       <c r="L68" s="9" t="inlineStr"/>
-      <c r="M68" s="9" t="inlineStr">
-        <is>
-          <t>🖱右</t>
-        </is>
-      </c>
-      <c r="N68" s="9" t="inlineStr"/>
-    </row>
-    <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
+      <c r="M68" s="9" t="inlineStr"/>
+      <c r="N68" s="9" t="inlineStr">
+        <is>
+          <t>⇧HOME</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>Shift+</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr"/>
+      <c r="C69" s="9" t="inlineStr"/>
+      <c r="D69" s="9" t="inlineStr"/>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>⇧END</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr"/>
+      <c r="G69" s="9" t="inlineStr"/>
+      <c r="H69" s="9" t="inlineStr"/>
+      <c r="I69" s="9" t="inlineStr"/>
+      <c r="J69" s="9" t="inlineStr">
+        <is>
+          <t>⇧HOME</t>
+        </is>
+      </c>
+      <c r="K69" s="9" t="inlineStr"/>
+      <c r="L69" s="9" t="inlineStr"/>
+      <c r="M69" s="9" t="inlineStr"/>
+      <c r="N69" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Row 2</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>pos 10
+&amp;kp LCTRL</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>pos 11
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>pos 12
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>pos 13
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>pos 14
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;none</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr"/>
+      <c r="I70" s="7" t="inlineStr">
+        <is>
+          <t>pos 16
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J70" s="7" t="inlineStr">
+        <is>
+          <t>pos 17
+&amp;kp LS(LEFT)</t>
+        </is>
+      </c>
+      <c r="K70" s="7" t="inlineStr">
+        <is>
+          <t>pos 18
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L70" s="7" t="inlineStr">
+        <is>
+          <t>pos 19
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M70" s="7" t="inlineStr">
+        <is>
+          <t>pos 20
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N70" s="7" t="inlineStr">
+        <is>
+          <t>pos 21
+&amp;kp RCTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>LCtrl</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr"/>
+      <c r="D71" s="9" t="inlineStr"/>
+      <c r="E71" s="9" t="inlineStr"/>
+      <c r="F71" s="9" t="inlineStr"/>
+      <c r="G71" s="9" t="inlineStr"/>
+      <c r="H71" s="9" t="inlineStr"/>
+      <c r="I71" s="9" t="inlineStr"/>
+      <c r="J71" s="9" t="inlineStr">
+        <is>
+          <t>⇧←</t>
+        </is>
+      </c>
+      <c r="K71" s="9" t="inlineStr"/>
+      <c r="L71" s="9" t="inlineStr"/>
+      <c r="M71" s="9" t="inlineStr"/>
+      <c r="N71" s="9" t="inlineStr">
+        <is>
+          <t>RCtrl</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>Row 3</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
+      <c r="B72" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C69" s="7" t="inlineStr">
+&amp;kp LEFT_SHIFT</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
         <is>
           <t>pos 23
 &amp;none</t>
         </is>
       </c>
-      <c r="D69" s="7" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>pos 24
 &amp;none</t>
         </is>
       </c>
-      <c r="E69" s="7" t="inlineStr">
+      <c r="E72" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
-      <c r="F69" s="7" t="inlineStr">
+      <c r="F72" s="7" t="inlineStr">
         <is>
           <t>pos 26
 &amp;none</t>
         </is>
       </c>
-      <c r="G69" s="7" t="inlineStr">
+      <c r="G72" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="H69" s="7" t="inlineStr"/>
-      <c r="I69" s="7" t="inlineStr">
+      <c r="H72" s="7" t="inlineStr"/>
+      <c r="I72" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="J69" s="7" t="inlineStr">
+      <c r="J72" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;none</t>
         </is>
       </c>
-      <c r="K69" s="7" t="inlineStr">
+      <c r="K72" s="7" t="inlineStr">
         <is>
           <t>pos 30
-&amp;mkp MB4</t>
-        </is>
-      </c>
-      <c r="L69" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L72" s="7" t="inlineStr">
         <is>
           <t>pos 31
 &amp;none</t>
         </is>
       </c>
-      <c r="M69" s="7" t="inlineStr">
+      <c r="M72" s="7" t="inlineStr">
         <is>
           <t>pos 32
-&amp;mkp MB5</t>
-        </is>
-      </c>
-      <c r="N69" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N72" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="8" t="inlineStr">
+&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B70" s="9" t="inlineStr"/>
-      <c r="C70" s="9" t="inlineStr"/>
-      <c r="D70" s="9" t="inlineStr"/>
-      <c r="E70" s="9" t="inlineStr"/>
-      <c r="F70" s="9" t="inlineStr"/>
-      <c r="G70" s="9" t="inlineStr"/>
-      <c r="H70" s="9" t="inlineStr"/>
-      <c r="I70" s="9" t="inlineStr"/>
-      <c r="J70" s="9" t="inlineStr"/>
-      <c r="K70" s="9" t="inlineStr">
-        <is>
-          <t>🖱戻</t>
-        </is>
-      </c>
-      <c r="L70" s="9" t="inlineStr"/>
-      <c r="M70" s="9" t="inlineStr">
-        <is>
-          <t>🖱進</t>
-        </is>
-      </c>
-      <c r="N70" s="9" t="inlineStr"/>
-    </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>Row 4</t>
-        </is>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>pos 34
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>pos 35
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>pos 36
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G71" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="H71" s="7" t="inlineStr"/>
-      <c r="I71" s="7" t="inlineStr">
-        <is>
-          <t>pos 40
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J71" s="7" t="inlineStr">
-        <is>
-          <t>pos 41
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K71" s="7" t="inlineStr"/>
-      <c r="L71" s="7" t="inlineStr"/>
-      <c r="M71" s="7" t="inlineStr"/>
-      <c r="N71" s="7" t="inlineStr">
-        <is>
-          <t>pos 42
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B72" s="9" t="inlineStr"/>
-      <c r="C72" s="9" t="inlineStr"/>
-      <c r="D72" s="9" t="inlineStr"/>
-      <c r="E72" s="9" t="inlineStr"/>
-      <c r="F72" s="9" t="inlineStr"/>
-      <c r="G72" s="9" t="inlineStr"/>
-      <c r="H72" s="9" t="inlineStr"/>
-      <c r="I72" s="9" t="inlineStr"/>
-      <c r="J72" s="9" t="inlineStr"/>
-      <c r="K72" s="9" t="inlineStr"/>
-      <c r="L72" s="9" t="inlineStr"/>
-      <c r="M72" s="9" t="inlineStr"/>
-      <c r="N72" s="9" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>FUNCTION レイヤー</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="n"/>
-      <c r="C73" s="4" t="n"/>
-      <c r="D73" s="4" t="n"/>
-      <c r="E73" s="4" t="n"/>
-      <c r="F73" s="4" t="n"/>
-      <c r="G73" s="4" t="n"/>
-      <c r="H73" s="4" t="n"/>
-      <c r="I73" s="4" t="n"/>
-      <c r="J73" s="4" t="n"/>
-      <c r="K73" s="4" t="n"/>
-      <c r="L73" s="4" t="n"/>
-      <c r="M73" s="4" t="n"/>
-      <c r="N73" s="5" t="n"/>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>LShift</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr"/>
+      <c r="D73" s="9" t="inlineStr"/>
+      <c r="E73" s="9" t="inlineStr"/>
+      <c r="F73" s="9" t="inlineStr"/>
+      <c r="G73" s="9" t="inlineStr"/>
+      <c r="H73" s="9" t="inlineStr"/>
+      <c r="I73" s="9" t="inlineStr"/>
+      <c r="J73" s="9" t="inlineStr"/>
+      <c r="K73" s="9" t="inlineStr"/>
+      <c r="L73" s="9" t="inlineStr"/>
+      <c r="M73" s="9" t="inlineStr"/>
+      <c r="N73" s="9" t="inlineStr">
+        <is>
+          <t>RShift</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>Row 1</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>pos 0
-&amp;kp F1</t>
+          <t>pos 34
+&amp;none</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>pos 1
-&amp;kp F2</t>
+          <t>pos 35
+&amp;none</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>pos 2
-&amp;kp F3</t>
+          <t>pos 36
+&amp;none</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>pos 3
-&amp;kp F4</t>
+          <t>pos 37
+&amp;none</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>pos 4
-&amp;kp F5</t>
-        </is>
-      </c>
-      <c r="G74" s="7" t="inlineStr"/>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
       <c r="H74" s="7" t="inlineStr"/>
-      <c r="I74" s="7" t="inlineStr"/>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>pos 5
-&amp;kp F6</t>
-        </is>
-      </c>
-      <c r="K74" s="7" t="inlineStr">
-        <is>
-          <t>pos 6
-&amp;kp F7</t>
-        </is>
-      </c>
-      <c r="L74" s="7" t="inlineStr">
-        <is>
-          <t>pos 7
-&amp;kp F8</t>
-        </is>
-      </c>
-      <c r="M74" s="7" t="inlineStr">
-        <is>
-          <t>pos 8
-&amp;kp F9</t>
-        </is>
-      </c>
+          <t>pos 41
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K74" s="7" t="inlineStr"/>
+      <c r="L74" s="7" t="inlineStr"/>
+      <c r="M74" s="7" t="inlineStr"/>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>pos 9
-&amp;kp F10</t>
+          <t>pos 42
+&amp;none</t>
         </is>
       </c>
     </row>
@@ -4251,447 +4373,447 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B75" s="9" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="C75" s="9" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="D75" s="9" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="E75" s="9" t="inlineStr">
-        <is>
-          <t>F4</t>
-        </is>
-      </c>
-      <c r="F75" s="9" t="inlineStr">
-        <is>
-          <t>F5</t>
-        </is>
-      </c>
+      <c r="B75" s="9" t="inlineStr"/>
+      <c r="C75" s="9" t="inlineStr"/>
+      <c r="D75" s="9" t="inlineStr"/>
+      <c r="E75" s="9" t="inlineStr"/>
+      <c r="F75" s="9" t="inlineStr"/>
       <c r="G75" s="9" t="inlineStr"/>
       <c r="H75" s="9" t="inlineStr"/>
       <c r="I75" s="9" t="inlineStr"/>
-      <c r="J75" s="9" t="inlineStr">
+      <c r="J75" s="9" t="inlineStr"/>
+      <c r="K75" s="9" t="inlineStr"/>
+      <c r="L75" s="9" t="inlineStr"/>
+      <c r="M75" s="9" t="inlineStr"/>
+      <c r="N75" s="9" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>FUNCTION レイヤー</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="n"/>
+      <c r="C76" s="4" t="n"/>
+      <c r="D76" s="4" t="n"/>
+      <c r="E76" s="4" t="n"/>
+      <c r="F76" s="4" t="n"/>
+      <c r="G76" s="4" t="n"/>
+      <c r="H76" s="4" t="n"/>
+      <c r="I76" s="4" t="n"/>
+      <c r="J76" s="4" t="n"/>
+      <c r="K76" s="4" t="n"/>
+      <c r="L76" s="4" t="n"/>
+      <c r="M76" s="4" t="n"/>
+      <c r="N76" s="5" t="n"/>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Row 1</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>pos 0
+&amp;kp F1</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>pos 1
+&amp;kp F2</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>pos 2
+&amp;kp F3</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>pos 3
+&amp;kp F4</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>pos 4
+&amp;kp F5</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr"/>
+      <c r="H77" s="7" t="inlineStr"/>
+      <c r="I77" s="7" t="inlineStr"/>
+      <c r="J77" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;kp F6</t>
+        </is>
+      </c>
+      <c r="K77" s="7" t="inlineStr">
+        <is>
+          <t>pos 6
+&amp;kp F7</t>
+        </is>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>pos 7
+&amp;kp F8</t>
+        </is>
+      </c>
+      <c r="M77" s="7" t="inlineStr">
+        <is>
+          <t>pos 8
+&amp;kp F9</t>
+        </is>
+      </c>
+      <c r="N77" s="7" t="inlineStr">
+        <is>
+          <t>pos 9
+&amp;kp F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="G78" s="9" t="inlineStr"/>
+      <c r="H78" s="9" t="inlineStr"/>
+      <c r="I78" s="9" t="inlineStr"/>
+      <c r="J78" s="9" t="inlineStr">
         <is>
           <t>F6</t>
         </is>
       </c>
-      <c r="K75" s="9" t="inlineStr">
+      <c r="K78" s="9" t="inlineStr">
         <is>
           <t>F7</t>
         </is>
       </c>
-      <c r="L75" s="9" t="inlineStr">
+      <c r="L78" s="9" t="inlineStr">
         <is>
           <t>F8</t>
         </is>
       </c>
-      <c r="M75" s="9" t="inlineStr">
+      <c r="M78" s="9" t="inlineStr">
         <is>
           <t>F9</t>
         </is>
       </c>
-      <c r="N75" s="9" t="inlineStr">
+      <c r="N78" s="9" t="inlineStr">
         <is>
           <t>F10</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="6" t="inlineStr">
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>Row 2</t>
         </is>
       </c>
-      <c r="B76" s="7" t="inlineStr">
+      <c r="B79" s="7" t="inlineStr">
         <is>
           <t>pos 10
 &amp;none</t>
         </is>
       </c>
-      <c r="C76" s="7" t="inlineStr">
+      <c r="C79" s="7" t="inlineStr">
         <is>
           <t>pos 11
 &amp;sys_reset</t>
         </is>
       </c>
-      <c r="D76" s="7" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>pos 12
 &amp;none</t>
         </is>
       </c>
-      <c r="E76" s="7" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t>pos 13
 &amp;none</t>
         </is>
       </c>
-      <c r="F76" s="7" t="inlineStr">
+      <c r="F79" s="7" t="inlineStr">
         <is>
           <t>pos 14
 &amp;none</t>
         </is>
       </c>
-      <c r="G76" s="7" t="inlineStr">
+      <c r="G79" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;none</t>
         </is>
       </c>
-      <c r="H76" s="7" t="inlineStr"/>
-      <c r="I76" s="7" t="inlineStr">
+      <c r="H79" s="7" t="inlineStr"/>
+      <c r="I79" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="J76" s="7" t="inlineStr">
+      <c r="J79" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="K76" s="7" t="inlineStr">
+      <c r="K79" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;none</t>
         </is>
       </c>
-      <c r="L76" s="7" t="inlineStr">
+      <c r="L79" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;none</t>
         </is>
       </c>
-      <c r="M76" s="7" t="inlineStr">
+      <c r="M79" s="7" t="inlineStr">
         <is>
           <t>pos 20
 &amp;sys_reset</t>
         </is>
       </c>
-      <c r="N76" s="7" t="inlineStr">
+      <c r="N79" s="7" t="inlineStr">
         <is>
           <t>pos 21
 &amp;none</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="8" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B77" s="9" t="inlineStr"/>
-      <c r="C77" s="9" t="inlineStr">
+      <c r="B80" s="9" t="inlineStr"/>
+      <c r="C80" s="9" t="inlineStr">
         <is>
           <t>リセット</t>
         </is>
       </c>
-      <c r="D77" s="9" t="inlineStr"/>
-      <c r="E77" s="9" t="inlineStr"/>
-      <c r="F77" s="9" t="inlineStr"/>
-      <c r="G77" s="9" t="inlineStr"/>
-      <c r="H77" s="9" t="inlineStr"/>
-      <c r="I77" s="9" t="inlineStr"/>
-      <c r="J77" s="9" t="inlineStr"/>
-      <c r="K77" s="9" t="inlineStr"/>
-      <c r="L77" s="9" t="inlineStr"/>
-      <c r="M77" s="9" t="inlineStr">
+      <c r="D80" s="9" t="inlineStr"/>
+      <c r="E80" s="9" t="inlineStr"/>
+      <c r="F80" s="9" t="inlineStr"/>
+      <c r="G80" s="9" t="inlineStr"/>
+      <c r="H80" s="9" t="inlineStr"/>
+      <c r="I80" s="9" t="inlineStr"/>
+      <c r="J80" s="9" t="inlineStr"/>
+      <c r="K80" s="9" t="inlineStr"/>
+      <c r="L80" s="9" t="inlineStr"/>
+      <c r="M80" s="9" t="inlineStr">
         <is>
           <t>リセット</t>
         </is>
       </c>
-      <c r="N77" s="9" t="inlineStr"/>
-    </row>
-    <row r="78" ht="30" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
+      <c r="N80" s="9" t="inlineStr"/>
+    </row>
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>Row 3</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
+      <c r="B81" s="7" t="inlineStr">
         <is>
           <t>pos 22
 &amp;none</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
+      <c r="C81" s="7" t="inlineStr">
         <is>
           <t>pos 23
 &amp;none</t>
         </is>
       </c>
-      <c r="D78" s="7" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr">
         <is>
           <t>pos 24
 &amp;none</t>
         </is>
       </c>
-      <c r="E78" s="7" t="inlineStr">
+      <c r="E81" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
-      <c r="F78" s="7" t="inlineStr">
+      <c r="F81" s="7" t="inlineStr">
         <is>
           <t>pos 26
 &amp;bootloader</t>
         </is>
       </c>
-      <c r="G78" s="7" t="inlineStr">
+      <c r="G81" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="H78" s="7" t="inlineStr"/>
-      <c r="I78" s="7" t="inlineStr">
+      <c r="H81" s="7" t="inlineStr"/>
+      <c r="I81" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="J78" s="7" t="inlineStr">
+      <c r="J81" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;bootloader</t>
         </is>
       </c>
-      <c r="K78" s="7" t="inlineStr">
+      <c r="K81" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;none</t>
         </is>
       </c>
-      <c r="L78" s="7" t="inlineStr">
+      <c r="L81" s="7" t="inlineStr">
         <is>
           <t>pos 31
 &amp;none</t>
         </is>
       </c>
-      <c r="M78" s="7" t="inlineStr">
+      <c r="M81" s="7" t="inlineStr">
         <is>
           <t>pos 32
 &amp;none</t>
         </is>
       </c>
-      <c r="N78" s="7" t="inlineStr">
+      <c r="N81" s="7" t="inlineStr">
         <is>
           <t>pos 33
 &amp;none</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="8" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B79" s="9" t="inlineStr"/>
-      <c r="C79" s="9" t="inlineStr"/>
-      <c r="D79" s="9" t="inlineStr"/>
-      <c r="E79" s="9" t="inlineStr"/>
-      <c r="F79" s="9" t="inlineStr">
+      <c r="B82" s="9" t="inlineStr"/>
+      <c r="C82" s="9" t="inlineStr"/>
+      <c r="D82" s="9" t="inlineStr"/>
+      <c r="E82" s="9" t="inlineStr"/>
+      <c r="F82" s="9" t="inlineStr">
         <is>
           <t>ブートローダ</t>
         </is>
       </c>
-      <c r="G79" s="9" t="inlineStr"/>
-      <c r="H79" s="9" t="inlineStr"/>
-      <c r="I79" s="9" t="inlineStr"/>
-      <c r="J79" s="9" t="inlineStr">
+      <c r="G82" s="9" t="inlineStr"/>
+      <c r="H82" s="9" t="inlineStr"/>
+      <c r="I82" s="9" t="inlineStr"/>
+      <c r="J82" s="9" t="inlineStr">
         <is>
           <t>ブートローダ</t>
         </is>
       </c>
-      <c r="K79" s="9" t="inlineStr"/>
-      <c r="L79" s="9" t="inlineStr"/>
-      <c r="M79" s="9" t="inlineStr"/>
-      <c r="N79" s="9" t="inlineStr"/>
-    </row>
-    <row r="80" ht="30" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>Row 4</t>
-        </is>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>pos 34
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C80" s="7" t="inlineStr">
-        <is>
-          <t>pos 35
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>pos 36
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F80" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G80" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="H80" s="7" t="inlineStr"/>
-      <c r="I80" s="7" t="inlineStr">
-        <is>
-          <t>pos 40
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J80" s="7" t="inlineStr">
-        <is>
-          <t>pos 41
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K80" s="7" t="inlineStr"/>
-      <c r="L80" s="7" t="inlineStr"/>
-      <c r="M80" s="7" t="inlineStr"/>
-      <c r="N80" s="7" t="inlineStr">
-        <is>
-          <t>pos 42
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B81" s="9" t="inlineStr"/>
-      <c r="C81" s="9" t="inlineStr"/>
-      <c r="D81" s="9" t="inlineStr"/>
-      <c r="E81" s="9" t="inlineStr"/>
-      <c r="F81" s="9" t="inlineStr"/>
-      <c r="G81" s="9" t="inlineStr"/>
-      <c r="H81" s="9" t="inlineStr"/>
-      <c r="I81" s="9" t="inlineStr"/>
-      <c r="J81" s="9" t="inlineStr"/>
-      <c r="K81" s="9" t="inlineStr"/>
-      <c r="L81" s="9" t="inlineStr"/>
-      <c r="M81" s="9" t="inlineStr"/>
-      <c r="N81" s="9" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t>BLUETOOTH レイヤー</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="n"/>
-      <c r="C82" s="4" t="n"/>
-      <c r="D82" s="4" t="n"/>
-      <c r="E82" s="4" t="n"/>
-      <c r="F82" s="4" t="n"/>
-      <c r="G82" s="4" t="n"/>
-      <c r="H82" s="4" t="n"/>
-      <c r="I82" s="4" t="n"/>
-      <c r="J82" s="4" t="n"/>
-      <c r="K82" s="4" t="n"/>
-      <c r="L82" s="4" t="n"/>
-      <c r="M82" s="4" t="n"/>
-      <c r="N82" s="5" t="n"/>
+      <c r="K82" s="9" t="inlineStr"/>
+      <c r="L82" s="9" t="inlineStr"/>
+      <c r="M82" s="9" t="inlineStr"/>
+      <c r="N82" s="9" t="inlineStr"/>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>Row 1</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>pos 0
-&amp;bt BT_SEL 0</t>
+          <t>pos 34
+&amp;none</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>pos 1
-&amp;bt BT_SEL 1</t>
+          <t>pos 35
+&amp;none</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>pos 2
-&amp;bt BT_SEL 2</t>
+          <t>pos 36
+&amp;none</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>pos 3
-&amp;bt BT_SEL 3</t>
+          <t>pos 37
+&amp;none</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>pos 4
-&amp;bt BT_SEL 4</t>
-        </is>
-      </c>
-      <c r="G83" s="7" t="inlineStr"/>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
       <c r="H83" s="7" t="inlineStr"/>
-      <c r="I83" s="7" t="inlineStr"/>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>pos 5
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K83" s="7" t="inlineStr">
-        <is>
-          <t>pos 6
-&amp;out OUT_USB</t>
-        </is>
-      </c>
-      <c r="L83" s="7" t="inlineStr">
-        <is>
-          <t>pos 7
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M83" s="7" t="inlineStr">
-        <is>
-          <t>pos 8
-&amp;none</t>
-        </is>
-      </c>
+          <t>pos 41
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K83" s="7" t="inlineStr"/>
+      <c r="L83" s="7" t="inlineStr"/>
+      <c r="M83" s="7" t="inlineStr"/>
       <c r="N83" s="7" t="inlineStr">
         <is>
-          <t>pos 9
+          <t>pos 42
 &amp;none</t>
         </is>
       </c>
@@ -4702,1077 +4824,959 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t>BT0</t>
-        </is>
-      </c>
-      <c r="C84" s="9" t="inlineStr">
-        <is>
-          <t>BT1</t>
-        </is>
-      </c>
-      <c r="D84" s="9" t="inlineStr">
-        <is>
-          <t>BT2</t>
-        </is>
-      </c>
-      <c r="E84" s="9" t="inlineStr">
-        <is>
-          <t>BT3</t>
-        </is>
-      </c>
-      <c r="F84" s="9" t="inlineStr">
-        <is>
-          <t>BT4</t>
-        </is>
-      </c>
+      <c r="B84" s="9" t="inlineStr"/>
+      <c r="C84" s="9" t="inlineStr"/>
+      <c r="D84" s="9" t="inlineStr"/>
+      <c r="E84" s="9" t="inlineStr"/>
+      <c r="F84" s="9" t="inlineStr"/>
       <c r="G84" s="9" t="inlineStr"/>
       <c r="H84" s="9" t="inlineStr"/>
       <c r="I84" s="9" t="inlineStr"/>
       <c r="J84" s="9" t="inlineStr"/>
-      <c r="K84" s="9" t="inlineStr">
-        <is>
-          <t>USB出力</t>
-        </is>
-      </c>
+      <c r="K84" s="9" t="inlineStr"/>
       <c r="L84" s="9" t="inlineStr"/>
       <c r="M84" s="9" t="inlineStr"/>
       <c r="N84" s="9" t="inlineStr"/>
     </row>
-    <row r="85" ht="30" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>BLUETOOTH レイヤー</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="n"/>
+      <c r="C85" s="4" t="n"/>
+      <c r="D85" s="4" t="n"/>
+      <c r="E85" s="4" t="n"/>
+      <c r="F85" s="4" t="n"/>
+      <c r="G85" s="4" t="n"/>
+      <c r="H85" s="4" t="n"/>
+      <c r="I85" s="4" t="n"/>
+      <c r="J85" s="4" t="n"/>
+      <c r="K85" s="4" t="n"/>
+      <c r="L85" s="4" t="n"/>
+      <c r="M85" s="4" t="n"/>
+      <c r="N85" s="5" t="n"/>
+    </row>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>Row 1</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>pos 0
+&amp;bt BT_SEL 0</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>pos 1
+&amp;bt BT_SEL 1</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>pos 2
+&amp;bt BT_SEL 2</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>pos 3
+&amp;bt BT_SEL 3</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>pos 4
+&amp;bt BT_SEL 4</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="inlineStr"/>
+      <c r="H86" s="7" t="inlineStr"/>
+      <c r="I86" s="7" t="inlineStr"/>
+      <c r="J86" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K86" s="7" t="inlineStr">
+        <is>
+          <t>pos 6
+&amp;out OUT_USB</t>
+        </is>
+      </c>
+      <c r="L86" s="7" t="inlineStr">
+        <is>
+          <t>pos 7
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M86" s="7" t="inlineStr">
+        <is>
+          <t>pos 8
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N86" s="7" t="inlineStr">
+        <is>
+          <t>pos 9
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>BT0</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>BT1</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>BT2</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="inlineStr">
+        <is>
+          <t>BT3</t>
+        </is>
+      </c>
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>BT4</t>
+        </is>
+      </c>
+      <c r="G87" s="9" t="inlineStr"/>
+      <c r="H87" s="9" t="inlineStr"/>
+      <c r="I87" s="9" t="inlineStr"/>
+      <c r="J87" s="9" t="inlineStr"/>
+      <c r="K87" s="9" t="inlineStr">
+        <is>
+          <t>USB出力</t>
+        </is>
+      </c>
+      <c r="L87" s="9" t="inlineStr"/>
+      <c r="M87" s="9" t="inlineStr"/>
+      <c r="N87" s="9" t="inlineStr"/>
+    </row>
+    <row r="88" ht="30" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>Row 2</t>
         </is>
       </c>
-      <c r="B85" s="7" t="inlineStr">
+      <c r="B88" s="7" t="inlineStr">
         <is>
           <t>pos 10
 &amp;bt BT_CLR_ALL</t>
         </is>
       </c>
-      <c r="C85" s="7" t="inlineStr">
+      <c r="C88" s="7" t="inlineStr">
         <is>
           <t>pos 11
 &amp;none</t>
         </is>
       </c>
-      <c r="D85" s="7" t="inlineStr">
+      <c r="D88" s="7" t="inlineStr">
         <is>
           <t>pos 12
 &amp;none</t>
         </is>
       </c>
-      <c r="E85" s="7" t="inlineStr">
+      <c r="E88" s="7" t="inlineStr">
         <is>
           <t>pos 13
 &amp;none</t>
         </is>
       </c>
-      <c r="F85" s="7" t="inlineStr">
+      <c r="F88" s="7" t="inlineStr">
         <is>
           <t>pos 14
 &amp;none</t>
         </is>
       </c>
-      <c r="G85" s="7" t="inlineStr">
+      <c r="G88" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;none</t>
         </is>
       </c>
-      <c r="H85" s="7" t="inlineStr"/>
-      <c r="I85" s="7" t="inlineStr">
+      <c r="H88" s="7" t="inlineStr"/>
+      <c r="I88" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="J85" s="7" t="inlineStr">
+      <c r="J88" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="K85" s="7" t="inlineStr">
+      <c r="K88" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;none</t>
         </is>
       </c>
-      <c r="L85" s="7" t="inlineStr">
+      <c r="L88" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;none</t>
         </is>
       </c>
-      <c r="M85" s="7" t="inlineStr">
+      <c r="M88" s="7" t="inlineStr">
         <is>
           <t>pos 20
 &amp;none</t>
         </is>
       </c>
-      <c r="N85" s="7" t="inlineStr">
+      <c r="N88" s="7" t="inlineStr">
         <is>
           <t>pos 21
 &amp;none</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="8" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B86" s="9" t="inlineStr">
+      <c r="B89" s="9" t="inlineStr">
         <is>
           <t>BT全解除</t>
         </is>
       </c>
-      <c r="C86" s="9" t="inlineStr"/>
-      <c r="D86" s="9" t="inlineStr"/>
-      <c r="E86" s="9" t="inlineStr"/>
-      <c r="F86" s="9" t="inlineStr"/>
-      <c r="G86" s="9" t="inlineStr"/>
-      <c r="H86" s="9" t="inlineStr"/>
-      <c r="I86" s="9" t="inlineStr"/>
-      <c r="J86" s="9" t="inlineStr"/>
-      <c r="K86" s="9" t="inlineStr"/>
-      <c r="L86" s="9" t="inlineStr"/>
-      <c r="M86" s="9" t="inlineStr"/>
-      <c r="N86" s="9" t="inlineStr"/>
-    </row>
-    <row r="87" ht="30" customHeight="1">
-      <c r="A87" s="6" t="inlineStr">
+      <c r="C89" s="9" t="inlineStr"/>
+      <c r="D89" s="9" t="inlineStr"/>
+      <c r="E89" s="9" t="inlineStr"/>
+      <c r="F89" s="9" t="inlineStr"/>
+      <c r="G89" s="9" t="inlineStr"/>
+      <c r="H89" s="9" t="inlineStr"/>
+      <c r="I89" s="9" t="inlineStr"/>
+      <c r="J89" s="9" t="inlineStr"/>
+      <c r="K89" s="9" t="inlineStr"/>
+      <c r="L89" s="9" t="inlineStr"/>
+      <c r="M89" s="9" t="inlineStr"/>
+      <c r="N89" s="9" t="inlineStr"/>
+    </row>
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>Row 3</t>
         </is>
       </c>
-      <c r="B87" s="7" t="inlineStr">
+      <c r="B90" s="7" t="inlineStr">
         <is>
           <t>pos 22
 &amp;none</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr">
+      <c r="C90" s="7" t="inlineStr">
         <is>
           <t>pos 23
 &amp;none</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
         <is>
           <t>pos 24
 &amp;bt BT_CLR</t>
         </is>
       </c>
-      <c r="E87" s="7" t="inlineStr">
+      <c r="E90" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
-      <c r="F87" s="7" t="inlineStr">
+      <c r="F90" s="7" t="inlineStr">
         <is>
           <t>pos 26
 &amp;out OUT_BLE</t>
         </is>
       </c>
-      <c r="G87" s="7" t="inlineStr">
+      <c r="G90" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="H87" s="7" t="inlineStr"/>
-      <c r="I87" s="7" t="inlineStr">
+      <c r="H90" s="7" t="inlineStr"/>
+      <c r="I90" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="J87" s="7" t="inlineStr">
+      <c r="J90" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;none</t>
         </is>
       </c>
-      <c r="K87" s="7" t="inlineStr">
+      <c r="K90" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;none</t>
         </is>
       </c>
-      <c r="L87" s="7" t="inlineStr">
+      <c r="L90" s="7" t="inlineStr">
         <is>
           <t>pos 31
 &amp;none</t>
         </is>
       </c>
-      <c r="M87" s="7" t="inlineStr">
+      <c r="M90" s="7" t="inlineStr">
         <is>
           <t>pos 32
 &amp;none</t>
         </is>
       </c>
-      <c r="N87" s="7" t="inlineStr">
+      <c r="N90" s="7" t="inlineStr">
         <is>
           <t>pos 33
 &amp;none</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="8" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B88" s="9" t="inlineStr"/>
-      <c r="C88" s="9" t="inlineStr"/>
-      <c r="D88" s="9" t="inlineStr">
+      <c r="B91" s="9" t="inlineStr"/>
+      <c r="C91" s="9" t="inlineStr"/>
+      <c r="D91" s="9" t="inlineStr">
         <is>
           <t>BT解除</t>
         </is>
       </c>
-      <c r="E88" s="9" t="inlineStr"/>
-      <c r="F88" s="9" t="inlineStr">
+      <c r="E91" s="9" t="inlineStr"/>
+      <c r="F91" s="9" t="inlineStr">
         <is>
           <t>BLE出力</t>
         </is>
       </c>
-      <c r="G88" s="9" t="inlineStr"/>
-      <c r="H88" s="9" t="inlineStr"/>
-      <c r="I88" s="9" t="inlineStr"/>
-      <c r="J88" s="9" t="inlineStr"/>
-      <c r="K88" s="9" t="inlineStr"/>
-      <c r="L88" s="9" t="inlineStr"/>
-      <c r="M88" s="9" t="inlineStr"/>
-      <c r="N88" s="9" t="inlineStr"/>
-    </row>
-    <row r="89" ht="30" customHeight="1">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>Row 4</t>
-        </is>
-      </c>
-      <c r="B89" s="7" t="inlineStr">
-        <is>
-          <t>pos 34
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>pos 35
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>pos 36
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F89" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G89" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="H89" s="7" t="inlineStr"/>
-      <c r="I89" s="7" t="inlineStr">
-        <is>
-          <t>pos 40
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J89" s="7" t="inlineStr">
-        <is>
-          <t>pos 41
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K89" s="7" t="inlineStr"/>
-      <c r="L89" s="7" t="inlineStr"/>
-      <c r="M89" s="7" t="inlineStr"/>
-      <c r="N89" s="7" t="inlineStr">
-        <is>
-          <t>pos 42
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B90" s="9" t="inlineStr"/>
-      <c r="C90" s="9" t="inlineStr"/>
-      <c r="D90" s="9" t="inlineStr"/>
-      <c r="E90" s="9" t="inlineStr"/>
-      <c r="F90" s="9" t="inlineStr"/>
-      <c r="G90" s="9" t="inlineStr"/>
-      <c r="H90" s="9" t="inlineStr"/>
-      <c r="I90" s="9" t="inlineStr"/>
-      <c r="J90" s="9" t="inlineStr"/>
-      <c r="K90" s="9" t="inlineStr"/>
-      <c r="L90" s="9" t="inlineStr"/>
-      <c r="M90" s="9" t="inlineStr"/>
-      <c r="N90" s="9" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>VIM_VISUAL_BASE レイヤー</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="n"/>
-      <c r="C91" s="4" t="n"/>
-      <c r="D91" s="4" t="n"/>
-      <c r="E91" s="4" t="n"/>
-      <c r="F91" s="4" t="n"/>
-      <c r="G91" s="4" t="n"/>
-      <c r="H91" s="4" t="n"/>
-      <c r="I91" s="4" t="n"/>
-      <c r="J91" s="4" t="n"/>
-      <c r="K91" s="4" t="n"/>
-      <c r="L91" s="4" t="n"/>
-      <c r="M91" s="4" t="n"/>
-      <c r="N91" s="5" t="n"/>
+      <c r="G91" s="9" t="inlineStr"/>
+      <c r="H91" s="9" t="inlineStr"/>
+      <c r="I91" s="9" t="inlineStr"/>
+      <c r="J91" s="9" t="inlineStr"/>
+      <c r="K91" s="9" t="inlineStr"/>
+      <c r="L91" s="9" t="inlineStr"/>
+      <c r="M91" s="9" t="inlineStr"/>
+      <c r="N91" s="9" t="inlineStr"/>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>Row 1</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>pos 0
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>pos 1
-&amp;kp LS(LC(RIGHT))</t>
+          <t>pos 35
+&amp;none</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>pos 2
-&amp;kp LS(LC(RIGHT))</t>
+          <t>pos 36
+&amp;none</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>pos 3
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>pos 4
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G92" s="7" t="inlineStr"/>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
       <c r="H92" s="7" t="inlineStr"/>
-      <c r="I92" s="7" t="inlineStr"/>
+      <c r="I92" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
       <c r="J92" s="7" t="inlineStr">
         <is>
-          <t>pos 5
-&amp;macro_vim_visual_y</t>
-        </is>
-      </c>
-      <c r="K92" s="7" t="inlineStr">
-        <is>
-          <t>pos 6
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L92" s="7" t="inlineStr">
-        <is>
-          <t>pos 7
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M92" s="7" t="inlineStr">
-        <is>
-          <t>pos 8
-&amp;none</t>
-        </is>
-      </c>
+          <t>pos 41
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K92" s="7" t="inlineStr"/>
+      <c r="L92" s="7" t="inlineStr"/>
+      <c r="M92" s="7" t="inlineStr"/>
       <c r="N92" s="7" t="inlineStr">
         <is>
-          <t>pos 9
-&amp;macro_vim_visual_p</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="75" customHeight="1">
+          <t>pos 42
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
       <c r="B93" s="9" t="inlineStr"/>
-      <c r="C93" s="9" t="inlineStr">
-        <is>
-          <t>⇧⌃→</t>
-        </is>
-      </c>
-      <c r="D93" s="9" t="inlineStr">
-        <is>
-          <t>⇧⌃→</t>
-        </is>
-      </c>
+      <c r="C93" s="9" t="inlineStr"/>
+      <c r="D93" s="9" t="inlineStr"/>
       <c r="E93" s="9" t="inlineStr"/>
       <c r="F93" s="9" t="inlineStr"/>
       <c r="G93" s="9" t="inlineStr"/>
       <c r="H93" s="9" t="inlineStr"/>
       <c r="I93" s="9" t="inlineStr"/>
-      <c r="J93" s="10" t="inlineStr">
-        <is>
-          <t>LShift
-▸ RShift
-▸ ⌃C
-▸ →
-▸ ⇒BASE_QWERTY</t>
-        </is>
-      </c>
+      <c r="J93" s="9" t="inlineStr"/>
       <c r="K93" s="9" t="inlineStr"/>
       <c r="L93" s="9" t="inlineStr"/>
       <c r="M93" s="9" t="inlineStr"/>
-      <c r="N93" s="10" t="inlineStr">
-        <is>
-          <t>LShift
-▸ RShift
-▸ ⌃V
-▸ ⇒BASE_QWERTY</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="30" customHeight="1">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>Row 2</t>
-        </is>
-      </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>pos 10
-&amp;kp LCTRL</t>
-        </is>
-      </c>
-      <c r="C94" s="7" t="inlineStr">
-        <is>
-          <t>pos 11
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>pos 12
-&amp;macro_vim_visual_cut</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t>pos 13
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F94" s="7" t="inlineStr">
-        <is>
-          <t>pos 14
-&amp;mm_vim_visual_g</t>
-        </is>
-      </c>
-      <c r="G94" s="7" t="inlineStr">
-        <is>
-          <t>pos 15
-&amp;none</t>
-        </is>
-      </c>
-      <c r="H94" s="7" t="inlineStr"/>
-      <c r="I94" s="7" t="inlineStr">
-        <is>
-          <t>pos 16
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J94" s="7" t="inlineStr">
-        <is>
-          <t>pos 17
-&amp;kp LS(LEFT)</t>
-        </is>
-      </c>
-      <c r="K94" s="7" t="inlineStr">
-        <is>
-          <t>pos 18
-&amp;kp LS(DOWN)</t>
-        </is>
-      </c>
-      <c r="L94" s="7" t="inlineStr">
-        <is>
-          <t>pos 19
-&amp;kp LS(UP)</t>
-        </is>
-      </c>
-      <c r="M94" s="7" t="inlineStr">
-        <is>
-          <t>pos 20
-&amp;kp LS(RIGHT)</t>
-        </is>
-      </c>
-      <c r="N94" s="7" t="inlineStr">
-        <is>
-          <t>pos 21
-&amp;kp RCTRL</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B95" s="9" t="inlineStr">
-        <is>
-          <t>LCtrl</t>
-        </is>
-      </c>
-      <c r="C95" s="9" t="inlineStr"/>
-      <c r="D95" s="10" t="inlineStr">
-        <is>
-          <t>LShift
-▸ RShift
-▸ ⌃X
-▸ ⇒BASE_QWERTY</t>
-        </is>
-      </c>
-      <c r="E95" s="9" t="inlineStr"/>
-      <c r="F95" s="9" t="inlineStr"/>
-      <c r="G95" s="9" t="inlineStr"/>
-      <c r="H95" s="9" t="inlineStr"/>
-      <c r="I95" s="9" t="inlineStr"/>
-      <c r="J95" s="9" t="inlineStr">
-        <is>
-          <t>⇧←</t>
-        </is>
-      </c>
-      <c r="K95" s="9" t="inlineStr">
-        <is>
-          <t>⇧↓</t>
-        </is>
-      </c>
-      <c r="L95" s="9" t="inlineStr">
-        <is>
-          <t>⇧↑</t>
-        </is>
-      </c>
-      <c r="M95" s="9" t="inlineStr">
-        <is>
-          <t>⇧→</t>
-        </is>
-      </c>
-      <c r="N95" s="9" t="inlineStr">
-        <is>
-          <t>RCtrl</t>
+      <c r="N93" s="9" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>MOUSE_MOVE レイヤー</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="n"/>
+      <c r="C94" s="4" t="n"/>
+      <c r="D94" s="4" t="n"/>
+      <c r="E94" s="4" t="n"/>
+      <c r="F94" s="4" t="n"/>
+      <c r="G94" s="4" t="n"/>
+      <c r="H94" s="4" t="n"/>
+      <c r="I94" s="4" t="n"/>
+      <c r="J94" s="4" t="n"/>
+      <c r="K94" s="4" t="n"/>
+      <c r="L94" s="4" t="n"/>
+      <c r="M94" s="4" t="n"/>
+      <c r="N94" s="5" t="n"/>
+    </row>
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>Row 1</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>pos 0
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>pos 1
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>pos 2
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>pos 3
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>pos 4
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr"/>
+      <c r="H95" s="7" t="inlineStr"/>
+      <c r="I95" s="7" t="inlineStr"/>
+      <c r="J95" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K95" s="7" t="inlineStr">
+        <is>
+          <t>pos 6
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
+        <is>
+          <t>pos 7
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M95" s="7" t="inlineStr">
+        <is>
+          <t>pos 8
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N95" s="7" t="inlineStr">
+        <is>
+          <t>pos 9
+&amp;none</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t>ダブルタップ</t>
-        </is>
-      </c>
-      <c r="B96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="inlineStr"/>
       <c r="C96" s="9" t="inlineStr"/>
-      <c r="D96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="D96" s="9" t="inlineStr"/>
       <c r="E96" s="9" t="inlineStr"/>
-      <c r="F96" s="9" t="inlineStr">
-        <is>
-          <t>⇧⌃HOME</t>
-        </is>
-      </c>
+      <c r="F96" s="9" t="inlineStr"/>
       <c r="G96" s="9" t="inlineStr"/>
       <c r="H96" s="9" t="inlineStr"/>
       <c r="I96" s="9" t="inlineStr"/>
-      <c r="J96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="K96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="L96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="M96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="8" t="inlineStr">
-        <is>
-          <t>Shift+</t>
-        </is>
-      </c>
-      <c r="B97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="C97" s="9" t="inlineStr"/>
-      <c r="D97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="E97" s="9" t="inlineStr"/>
-      <c r="F97" s="9" t="inlineStr">
-        <is>
-          <t>⇧⌃END</t>
-        </is>
-      </c>
-      <c r="G97" s="9" t="inlineStr"/>
-      <c r="H97" s="9" t="inlineStr"/>
-      <c r="I97" s="9" t="inlineStr"/>
-      <c r="J97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="K97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="L97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="M97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="30" customHeight="1">
-      <c r="A98" s="6" t="inlineStr">
+      <c r="J96" s="9" t="inlineStr"/>
+      <c r="K96" s="9" t="inlineStr"/>
+      <c r="L96" s="9" t="inlineStr"/>
+      <c r="M96" s="9" t="inlineStr"/>
+      <c r="N96" s="9" t="inlineStr"/>
+    </row>
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>Row 2</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>pos 10
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>pos 11
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>pos 12
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>pos 13
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>pos 14
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;none</t>
+        </is>
+      </c>
+      <c r="H97" s="7" t="inlineStr"/>
+      <c r="I97" s="7" t="inlineStr">
+        <is>
+          <t>pos 16
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J97" s="7" t="inlineStr">
+        <is>
+          <t>pos 17
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K97" s="7" t="inlineStr">
+        <is>
+          <t>pos 18
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>pos 19
+&amp;mo MOUSE_SCROLL</t>
+        </is>
+      </c>
+      <c r="M97" s="7" t="inlineStr">
+        <is>
+          <t>pos 20
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N97" s="7" t="inlineStr">
+        <is>
+          <t>pos 21
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="inlineStr"/>
+      <c r="C98" s="9" t="inlineStr"/>
+      <c r="D98" s="9" t="inlineStr"/>
+      <c r="E98" s="9" t="inlineStr"/>
+      <c r="F98" s="9" t="inlineStr"/>
+      <c r="G98" s="9" t="inlineStr"/>
+      <c r="H98" s="9" t="inlineStr"/>
+      <c r="I98" s="9" t="inlineStr"/>
+      <c r="J98" s="9" t="inlineStr"/>
+      <c r="K98" s="9" t="inlineStr"/>
+      <c r="L98" s="9" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="M98" s="9" t="inlineStr"/>
+      <c r="N98" s="9" t="inlineStr"/>
+    </row>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>Row 3</t>
         </is>
       </c>
-      <c r="B98" s="7" t="inlineStr">
+      <c r="B99" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;kp LEFT_SHIFT</t>
-        </is>
-      </c>
-      <c r="C98" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
         <is>
           <t>pos 23
-&amp;macro_vim_visual_cut</t>
-        </is>
-      </c>
-      <c r="D98" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
         <is>
           <t>pos 24
 &amp;none</t>
         </is>
       </c>
-      <c r="E98" s="7" t="inlineStr">
+      <c r="E99" s="7" t="inlineStr">
         <is>
           <t>pos 25
-&amp;macro_vim_visual_exit</t>
-        </is>
-      </c>
-      <c r="F98" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
         <is>
           <t>pos 26
-&amp;kp LS(LC(LEFT))</t>
-        </is>
-      </c>
-      <c r="G98" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="H98" s="7" t="inlineStr"/>
-      <c r="I98" s="7" t="inlineStr">
+      <c r="H99" s="7" t="inlineStr"/>
+      <c r="I99" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="J98" s="7" t="inlineStr">
+      <c r="J99" s="7" t="inlineStr">
         <is>
           <t>pos 29
-&amp;kp F3</t>
-        </is>
-      </c>
-      <c r="K98" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K99" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;none</t>
         </is>
       </c>
-      <c r="L98" s="7" t="inlineStr">
+      <c r="L99" s="7" t="inlineStr">
         <is>
           <t>pos 31
 &amp;none</t>
         </is>
       </c>
-      <c r="M98" s="7" t="inlineStr">
+      <c r="M99" s="7" t="inlineStr">
         <is>
           <t>pos 32
 &amp;none</t>
         </is>
       </c>
-      <c r="N98" s="7" t="inlineStr">
+      <c r="N99" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;kp RIGHT_SHIFT</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" s="8" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B99" s="9" t="inlineStr">
-        <is>
-          <t>LShift</t>
-        </is>
-      </c>
-      <c r="C99" s="10" t="inlineStr">
-        <is>
-          <t>LShift
-▸ RShift
-▸ ⌃X
-▸ ⇒BASE_QWERTY</t>
-        </is>
-      </c>
-      <c r="D99" s="9" t="inlineStr"/>
-      <c r="E99" s="10" t="inlineStr">
-        <is>
-          <t>LShift
-▸ RShift
-▸ →
-▸ ⇒BASE_QWERTY</t>
-        </is>
-      </c>
-      <c r="F99" s="9" t="inlineStr">
-        <is>
-          <t>⇧⌃←</t>
-        </is>
-      </c>
-      <c r="G99" s="9" t="inlineStr"/>
-      <c r="H99" s="9" t="inlineStr"/>
-      <c r="I99" s="9" t="inlineStr"/>
-      <c r="J99" s="9" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="K99" s="9" t="inlineStr"/>
-      <c r="L99" s="9" t="inlineStr"/>
-      <c r="M99" s="9" t="inlineStr"/>
-      <c r="N99" s="9" t="inlineStr">
-        <is>
-          <t>RShift</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="30" customHeight="1">
-      <c r="A100" s="6" t="inlineStr">
+      <c r="B100" s="9" t="inlineStr"/>
+      <c r="C100" s="9" t="inlineStr"/>
+      <c r="D100" s="9" t="inlineStr"/>
+      <c r="E100" s="9" t="inlineStr"/>
+      <c r="F100" s="9" t="inlineStr"/>
+      <c r="G100" s="9" t="inlineStr"/>
+      <c r="H100" s="9" t="inlineStr"/>
+      <c r="I100" s="9" t="inlineStr"/>
+      <c r="J100" s="9" t="inlineStr"/>
+      <c r="K100" s="9" t="inlineStr"/>
+      <c r="L100" s="9" t="inlineStr"/>
+      <c r="M100" s="9" t="inlineStr"/>
+      <c r="N100" s="9" t="inlineStr"/>
+    </row>
+    <row r="101" ht="30" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>Row 4</t>
         </is>
       </c>
-      <c r="B100" s="7" t="inlineStr">
+      <c r="B101" s="7" t="inlineStr">
         <is>
           <t>pos 34
 &amp;none</t>
         </is>
       </c>
-      <c r="C100" s="7" t="inlineStr">
+      <c r="C101" s="7" t="inlineStr">
         <is>
           <t>pos 35
 &amp;none</t>
         </is>
       </c>
-      <c r="D100" s="7" t="inlineStr">
+      <c r="D101" s="7" t="inlineStr">
         <is>
           <t>pos 36
 &amp;none</t>
         </is>
       </c>
-      <c r="E100" s="7" t="inlineStr">
+      <c r="E101" s="7" t="inlineStr">
         <is>
           <t>pos 37
 &amp;none</t>
         </is>
       </c>
-      <c r="F100" s="7" t="inlineStr">
+      <c r="F101" s="7" t="inlineStr">
         <is>
           <t>pos 38
 &amp;none</t>
         </is>
       </c>
-      <c r="G100" s="7" t="inlineStr">
+      <c r="G101" s="7" t="inlineStr">
         <is>
           <t>pos 39
-&amp;mo VIM_VISUAL_SYM</t>
-        </is>
-      </c>
-      <c r="H100" s="7" t="inlineStr"/>
-      <c r="I100" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="inlineStr"/>
+      <c r="I101" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;none</t>
         </is>
       </c>
-      <c r="J100" s="7" t="inlineStr">
+      <c r="J101" s="7" t="inlineStr">
         <is>
           <t>pos 41
-&amp;mo VIM_VISUAL_SYM</t>
-        </is>
-      </c>
-      <c r="K100" s="7" t="inlineStr"/>
-      <c r="L100" s="7" t="inlineStr"/>
-      <c r="M100" s="7" t="inlineStr"/>
-      <c r="N100" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K101" s="7" t="inlineStr"/>
+      <c r="L101" s="7" t="inlineStr"/>
+      <c r="M101" s="7" t="inlineStr"/>
+      <c r="N101" s="7" t="inlineStr">
         <is>
           <t>pos 42
 &amp;none</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="8" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B101" s="9" t="inlineStr"/>
-      <c r="C101" s="9" t="inlineStr"/>
-      <c r="D101" s="9" t="inlineStr"/>
-      <c r="E101" s="9" t="inlineStr"/>
-      <c r="F101" s="9" t="inlineStr"/>
-      <c r="G101" s="9" t="inlineStr">
-        <is>
-          <t>L9</t>
-        </is>
-      </c>
-      <c r="H101" s="9" t="inlineStr"/>
-      <c r="I101" s="9" t="inlineStr"/>
-      <c r="J101" s="9" t="inlineStr">
-        <is>
-          <t>L9</t>
-        </is>
-      </c>
-      <c r="K101" s="9" t="inlineStr"/>
-      <c r="L101" s="9" t="inlineStr"/>
-      <c r="M101" s="9" t="inlineStr"/>
-      <c r="N101" s="9" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="inlineStr">
-        <is>
-          <t>VIM_VISUAL_SYM レイヤー</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="n"/>
-      <c r="C102" s="4" t="n"/>
-      <c r="D102" s="4" t="n"/>
-      <c r="E102" s="4" t="n"/>
-      <c r="F102" s="4" t="n"/>
-      <c r="G102" s="4" t="n"/>
-      <c r="H102" s="4" t="n"/>
-      <c r="I102" s="4" t="n"/>
-      <c r="J102" s="4" t="n"/>
-      <c r="K102" s="4" t="n"/>
-      <c r="L102" s="4" t="n"/>
-      <c r="M102" s="4" t="n"/>
-      <c r="N102" s="5" t="n"/>
-    </row>
-    <row r="103" ht="30" customHeight="1">
-      <c r="A103" s="6" t="inlineStr">
+      <c r="B102" s="9" t="inlineStr"/>
+      <c r="C102" s="9" t="inlineStr"/>
+      <c r="D102" s="9" t="inlineStr"/>
+      <c r="E102" s="9" t="inlineStr"/>
+      <c r="F102" s="9" t="inlineStr"/>
+      <c r="G102" s="9" t="inlineStr"/>
+      <c r="H102" s="9" t="inlineStr"/>
+      <c r="I102" s="9" t="inlineStr"/>
+      <c r="J102" s="9" t="inlineStr"/>
+      <c r="K102" s="9" t="inlineStr"/>
+      <c r="L102" s="9" t="inlineStr"/>
+      <c r="M102" s="9" t="inlineStr"/>
+      <c r="N102" s="9" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>MOUSE_SCROLL レイヤー</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="n"/>
+      <c r="C103" s="4" t="n"/>
+      <c r="D103" s="4" t="n"/>
+      <c r="E103" s="4" t="n"/>
+      <c r="F103" s="4" t="n"/>
+      <c r="G103" s="4" t="n"/>
+      <c r="H103" s="4" t="n"/>
+      <c r="I103" s="4" t="n"/>
+      <c r="J103" s="4" t="n"/>
+      <c r="K103" s="4" t="n"/>
+      <c r="L103" s="4" t="n"/>
+      <c r="M103" s="4" t="n"/>
+      <c r="N103" s="5" t="n"/>
+    </row>
+    <row r="104" ht="30" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
         <is>
           <t>Row 1</t>
         </is>
       </c>
-      <c r="B103" s="7" t="inlineStr">
+      <c r="B104" s="7" t="inlineStr">
         <is>
           <t>pos 0
 &amp;none</t>
         </is>
       </c>
-      <c r="C103" s="7" t="inlineStr">
+      <c r="C104" s="7" t="inlineStr">
         <is>
           <t>pos 1
 &amp;none</t>
         </is>
       </c>
-      <c r="D103" s="7" t="inlineStr">
+      <c r="D104" s="7" t="inlineStr">
         <is>
           <t>pos 2
 &amp;none</t>
         </is>
       </c>
-      <c r="E103" s="7" t="inlineStr">
+      <c r="E104" s="7" t="inlineStr">
         <is>
           <t>pos 3
-&amp;mm_vim_visual_shift_4</t>
-        </is>
-      </c>
-      <c r="F103" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr">
         <is>
           <t>pos 4
 &amp;none</t>
         </is>
       </c>
-      <c r="G103" s="7" t="inlineStr"/>
-      <c r="H103" s="7" t="inlineStr"/>
-      <c r="I103" s="7" t="inlineStr"/>
-      <c r="J103" s="7" t="inlineStr">
+      <c r="G104" s="7" t="inlineStr"/>
+      <c r="H104" s="7" t="inlineStr"/>
+      <c r="I104" s="7" t="inlineStr"/>
+      <c r="J104" s="7" t="inlineStr">
         <is>
           <t>pos 5
-&amp;mm_vim_visual_shift_6</t>
-        </is>
-      </c>
-      <c r="K103" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K104" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;none</t>
         </is>
       </c>
-      <c r="L103" s="7" t="inlineStr">
+      <c r="L104" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="M103" s="7" t="inlineStr">
+      <c r="M104" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;none</t>
         </is>
       </c>
-      <c r="N103" s="7" t="inlineStr">
+      <c r="N104" s="7" t="inlineStr">
         <is>
           <t>pos 9
-&amp;kp LS(HOME)</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B104" s="9" t="inlineStr"/>
-      <c r="C104" s="9" t="inlineStr"/>
-      <c r="D104" s="9" t="inlineStr"/>
-      <c r="E104" s="9" t="inlineStr"/>
-      <c r="F104" s="9" t="inlineStr"/>
-      <c r="G104" s="9" t="inlineStr"/>
-      <c r="H104" s="9" t="inlineStr"/>
-      <c r="I104" s="9" t="inlineStr"/>
-      <c r="J104" s="9" t="inlineStr"/>
-      <c r="K104" s="9" t="inlineStr"/>
-      <c r="L104" s="9" t="inlineStr"/>
-      <c r="M104" s="9" t="inlineStr"/>
-      <c r="N104" s="9" t="inlineStr">
-        <is>
-          <t>⇧HOME</t>
+&amp;none</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>Shift+</t>
+          <t>タップ</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr"/>
       <c r="C105" s="9" t="inlineStr"/>
       <c r="D105" s="9" t="inlineStr"/>
-      <c r="E105" s="9" t="inlineStr">
-        <is>
-          <t>⇧END</t>
-        </is>
-      </c>
+      <c r="E105" s="9" t="inlineStr"/>
       <c r="F105" s="9" t="inlineStr"/>
       <c r="G105" s="9" t="inlineStr"/>
       <c r="H105" s="9" t="inlineStr"/>
       <c r="I105" s="9" t="inlineStr"/>
-      <c r="J105" s="9" t="inlineStr">
-        <is>
-          <t>⇧HOME</t>
-        </is>
-      </c>
+      <c r="J105" s="9" t="inlineStr"/>
       <c r="K105" s="9" t="inlineStr"/>
       <c r="L105" s="9" t="inlineStr"/>
       <c r="M105" s="9" t="inlineStr"/>
-      <c r="N105" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="N105" s="9" t="inlineStr"/>
     </row>
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="6" t="inlineStr">
@@ -5783,7 +5787,7 @@
       <c r="B106" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;kp LCTRL</t>
+&amp;none</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
@@ -5826,13 +5830,13 @@
       <c r="J106" s="7" t="inlineStr">
         <is>
           <t>pos 17
-&amp;kp LS(LEFT)</t>
+&amp;none</t>
         </is>
       </c>
       <c r="K106" s="7" t="inlineStr">
         <is>
           <t>pos 18
-&amp;none</t>
+&amp;mkp MB1</t>
         </is>
       </c>
       <c r="L106" s="7" t="inlineStr">
@@ -5844,13 +5848,13 @@
       <c r="M106" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
+&amp;mkp MB2</t>
         </is>
       </c>
       <c r="N106" s="7" t="inlineStr">
         <is>
           <t>pos 21
-&amp;kp RCTRL</t>
+&amp;none</t>
         </is>
       </c>
     </row>
@@ -5860,11 +5864,7 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B107" s="9" t="inlineStr">
-        <is>
-          <t>LCtrl</t>
-        </is>
-      </c>
+      <c r="B107" s="9" t="inlineStr"/>
       <c r="C107" s="9" t="inlineStr"/>
       <c r="D107" s="9" t="inlineStr"/>
       <c r="E107" s="9" t="inlineStr"/>
@@ -5872,19 +5872,19 @@
       <c r="G107" s="9" t="inlineStr"/>
       <c r="H107" s="9" t="inlineStr"/>
       <c r="I107" s="9" t="inlineStr"/>
-      <c r="J107" s="9" t="inlineStr">
-        <is>
-          <t>⇧←</t>
-        </is>
-      </c>
-      <c r="K107" s="9" t="inlineStr"/>
+      <c r="J107" s="9" t="inlineStr"/>
+      <c r="K107" s="9" t="inlineStr">
+        <is>
+          <t>🖱左</t>
+        </is>
+      </c>
       <c r="L107" s="9" t="inlineStr"/>
-      <c r="M107" s="9" t="inlineStr"/>
-      <c r="N107" s="9" t="inlineStr">
-        <is>
-          <t>RCtrl</t>
-        </is>
-      </c>
+      <c r="M107" s="9" t="inlineStr">
+        <is>
+          <t>🖱右</t>
+        </is>
+      </c>
+      <c r="N107" s="9" t="inlineStr"/>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
@@ -5895,7 +5895,7 @@
       <c r="B108" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;kp LEFT_SHIFT</t>
+&amp;none</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
@@ -5944,7 +5944,7 @@
       <c r="K108" s="7" t="inlineStr">
         <is>
           <t>pos 30
-&amp;none</t>
+&amp;mkp MB4</t>
         </is>
       </c>
       <c r="L108" s="7" t="inlineStr">
@@ -5956,13 +5956,13 @@
       <c r="M108" s="7" t="inlineStr">
         <is>
           <t>pos 32
-&amp;none</t>
+&amp;mkp MB5</t>
         </is>
       </c>
       <c r="N108" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;kp RIGHT_SHIFT</t>
+&amp;none</t>
         </is>
       </c>
     </row>
@@ -5972,11 +5972,7 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B109" s="9" t="inlineStr">
-        <is>
-          <t>LShift</t>
-        </is>
-      </c>
+      <c r="B109" s="9" t="inlineStr"/>
       <c r="C109" s="9" t="inlineStr"/>
       <c r="D109" s="9" t="inlineStr"/>
       <c r="E109" s="9" t="inlineStr"/>
@@ -5985,14 +5981,18 @@
       <c r="H109" s="9" t="inlineStr"/>
       <c r="I109" s="9" t="inlineStr"/>
       <c r="J109" s="9" t="inlineStr"/>
-      <c r="K109" s="9" t="inlineStr"/>
+      <c r="K109" s="9" t="inlineStr">
+        <is>
+          <t>🖱戻</t>
+        </is>
+      </c>
       <c r="L109" s="9" t="inlineStr"/>
-      <c r="M109" s="9" t="inlineStr"/>
-      <c r="N109" s="9" t="inlineStr">
-        <is>
-          <t>RShift</t>
-        </is>
-      </c>
+      <c r="M109" s="9" t="inlineStr">
+        <is>
+          <t>🖱進</t>
+        </is>
+      </c>
+      <c r="N109" s="9" t="inlineStr"/>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
@@ -6081,16 +6081,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A91:N91"/>
     <mergeCell ref="A55:N55"/>
     <mergeCell ref="A4:N4"/>
     <mergeCell ref="A45:N45"/>
     <mergeCell ref="A16:N16"/>
-    <mergeCell ref="A64:N64"/>
-    <mergeCell ref="A82:N82"/>
-    <mergeCell ref="A73:N73"/>
+    <mergeCell ref="A76:N76"/>
+    <mergeCell ref="A85:N85"/>
     <mergeCell ref="A28:N28"/>
-    <mergeCell ref="A102:N102"/>
+    <mergeCell ref="A103:N103"/>
+    <mergeCell ref="A66:N66"/>
+    <mergeCell ref="A94:N94"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8959,7 +8959,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>MOUSE_MOVE レイヤー</t>
+          <t>VIM_VISUAL_BASE レイヤー</t>
         </is>
       </c>
       <c r="B55" s="4" t="n"/>
@@ -8991,13 +8991,13 @@
       <c r="C56" s="7" t="inlineStr">
         <is>
           <t>pos 1
-&amp;none</t>
+&amp;kp LS(LC(RIGHT))</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
           <t>pos 2
-&amp;none</t>
+&amp;kp LS(LC(RIGHT))</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
@@ -9018,7 +9018,7 @@
       <c r="J56" s="7" t="inlineStr">
         <is>
           <t>pos 5
-&amp;none</t>
+&amp;macro_vim_visual_y</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
@@ -9042,7 +9042,7 @@
       <c r="N56" s="7" t="inlineStr">
         <is>
           <t>pos 9
-&amp;none</t>
+&amp;macro_vim_visual_p</t>
         </is>
       </c>
     </row>
@@ -9053,18 +9053,34 @@
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr"/>
-      <c r="C57" s="9" t="inlineStr"/>
-      <c r="D57" s="9" t="inlineStr"/>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LS(LC(RIGHT))</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LS(LC(RIGHT))</t>
+        </is>
+      </c>
       <c r="E57" s="9" t="inlineStr"/>
       <c r="F57" s="9" t="inlineStr"/>
       <c r="G57" s="9" t="inlineStr"/>
       <c r="H57" s="9" t="inlineStr"/>
       <c r="I57" s="9" t="inlineStr"/>
-      <c r="J57" s="9" t="inlineStr"/>
+      <c r="J57" s="9" t="inlineStr">
+        <is>
+          <t>macro_vim_visual_y</t>
+        </is>
+      </c>
       <c r="K57" s="9" t="inlineStr"/>
       <c r="L57" s="9" t="inlineStr"/>
       <c r="M57" s="9" t="inlineStr"/>
-      <c r="N57" s="9" t="inlineStr"/>
+      <c r="N57" s="9" t="inlineStr">
+        <is>
+          <t>macro_vim_visual_p</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
@@ -9075,7 +9091,7 @@
       <c r="B58" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
@@ -9087,7 +9103,7 @@
       <c r="D58" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;macro_vim_visual_cut</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
@@ -9099,7 +9115,7 @@
       <c r="F58" s="7" t="inlineStr">
         <is>
           <t>pos 14
-&amp;none</t>
+&amp;mm_vim_visual_g</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
@@ -9118,220 +9134,272 @@
       <c r="J58" s="7" t="inlineStr">
         <is>
           <t>pos 17
-&amp;none</t>
+&amp;kp LS(LEFT)</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
           <t>pos 18
-&amp;none</t>
+&amp;kp LS(DOWN)</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;mo MOUSE_SCROLL</t>
+&amp;kp LS(UP)</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
+&amp;kp LS(RIGHT)</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
           <t>pos 21
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
+&amp;kp RCTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="45" customHeight="1">
       <c r="A59" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B59" s="9" t="inlineStr"/>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LCTRL</t>
+        </is>
+      </c>
       <c r="C59" s="9" t="inlineStr"/>
-      <c r="D59" s="9" t="inlineStr"/>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>macro_vim_visual_cut</t>
+        </is>
+      </c>
       <c r="E59" s="9" t="inlineStr"/>
-      <c r="F59" s="9" t="inlineStr"/>
+      <c r="F59" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_g[0]
+▸ td_vim_visual_g[0]
+▸ &amp;none</t>
+        </is>
+      </c>
       <c r="G59" s="9" t="inlineStr"/>
       <c r="H59" s="9" t="inlineStr"/>
       <c r="I59" s="9" t="inlineStr"/>
-      <c r="J59" s="9" t="inlineStr"/>
-      <c r="K59" s="9" t="inlineStr"/>
+      <c r="J59" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LS(LEFT)</t>
+        </is>
+      </c>
+      <c r="K59" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LS(DOWN)</t>
+        </is>
+      </c>
       <c r="L59" s="9" t="inlineStr">
         <is>
-          <t>&amp;mo MOUSE_SCROLL</t>
-        </is>
-      </c>
-      <c r="M59" s="9" t="inlineStr"/>
-      <c r="N59" s="9" t="inlineStr"/>
-    </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>Row 3</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>pos 22
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>pos 23
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>pos 24
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>pos 25
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>pos 26
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G60" s="7" t="inlineStr">
-        <is>
-          <t>pos 27
-&amp;none</t>
-        </is>
-      </c>
-      <c r="H60" s="7" t="inlineStr"/>
-      <c r="I60" s="7" t="inlineStr">
-        <is>
-          <t>pos 28
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J60" s="7" t="inlineStr">
-        <is>
-          <t>pos 29
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K60" s="7" t="inlineStr">
-        <is>
-          <t>pos 30
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L60" s="7" t="inlineStr">
-        <is>
-          <t>pos 31
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M60" s="7" t="inlineStr">
-        <is>
-          <t>pos 32
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N60" s="7" t="inlineStr">
-        <is>
-          <t>pos 33
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
+          <t>&amp;kp LS(UP)</t>
+        </is>
+      </c>
+      <c r="M59" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LS(RIGHT)</t>
+        </is>
+      </c>
+      <c r="N59" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RCTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="45" customHeight="1">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>ダブルタップ</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr"/>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr"/>
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_g[0]
+▸ td_vim_visual_g[1]
+▸ &amp;kp LS(LC(HOME))</t>
+        </is>
+      </c>
+      <c r="G60" s="9" t="inlineStr"/>
+      <c r="H60" s="9" t="inlineStr"/>
+      <c r="I60" s="9" t="inlineStr"/>
+      <c r="J60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="K60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="L60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="30" customHeight="1">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B61" s="9" t="inlineStr"/>
+          <t>Shift+</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="C61" s="9" t="inlineStr"/>
-      <c r="D61" s="9" t="inlineStr"/>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="E61" s="9" t="inlineStr"/>
-      <c r="F61" s="9" t="inlineStr"/>
+      <c r="F61" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_g[1]
+▸ &amp;kp LS(LC(END))</t>
+        </is>
+      </c>
       <c r="G61" s="9" t="inlineStr"/>
       <c r="H61" s="9" t="inlineStr"/>
       <c r="I61" s="9" t="inlineStr"/>
-      <c r="J61" s="9" t="inlineStr"/>
-      <c r="K61" s="9" t="inlineStr"/>
-      <c r="L61" s="9" t="inlineStr"/>
-      <c r="M61" s="9" t="inlineStr"/>
-      <c r="N61" s="9" t="inlineStr"/>
+      <c r="J61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="K61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="L61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>Row 4</t>
+          <t>Row 3</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>pos 34
-&amp;none</t>
+          <t>pos 22
+&amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>pos 35
-&amp;none</t>
+          <t>pos 23
+&amp;macro_vim_visual_cut</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>pos 36
+          <t>pos 24
 &amp;none</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>pos 37
-&amp;none</t>
+          <t>pos 25
+&amp;macro_vim_visual_exit</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>pos 38
-&amp;none</t>
+          <t>pos 26
+&amp;kp LS(LC(LEFT))</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>pos 39
+          <t>pos 27
 &amp;none</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr"/>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>pos 40
+          <t>pos 28
 &amp;none</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>pos 41
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K62" s="7" t="inlineStr"/>
-      <c r="L62" s="7" t="inlineStr"/>
-      <c r="M62" s="7" t="inlineStr"/>
+          <t>pos 29
+&amp;kp F3</t>
+        </is>
+      </c>
+      <c r="K62" s="7" t="inlineStr">
+        <is>
+          <t>pos 30
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M62" s="7" t="inlineStr">
+        <is>
+          <t>pos 32
+&amp;none</t>
+        </is>
+      </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>pos 42
-&amp;none</t>
+          <t>pos 33
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
     </row>
@@ -9341,211 +9409,228 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B63" s="9" t="inlineStr"/>
-      <c r="C63" s="9" t="inlineStr"/>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_SHIFT</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>macro_vim_visual_cut</t>
+        </is>
+      </c>
       <c r="D63" s="9" t="inlineStr"/>
-      <c r="E63" s="9" t="inlineStr"/>
-      <c r="F63" s="9" t="inlineStr"/>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>macro_vim_visual_exit</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LS(LC(LEFT))</t>
+        </is>
+      </c>
       <c r="G63" s="9" t="inlineStr"/>
       <c r="H63" s="9" t="inlineStr"/>
       <c r="I63" s="9" t="inlineStr"/>
-      <c r="J63" s="9" t="inlineStr"/>
+      <c r="J63" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F3</t>
+        </is>
+      </c>
       <c r="K63" s="9" t="inlineStr"/>
       <c r="L63" s="9" t="inlineStr"/>
       <c r="M63" s="9" t="inlineStr"/>
-      <c r="N63" s="9" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>MOUSE_SCROLL レイヤー</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="n"/>
-      <c r="C64" s="4" t="n"/>
-      <c r="D64" s="4" t="n"/>
-      <c r="E64" s="4" t="n"/>
-      <c r="F64" s="4" t="n"/>
-      <c r="G64" s="4" t="n"/>
-      <c r="H64" s="4" t="n"/>
-      <c r="I64" s="4" t="n"/>
-      <c r="J64" s="4" t="n"/>
-      <c r="K64" s="4" t="n"/>
-      <c r="L64" s="4" t="n"/>
-      <c r="M64" s="4" t="n"/>
-      <c r="N64" s="5" t="n"/>
-    </row>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>Row 1</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>pos 0
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>pos 1
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>pos 2
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t>pos 3
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F65" s="7" t="inlineStr">
-        <is>
-          <t>pos 4
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G65" s="7" t="inlineStr"/>
-      <c r="H65" s="7" t="inlineStr"/>
-      <c r="I65" s="7" t="inlineStr"/>
-      <c r="J65" s="7" t="inlineStr">
-        <is>
-          <t>pos 5
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K65" s="7" t="inlineStr">
-        <is>
-          <t>pos 6
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L65" s="7" t="inlineStr">
-        <is>
-          <t>pos 7
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M65" s="7" t="inlineStr">
-        <is>
-          <t>pos 8
-&amp;none</t>
-        </is>
-      </c>
-      <c r="N65" s="7" t="inlineStr">
-        <is>
-          <t>pos 9
-&amp;none</t>
-        </is>
-      </c>
+      <c r="N63" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Row 4</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>pos 34
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>pos 35
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>pos 36
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>pos 37
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;mo VIM_VISUAL_SYM</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="inlineStr"/>
+      <c r="I64" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J64" s="7" t="inlineStr">
+        <is>
+          <t>pos 41
+&amp;mo VIM_VISUAL_SYM</t>
+        </is>
+      </c>
+      <c r="K64" s="7" t="inlineStr"/>
+      <c r="L64" s="7" t="inlineStr"/>
+      <c r="M64" s="7" t="inlineStr"/>
+      <c r="N64" s="7" t="inlineStr">
+        <is>
+          <t>pos 42
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr"/>
+      <c r="C65" s="9" t="inlineStr"/>
+      <c r="D65" s="9" t="inlineStr"/>
+      <c r="E65" s="9" t="inlineStr"/>
+      <c r="F65" s="9" t="inlineStr"/>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mo VIM_VISUAL_SYM</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="inlineStr"/>
+      <c r="I65" s="9" t="inlineStr"/>
+      <c r="J65" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mo VIM_VISUAL_SYM</t>
+        </is>
+      </c>
+      <c r="K65" s="9" t="inlineStr"/>
+      <c r="L65" s="9" t="inlineStr"/>
+      <c r="M65" s="9" t="inlineStr"/>
+      <c r="N65" s="9" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B66" s="9" t="inlineStr"/>
-      <c r="C66" s="9" t="inlineStr"/>
-      <c r="D66" s="9" t="inlineStr"/>
-      <c r="E66" s="9" t="inlineStr"/>
-      <c r="F66" s="9" t="inlineStr"/>
-      <c r="G66" s="9" t="inlineStr"/>
-      <c r="H66" s="9" t="inlineStr"/>
-      <c r="I66" s="9" t="inlineStr"/>
-      <c r="J66" s="9" t="inlineStr"/>
-      <c r="K66" s="9" t="inlineStr"/>
-      <c r="L66" s="9" t="inlineStr"/>
-      <c r="M66" s="9" t="inlineStr"/>
-      <c r="N66" s="9" t="inlineStr"/>
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>VIM_VISUAL_SYM レイヤー</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="n"/>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n"/>
+      <c r="F66" s="4" t="n"/>
+      <c r="G66" s="4" t="n"/>
+      <c r="H66" s="4" t="n"/>
+      <c r="I66" s="4" t="n"/>
+      <c r="J66" s="4" t="n"/>
+      <c r="K66" s="4" t="n"/>
+      <c r="L66" s="4" t="n"/>
+      <c r="M66" s="4" t="n"/>
+      <c r="N66" s="5" t="n"/>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>Row 2</t>
+          <t>Row 1</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>pos 10
+          <t>pos 0
 &amp;none</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>pos 11
+          <t>pos 1
 &amp;none</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>pos 12
+          <t>pos 2
 &amp;none</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>pos 13
-&amp;none</t>
+          <t>pos 3
+&amp;mm_vim_visual_shift_4</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>pos 14
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G67" s="7" t="inlineStr">
-        <is>
-          <t>pos 15
-&amp;none</t>
-        </is>
-      </c>
+          <t>pos 4
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr"/>
       <c r="H67" s="7" t="inlineStr"/>
-      <c r="I67" s="7" t="inlineStr">
-        <is>
-          <t>pos 16
-&amp;none</t>
-        </is>
-      </c>
+      <c r="I67" s="7" t="inlineStr"/>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>pos 17
-&amp;none</t>
+          <t>pos 5
+&amp;mm_vim_visual_shift_6</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>pos 18
-&amp;mkp MB1</t>
+          <t>pos 6
+&amp;none</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>pos 19
+          <t>pos 7
 &amp;none</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>pos 20
-&amp;mkp MB2</t>
+          <t>pos 8
+&amp;none</t>
         </is>
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>pos 21
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
+          <t>pos 9
+&amp;kp LS(HOME)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="30" customHeight="1">
       <c r="A68" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
@@ -9554,305 +9639,347 @@
       <c r="B68" s="9" t="inlineStr"/>
       <c r="C68" s="9" t="inlineStr"/>
       <c r="D68" s="9" t="inlineStr"/>
-      <c r="E68" s="9" t="inlineStr"/>
+      <c r="E68" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_shift_4[0]
+▸ &amp;none</t>
+        </is>
+      </c>
       <c r="F68" s="9" t="inlineStr"/>
       <c r="G68" s="9" t="inlineStr"/>
       <c r="H68" s="9" t="inlineStr"/>
       <c r="I68" s="9" t="inlineStr"/>
-      <c r="J68" s="9" t="inlineStr"/>
-      <c r="K68" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mkp MB1</t>
-        </is>
-      </c>
+      <c r="J68" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_shift_6[0]
+▸ &amp;none</t>
+        </is>
+      </c>
+      <c r="K68" s="9" t="inlineStr"/>
       <c r="L68" s="9" t="inlineStr"/>
-      <c r="M68" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mkp MB2</t>
-        </is>
-      </c>
-      <c r="N68" s="9" t="inlineStr"/>
+      <c r="M68" s="9" t="inlineStr"/>
+      <c r="N68" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LS(HOME)</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>Shift+</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr"/>
+      <c r="C69" s="9" t="inlineStr"/>
+      <c r="D69" s="9" t="inlineStr"/>
+      <c r="E69" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_shift_4[1]
+▸ &amp;kp LS(END)</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr"/>
+      <c r="G69" s="9" t="inlineStr"/>
+      <c r="H69" s="9" t="inlineStr"/>
+      <c r="I69" s="9" t="inlineStr"/>
+      <c r="J69" s="10" t="inlineStr">
+        <is>
+          <t>mm_vim_visual_shift_6[1]
+▸ &amp;kp LS(HOME)</t>
+        </is>
+      </c>
+      <c r="K69" s="9" t="inlineStr"/>
+      <c r="L69" s="9" t="inlineStr"/>
+      <c r="M69" s="9" t="inlineStr"/>
+      <c r="N69" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Row 2</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>pos 10
+&amp;kp LCTRL</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>pos 11
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>pos 12
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>pos 13
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>pos 14
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;none</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr"/>
+      <c r="I70" s="7" t="inlineStr">
+        <is>
+          <t>pos 16
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J70" s="7" t="inlineStr">
+        <is>
+          <t>pos 17
+&amp;kp LS(LEFT)</t>
+        </is>
+      </c>
+      <c r="K70" s="7" t="inlineStr">
+        <is>
+          <t>pos 18
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L70" s="7" t="inlineStr">
+        <is>
+          <t>pos 19
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M70" s="7" t="inlineStr">
+        <is>
+          <t>pos 20
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N70" s="7" t="inlineStr">
+        <is>
+          <t>pos 21
+&amp;kp RCTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LCTRL</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr"/>
+      <c r="D71" s="9" t="inlineStr"/>
+      <c r="E71" s="9" t="inlineStr"/>
+      <c r="F71" s="9" t="inlineStr"/>
+      <c r="G71" s="9" t="inlineStr"/>
+      <c r="H71" s="9" t="inlineStr"/>
+      <c r="I71" s="9" t="inlineStr"/>
+      <c r="J71" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LS(LEFT)</t>
+        </is>
+      </c>
+      <c r="K71" s="9" t="inlineStr"/>
+      <c r="L71" s="9" t="inlineStr"/>
+      <c r="M71" s="9" t="inlineStr"/>
+      <c r="N71" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RCTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>Row 3</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
+      <c r="B72" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C69" s="7" t="inlineStr">
+&amp;kp LEFT_SHIFT</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
         <is>
           <t>pos 23
 &amp;none</t>
         </is>
       </c>
-      <c r="D69" s="7" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>pos 24
 &amp;none</t>
         </is>
       </c>
-      <c r="E69" s="7" t="inlineStr">
+      <c r="E72" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
-      <c r="F69" s="7" t="inlineStr">
+      <c r="F72" s="7" t="inlineStr">
         <is>
           <t>pos 26
 &amp;none</t>
         </is>
       </c>
-      <c r="G69" s="7" t="inlineStr">
+      <c r="G72" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="H69" s="7" t="inlineStr"/>
-      <c r="I69" s="7" t="inlineStr">
+      <c r="H72" s="7" t="inlineStr"/>
+      <c r="I72" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="J69" s="7" t="inlineStr">
+      <c r="J72" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;none</t>
         </is>
       </c>
-      <c r="K69" s="7" t="inlineStr">
+      <c r="K72" s="7" t="inlineStr">
         <is>
           <t>pos 30
-&amp;mkp MB4</t>
-        </is>
-      </c>
-      <c r="L69" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L72" s="7" t="inlineStr">
         <is>
           <t>pos 31
 &amp;none</t>
         </is>
       </c>
-      <c r="M69" s="7" t="inlineStr">
+      <c r="M72" s="7" t="inlineStr">
         <is>
           <t>pos 32
-&amp;mkp MB5</t>
-        </is>
-      </c>
-      <c r="N69" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N72" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="8" t="inlineStr">
+&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B70" s="9" t="inlineStr"/>
-      <c r="C70" s="9" t="inlineStr"/>
-      <c r="D70" s="9" t="inlineStr"/>
-      <c r="E70" s="9" t="inlineStr"/>
-      <c r="F70" s="9" t="inlineStr"/>
-      <c r="G70" s="9" t="inlineStr"/>
-      <c r="H70" s="9" t="inlineStr"/>
-      <c r="I70" s="9" t="inlineStr"/>
-      <c r="J70" s="9" t="inlineStr"/>
-      <c r="K70" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mkp MB4</t>
-        </is>
-      </c>
-      <c r="L70" s="9" t="inlineStr"/>
-      <c r="M70" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mkp MB5</t>
-        </is>
-      </c>
-      <c r="N70" s="9" t="inlineStr"/>
-    </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>Row 4</t>
-        </is>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>pos 34
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>pos 35
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>pos 36
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G71" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="H71" s="7" t="inlineStr"/>
-      <c r="I71" s="7" t="inlineStr">
-        <is>
-          <t>pos 40
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J71" s="7" t="inlineStr">
-        <is>
-          <t>pos 41
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K71" s="7" t="inlineStr"/>
-      <c r="L71" s="7" t="inlineStr"/>
-      <c r="M71" s="7" t="inlineStr"/>
-      <c r="N71" s="7" t="inlineStr">
-        <is>
-          <t>pos 42
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B72" s="9" t="inlineStr"/>
-      <c r="C72" s="9" t="inlineStr"/>
-      <c r="D72" s="9" t="inlineStr"/>
-      <c r="E72" s="9" t="inlineStr"/>
-      <c r="F72" s="9" t="inlineStr"/>
-      <c r="G72" s="9" t="inlineStr"/>
-      <c r="H72" s="9" t="inlineStr"/>
-      <c r="I72" s="9" t="inlineStr"/>
-      <c r="J72" s="9" t="inlineStr"/>
-      <c r="K72" s="9" t="inlineStr"/>
-      <c r="L72" s="9" t="inlineStr"/>
-      <c r="M72" s="9" t="inlineStr"/>
-      <c r="N72" s="9" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>FUNCTION レイヤー</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="n"/>
-      <c r="C73" s="4" t="n"/>
-      <c r="D73" s="4" t="n"/>
-      <c r="E73" s="4" t="n"/>
-      <c r="F73" s="4" t="n"/>
-      <c r="G73" s="4" t="n"/>
-      <c r="H73" s="4" t="n"/>
-      <c r="I73" s="4" t="n"/>
-      <c r="J73" s="4" t="n"/>
-      <c r="K73" s="4" t="n"/>
-      <c r="L73" s="4" t="n"/>
-      <c r="M73" s="4" t="n"/>
-      <c r="N73" s="5" t="n"/>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_SHIFT</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr"/>
+      <c r="D73" s="9" t="inlineStr"/>
+      <c r="E73" s="9" t="inlineStr"/>
+      <c r="F73" s="9" t="inlineStr"/>
+      <c r="G73" s="9" t="inlineStr"/>
+      <c r="H73" s="9" t="inlineStr"/>
+      <c r="I73" s="9" t="inlineStr"/>
+      <c r="J73" s="9" t="inlineStr"/>
+      <c r="K73" s="9" t="inlineStr"/>
+      <c r="L73" s="9" t="inlineStr"/>
+      <c r="M73" s="9" t="inlineStr"/>
+      <c r="N73" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>Row 1</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>pos 0
-&amp;kp F1</t>
+          <t>pos 34
+&amp;none</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>pos 1
-&amp;kp F2</t>
+          <t>pos 35
+&amp;none</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>pos 2
-&amp;kp F3</t>
+          <t>pos 36
+&amp;none</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>pos 3
-&amp;kp F4</t>
+          <t>pos 37
+&amp;none</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>pos 4
-&amp;kp F5</t>
-        </is>
-      </c>
-      <c r="G74" s="7" t="inlineStr"/>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
       <c r="H74" s="7" t="inlineStr"/>
-      <c r="I74" s="7" t="inlineStr"/>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>pos 5
-&amp;kp F6</t>
-        </is>
-      </c>
-      <c r="K74" s="7" t="inlineStr">
-        <is>
-          <t>pos 6
-&amp;kp F7</t>
-        </is>
-      </c>
-      <c r="L74" s="7" t="inlineStr">
-        <is>
-          <t>pos 7
-&amp;kp F8</t>
-        </is>
-      </c>
-      <c r="M74" s="7" t="inlineStr">
-        <is>
-          <t>pos 8
-&amp;kp F9</t>
-        </is>
-      </c>
+          <t>pos 41
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K74" s="7" t="inlineStr"/>
+      <c r="L74" s="7" t="inlineStr"/>
+      <c r="M74" s="7" t="inlineStr"/>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>pos 9
-&amp;kp F10</t>
+          <t>pos 42
+&amp;none</t>
         </is>
       </c>
     </row>
@@ -9862,447 +9989,447 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B75" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp F1</t>
-        </is>
-      </c>
-      <c r="C75" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp F2</t>
-        </is>
-      </c>
-      <c r="D75" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp F3</t>
-        </is>
-      </c>
-      <c r="E75" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp F4</t>
-        </is>
-      </c>
-      <c r="F75" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp F5</t>
-        </is>
-      </c>
+      <c r="B75" s="9" t="inlineStr"/>
+      <c r="C75" s="9" t="inlineStr"/>
+      <c r="D75" s="9" t="inlineStr"/>
+      <c r="E75" s="9" t="inlineStr"/>
+      <c r="F75" s="9" t="inlineStr"/>
       <c r="G75" s="9" t="inlineStr"/>
       <c r="H75" s="9" t="inlineStr"/>
       <c r="I75" s="9" t="inlineStr"/>
-      <c r="J75" s="9" t="inlineStr">
+      <c r="J75" s="9" t="inlineStr"/>
+      <c r="K75" s="9" t="inlineStr"/>
+      <c r="L75" s="9" t="inlineStr"/>
+      <c r="M75" s="9" t="inlineStr"/>
+      <c r="N75" s="9" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>FUNCTION レイヤー</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="n"/>
+      <c r="C76" s="4" t="n"/>
+      <c r="D76" s="4" t="n"/>
+      <c r="E76" s="4" t="n"/>
+      <c r="F76" s="4" t="n"/>
+      <c r="G76" s="4" t="n"/>
+      <c r="H76" s="4" t="n"/>
+      <c r="I76" s="4" t="n"/>
+      <c r="J76" s="4" t="n"/>
+      <c r="K76" s="4" t="n"/>
+      <c r="L76" s="4" t="n"/>
+      <c r="M76" s="4" t="n"/>
+      <c r="N76" s="5" t="n"/>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Row 1</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>pos 0
+&amp;kp F1</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>pos 1
+&amp;kp F2</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>pos 2
+&amp;kp F3</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>pos 3
+&amp;kp F4</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>pos 4
+&amp;kp F5</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr"/>
+      <c r="H77" s="7" t="inlineStr"/>
+      <c r="I77" s="7" t="inlineStr"/>
+      <c r="J77" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;kp F6</t>
+        </is>
+      </c>
+      <c r="K77" s="7" t="inlineStr">
+        <is>
+          <t>pos 6
+&amp;kp F7</t>
+        </is>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>pos 7
+&amp;kp F8</t>
+        </is>
+      </c>
+      <c r="M77" s="7" t="inlineStr">
+        <is>
+          <t>pos 8
+&amp;kp F9</t>
+        </is>
+      </c>
+      <c r="N77" s="7" t="inlineStr">
+        <is>
+          <t>pos 9
+&amp;kp F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F1</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F2</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F3</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F4</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F5</t>
+        </is>
+      </c>
+      <c r="G78" s="9" t="inlineStr"/>
+      <c r="H78" s="9" t="inlineStr"/>
+      <c r="I78" s="9" t="inlineStr"/>
+      <c r="J78" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F6</t>
         </is>
       </c>
-      <c r="K75" s="9" t="inlineStr">
+      <c r="K78" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F7</t>
         </is>
       </c>
-      <c r="L75" s="9" t="inlineStr">
+      <c r="L78" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F8</t>
         </is>
       </c>
-      <c r="M75" s="9" t="inlineStr">
+      <c r="M78" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F9</t>
         </is>
       </c>
-      <c r="N75" s="9" t="inlineStr">
+      <c r="N78" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F10</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="6" t="inlineStr">
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>Row 2</t>
         </is>
       </c>
-      <c r="B76" s="7" t="inlineStr">
+      <c r="B79" s="7" t="inlineStr">
         <is>
           <t>pos 10
 &amp;none</t>
         </is>
       </c>
-      <c r="C76" s="7" t="inlineStr">
+      <c r="C79" s="7" t="inlineStr">
         <is>
           <t>pos 11
 &amp;sys_reset</t>
         </is>
       </c>
-      <c r="D76" s="7" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>pos 12
 &amp;none</t>
         </is>
       </c>
-      <c r="E76" s="7" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t>pos 13
 &amp;none</t>
         </is>
       </c>
-      <c r="F76" s="7" t="inlineStr">
+      <c r="F79" s="7" t="inlineStr">
         <is>
           <t>pos 14
 &amp;none</t>
         </is>
       </c>
-      <c r="G76" s="7" t="inlineStr">
+      <c r="G79" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;none</t>
         </is>
       </c>
-      <c r="H76" s="7" t="inlineStr"/>
-      <c r="I76" s="7" t="inlineStr">
+      <c r="H79" s="7" t="inlineStr"/>
+      <c r="I79" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="J76" s="7" t="inlineStr">
+      <c r="J79" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="K76" s="7" t="inlineStr">
+      <c r="K79" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;none</t>
         </is>
       </c>
-      <c r="L76" s="7" t="inlineStr">
+      <c r="L79" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;none</t>
         </is>
       </c>
-      <c r="M76" s="7" t="inlineStr">
+      <c r="M79" s="7" t="inlineStr">
         <is>
           <t>pos 20
 &amp;sys_reset</t>
         </is>
       </c>
-      <c r="N76" s="7" t="inlineStr">
+      <c r="N79" s="7" t="inlineStr">
         <is>
           <t>pos 21
 &amp;none</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="8" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B77" s="9" t="inlineStr"/>
-      <c r="C77" s="9" t="inlineStr">
+      <c r="B80" s="9" t="inlineStr"/>
+      <c r="C80" s="9" t="inlineStr">
         <is>
           <t>&amp;sys_reset</t>
         </is>
       </c>
-      <c r="D77" s="9" t="inlineStr"/>
-      <c r="E77" s="9" t="inlineStr"/>
-      <c r="F77" s="9" t="inlineStr"/>
-      <c r="G77" s="9" t="inlineStr"/>
-      <c r="H77" s="9" t="inlineStr"/>
-      <c r="I77" s="9" t="inlineStr"/>
-      <c r="J77" s="9" t="inlineStr"/>
-      <c r="K77" s="9" t="inlineStr"/>
-      <c r="L77" s="9" t="inlineStr"/>
-      <c r="M77" s="9" t="inlineStr">
+      <c r="D80" s="9" t="inlineStr"/>
+      <c r="E80" s="9" t="inlineStr"/>
+      <c r="F80" s="9" t="inlineStr"/>
+      <c r="G80" s="9" t="inlineStr"/>
+      <c r="H80" s="9" t="inlineStr"/>
+      <c r="I80" s="9" t="inlineStr"/>
+      <c r="J80" s="9" t="inlineStr"/>
+      <c r="K80" s="9" t="inlineStr"/>
+      <c r="L80" s="9" t="inlineStr"/>
+      <c r="M80" s="9" t="inlineStr">
         <is>
           <t>&amp;sys_reset</t>
         </is>
       </c>
-      <c r="N77" s="9" t="inlineStr"/>
-    </row>
-    <row r="78" ht="30" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
+      <c r="N80" s="9" t="inlineStr"/>
+    </row>
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>Row 3</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
+      <c r="B81" s="7" t="inlineStr">
         <is>
           <t>pos 22
 &amp;none</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
+      <c r="C81" s="7" t="inlineStr">
         <is>
           <t>pos 23
 &amp;none</t>
         </is>
       </c>
-      <c r="D78" s="7" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr">
         <is>
           <t>pos 24
 &amp;none</t>
         </is>
       </c>
-      <c r="E78" s="7" t="inlineStr">
+      <c r="E81" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
-      <c r="F78" s="7" t="inlineStr">
+      <c r="F81" s="7" t="inlineStr">
         <is>
           <t>pos 26
 &amp;bootloader</t>
         </is>
       </c>
-      <c r="G78" s="7" t="inlineStr">
+      <c r="G81" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="H78" s="7" t="inlineStr"/>
-      <c r="I78" s="7" t="inlineStr">
+      <c r="H81" s="7" t="inlineStr"/>
+      <c r="I81" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="J78" s="7" t="inlineStr">
+      <c r="J81" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;bootloader</t>
         </is>
       </c>
-      <c r="K78" s="7" t="inlineStr">
+      <c r="K81" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;none</t>
         </is>
       </c>
-      <c r="L78" s="7" t="inlineStr">
+      <c r="L81" s="7" t="inlineStr">
         <is>
           <t>pos 31
 &amp;none</t>
         </is>
       </c>
-      <c r="M78" s="7" t="inlineStr">
+      <c r="M81" s="7" t="inlineStr">
         <is>
           <t>pos 32
 &amp;none</t>
         </is>
       </c>
-      <c r="N78" s="7" t="inlineStr">
+      <c r="N81" s="7" t="inlineStr">
         <is>
           <t>pos 33
 &amp;none</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="8" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B79" s="9" t="inlineStr"/>
-      <c r="C79" s="9" t="inlineStr"/>
-      <c r="D79" s="9" t="inlineStr"/>
-      <c r="E79" s="9" t="inlineStr"/>
-      <c r="F79" s="9" t="inlineStr">
+      <c r="B82" s="9" t="inlineStr"/>
+      <c r="C82" s="9" t="inlineStr"/>
+      <c r="D82" s="9" t="inlineStr"/>
+      <c r="E82" s="9" t="inlineStr"/>
+      <c r="F82" s="9" t="inlineStr">
         <is>
           <t>&amp;bootloader</t>
         </is>
       </c>
-      <c r="G79" s="9" t="inlineStr"/>
-      <c r="H79" s="9" t="inlineStr"/>
-      <c r="I79" s="9" t="inlineStr"/>
-      <c r="J79" s="9" t="inlineStr">
+      <c r="G82" s="9" t="inlineStr"/>
+      <c r="H82" s="9" t="inlineStr"/>
+      <c r="I82" s="9" t="inlineStr"/>
+      <c r="J82" s="9" t="inlineStr">
         <is>
           <t>&amp;bootloader</t>
         </is>
       </c>
-      <c r="K79" s="9" t="inlineStr"/>
-      <c r="L79" s="9" t="inlineStr"/>
-      <c r="M79" s="9" t="inlineStr"/>
-      <c r="N79" s="9" t="inlineStr"/>
-    </row>
-    <row r="80" ht="30" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>Row 4</t>
-        </is>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>pos 34
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C80" s="7" t="inlineStr">
-        <is>
-          <t>pos 35
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>pos 36
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F80" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G80" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="H80" s="7" t="inlineStr"/>
-      <c r="I80" s="7" t="inlineStr">
-        <is>
-          <t>pos 40
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J80" s="7" t="inlineStr">
-        <is>
-          <t>pos 41
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K80" s="7" t="inlineStr"/>
-      <c r="L80" s="7" t="inlineStr"/>
-      <c r="M80" s="7" t="inlineStr"/>
-      <c r="N80" s="7" t="inlineStr">
-        <is>
-          <t>pos 42
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B81" s="9" t="inlineStr"/>
-      <c r="C81" s="9" t="inlineStr"/>
-      <c r="D81" s="9" t="inlineStr"/>
-      <c r="E81" s="9" t="inlineStr"/>
-      <c r="F81" s="9" t="inlineStr"/>
-      <c r="G81" s="9" t="inlineStr"/>
-      <c r="H81" s="9" t="inlineStr"/>
-      <c r="I81" s="9" t="inlineStr"/>
-      <c r="J81" s="9" t="inlineStr"/>
-      <c r="K81" s="9" t="inlineStr"/>
-      <c r="L81" s="9" t="inlineStr"/>
-      <c r="M81" s="9" t="inlineStr"/>
-      <c r="N81" s="9" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t>BLUETOOTH レイヤー</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="n"/>
-      <c r="C82" s="4" t="n"/>
-      <c r="D82" s="4" t="n"/>
-      <c r="E82" s="4" t="n"/>
-      <c r="F82" s="4" t="n"/>
-      <c r="G82" s="4" t="n"/>
-      <c r="H82" s="4" t="n"/>
-      <c r="I82" s="4" t="n"/>
-      <c r="J82" s="4" t="n"/>
-      <c r="K82" s="4" t="n"/>
-      <c r="L82" s="4" t="n"/>
-      <c r="M82" s="4" t="n"/>
-      <c r="N82" s="5" t="n"/>
+      <c r="K82" s="9" t="inlineStr"/>
+      <c r="L82" s="9" t="inlineStr"/>
+      <c r="M82" s="9" t="inlineStr"/>
+      <c r="N82" s="9" t="inlineStr"/>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>Row 1</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>pos 0
-&amp;bt BT_SEL 0</t>
+          <t>pos 34
+&amp;none</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>pos 1
-&amp;bt BT_SEL 1</t>
+          <t>pos 35
+&amp;none</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>pos 2
-&amp;bt BT_SEL 2</t>
+          <t>pos 36
+&amp;none</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>pos 3
-&amp;bt BT_SEL 3</t>
+          <t>pos 37
+&amp;none</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>pos 4
-&amp;bt BT_SEL 4</t>
-        </is>
-      </c>
-      <c r="G83" s="7" t="inlineStr"/>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
       <c r="H83" s="7" t="inlineStr"/>
-      <c r="I83" s="7" t="inlineStr"/>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>pos 5
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K83" s="7" t="inlineStr">
-        <is>
-          <t>pos 6
-&amp;out OUT_USB</t>
-        </is>
-      </c>
-      <c r="L83" s="7" t="inlineStr">
-        <is>
-          <t>pos 7
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M83" s="7" t="inlineStr">
-        <is>
-          <t>pos 8
-&amp;none</t>
-        </is>
-      </c>
+          <t>pos 41
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K83" s="7" t="inlineStr"/>
+      <c r="L83" s="7" t="inlineStr"/>
+      <c r="M83" s="7" t="inlineStr"/>
       <c r="N83" s="7" t="inlineStr">
         <is>
-          <t>pos 9
+          <t>pos 42
 &amp;none</t>
         </is>
       </c>
@@ -10313,428 +10440,428 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bt BT_SEL 0</t>
-        </is>
-      </c>
-      <c r="C84" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bt BT_SEL 1</t>
-        </is>
-      </c>
-      <c r="D84" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bt BT_SEL 2</t>
-        </is>
-      </c>
-      <c r="E84" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bt BT_SEL 3</t>
-        </is>
-      </c>
-      <c r="F84" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bt BT_SEL 4</t>
-        </is>
-      </c>
+      <c r="B84" s="9" t="inlineStr"/>
+      <c r="C84" s="9" t="inlineStr"/>
+      <c r="D84" s="9" t="inlineStr"/>
+      <c r="E84" s="9" t="inlineStr"/>
+      <c r="F84" s="9" t="inlineStr"/>
       <c r="G84" s="9" t="inlineStr"/>
       <c r="H84" s="9" t="inlineStr"/>
       <c r="I84" s="9" t="inlineStr"/>
       <c r="J84" s="9" t="inlineStr"/>
-      <c r="K84" s="9" t="inlineStr">
-        <is>
-          <t>&amp;out OUT_USB</t>
-        </is>
-      </c>
+      <c r="K84" s="9" t="inlineStr"/>
       <c r="L84" s="9" t="inlineStr"/>
       <c r="M84" s="9" t="inlineStr"/>
       <c r="N84" s="9" t="inlineStr"/>
     </row>
-    <row r="85" ht="30" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>BLUETOOTH レイヤー</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="n"/>
+      <c r="C85" s="4" t="n"/>
+      <c r="D85" s="4" t="n"/>
+      <c r="E85" s="4" t="n"/>
+      <c r="F85" s="4" t="n"/>
+      <c r="G85" s="4" t="n"/>
+      <c r="H85" s="4" t="n"/>
+      <c r="I85" s="4" t="n"/>
+      <c r="J85" s="4" t="n"/>
+      <c r="K85" s="4" t="n"/>
+      <c r="L85" s="4" t="n"/>
+      <c r="M85" s="4" t="n"/>
+      <c r="N85" s="5" t="n"/>
+    </row>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>Row 1</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>pos 0
+&amp;bt BT_SEL 0</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>pos 1
+&amp;bt BT_SEL 1</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>pos 2
+&amp;bt BT_SEL 2</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>pos 3
+&amp;bt BT_SEL 3</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>pos 4
+&amp;bt BT_SEL 4</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="inlineStr"/>
+      <c r="H86" s="7" t="inlineStr"/>
+      <c r="I86" s="7" t="inlineStr"/>
+      <c r="J86" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K86" s="7" t="inlineStr">
+        <is>
+          <t>pos 6
+&amp;out OUT_USB</t>
+        </is>
+      </c>
+      <c r="L86" s="7" t="inlineStr">
+        <is>
+          <t>pos 7
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M86" s="7" t="inlineStr">
+        <is>
+          <t>pos 8
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N86" s="7" t="inlineStr">
+        <is>
+          <t>pos 9
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>&amp;bt BT_SEL 0</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>&amp;bt BT_SEL 1</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>&amp;bt BT_SEL 2</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="inlineStr">
+        <is>
+          <t>&amp;bt BT_SEL 3</t>
+        </is>
+      </c>
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>&amp;bt BT_SEL 4</t>
+        </is>
+      </c>
+      <c r="G87" s="9" t="inlineStr"/>
+      <c r="H87" s="9" t="inlineStr"/>
+      <c r="I87" s="9" t="inlineStr"/>
+      <c r="J87" s="9" t="inlineStr"/>
+      <c r="K87" s="9" t="inlineStr">
+        <is>
+          <t>&amp;out OUT_USB</t>
+        </is>
+      </c>
+      <c r="L87" s="9" t="inlineStr"/>
+      <c r="M87" s="9" t="inlineStr"/>
+      <c r="N87" s="9" t="inlineStr"/>
+    </row>
+    <row r="88" ht="30" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>Row 2</t>
         </is>
       </c>
-      <c r="B85" s="7" t="inlineStr">
+      <c r="B88" s="7" t="inlineStr">
         <is>
           <t>pos 10
 &amp;bt BT_CLR_ALL</t>
         </is>
       </c>
-      <c r="C85" s="7" t="inlineStr">
+      <c r="C88" s="7" t="inlineStr">
         <is>
           <t>pos 11
 &amp;none</t>
         </is>
       </c>
-      <c r="D85" s="7" t="inlineStr">
+      <c r="D88" s="7" t="inlineStr">
         <is>
           <t>pos 12
 &amp;none</t>
         </is>
       </c>
-      <c r="E85" s="7" t="inlineStr">
+      <c r="E88" s="7" t="inlineStr">
         <is>
           <t>pos 13
 &amp;none</t>
         </is>
       </c>
-      <c r="F85" s="7" t="inlineStr">
+      <c r="F88" s="7" t="inlineStr">
         <is>
           <t>pos 14
 &amp;none</t>
         </is>
       </c>
-      <c r="G85" s="7" t="inlineStr">
+      <c r="G88" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;none</t>
         </is>
       </c>
-      <c r="H85" s="7" t="inlineStr"/>
-      <c r="I85" s="7" t="inlineStr">
+      <c r="H88" s="7" t="inlineStr"/>
+      <c r="I88" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="J85" s="7" t="inlineStr">
+      <c r="J88" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="K85" s="7" t="inlineStr">
+      <c r="K88" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;none</t>
         </is>
       </c>
-      <c r="L85" s="7" t="inlineStr">
+      <c r="L88" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;none</t>
         </is>
       </c>
-      <c r="M85" s="7" t="inlineStr">
+      <c r="M88" s="7" t="inlineStr">
         <is>
           <t>pos 20
 &amp;none</t>
         </is>
       </c>
-      <c r="N85" s="7" t="inlineStr">
+      <c r="N88" s="7" t="inlineStr">
         <is>
           <t>pos 21
 &amp;none</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="8" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B86" s="9" t="inlineStr">
+      <c r="B89" s="9" t="inlineStr">
         <is>
           <t>&amp;bt BT_CLR_ALL</t>
         </is>
       </c>
-      <c r="C86" s="9" t="inlineStr"/>
-      <c r="D86" s="9" t="inlineStr"/>
-      <c r="E86" s="9" t="inlineStr"/>
-      <c r="F86" s="9" t="inlineStr"/>
-      <c r="G86" s="9" t="inlineStr"/>
-      <c r="H86" s="9" t="inlineStr"/>
-      <c r="I86" s="9" t="inlineStr"/>
-      <c r="J86" s="9" t="inlineStr"/>
-      <c r="K86" s="9" t="inlineStr"/>
-      <c r="L86" s="9" t="inlineStr"/>
-      <c r="M86" s="9" t="inlineStr"/>
-      <c r="N86" s="9" t="inlineStr"/>
-    </row>
-    <row r="87" ht="30" customHeight="1">
-      <c r="A87" s="6" t="inlineStr">
+      <c r="C89" s="9" t="inlineStr"/>
+      <c r="D89" s="9" t="inlineStr"/>
+      <c r="E89" s="9" t="inlineStr"/>
+      <c r="F89" s="9" t="inlineStr"/>
+      <c r="G89" s="9" t="inlineStr"/>
+      <c r="H89" s="9" t="inlineStr"/>
+      <c r="I89" s="9" t="inlineStr"/>
+      <c r="J89" s="9" t="inlineStr"/>
+      <c r="K89" s="9" t="inlineStr"/>
+      <c r="L89" s="9" t="inlineStr"/>
+      <c r="M89" s="9" t="inlineStr"/>
+      <c r="N89" s="9" t="inlineStr"/>
+    </row>
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>Row 3</t>
         </is>
       </c>
-      <c r="B87" s="7" t="inlineStr">
+      <c r="B90" s="7" t="inlineStr">
         <is>
           <t>pos 22
 &amp;none</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr">
+      <c r="C90" s="7" t="inlineStr">
         <is>
           <t>pos 23
 &amp;none</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
         <is>
           <t>pos 24
 &amp;bt BT_CLR</t>
         </is>
       </c>
-      <c r="E87" s="7" t="inlineStr">
+      <c r="E90" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
-      <c r="F87" s="7" t="inlineStr">
+      <c r="F90" s="7" t="inlineStr">
         <is>
           <t>pos 26
 &amp;out OUT_BLE</t>
         </is>
       </c>
-      <c r="G87" s="7" t="inlineStr">
+      <c r="G90" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="H87" s="7" t="inlineStr"/>
-      <c r="I87" s="7" t="inlineStr">
+      <c r="H90" s="7" t="inlineStr"/>
+      <c r="I90" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="J87" s="7" t="inlineStr">
+      <c r="J90" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;none</t>
         </is>
       </c>
-      <c r="K87" s="7" t="inlineStr">
+      <c r="K90" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;none</t>
         </is>
       </c>
-      <c r="L87" s="7" t="inlineStr">
+      <c r="L90" s="7" t="inlineStr">
         <is>
           <t>pos 31
 &amp;none</t>
         </is>
       </c>
-      <c r="M87" s="7" t="inlineStr">
+      <c r="M90" s="7" t="inlineStr">
         <is>
           <t>pos 32
 &amp;none</t>
         </is>
       </c>
-      <c r="N87" s="7" t="inlineStr">
+      <c r="N90" s="7" t="inlineStr">
         <is>
           <t>pos 33
 &amp;none</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="8" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B88" s="9" t="inlineStr"/>
-      <c r="C88" s="9" t="inlineStr"/>
-      <c r="D88" s="9" t="inlineStr">
+      <c r="B91" s="9" t="inlineStr"/>
+      <c r="C91" s="9" t="inlineStr"/>
+      <c r="D91" s="9" t="inlineStr">
         <is>
           <t>&amp;bt BT_CLR</t>
         </is>
       </c>
-      <c r="E88" s="9" t="inlineStr"/>
-      <c r="F88" s="9" t="inlineStr">
+      <c r="E91" s="9" t="inlineStr"/>
+      <c r="F91" s="9" t="inlineStr">
         <is>
           <t>&amp;out OUT_BLE</t>
         </is>
       </c>
-      <c r="G88" s="9" t="inlineStr"/>
-      <c r="H88" s="9" t="inlineStr"/>
-      <c r="I88" s="9" t="inlineStr"/>
-      <c r="J88" s="9" t="inlineStr"/>
-      <c r="K88" s="9" t="inlineStr"/>
-      <c r="L88" s="9" t="inlineStr"/>
-      <c r="M88" s="9" t="inlineStr"/>
-      <c r="N88" s="9" t="inlineStr"/>
-    </row>
-    <row r="89" ht="30" customHeight="1">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>Row 4</t>
-        </is>
-      </c>
-      <c r="B89" s="7" t="inlineStr">
-        <is>
-          <t>pos 34
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>pos 35
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>pos 36
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F89" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G89" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="H89" s="7" t="inlineStr"/>
-      <c r="I89" s="7" t="inlineStr">
-        <is>
-          <t>pos 40
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J89" s="7" t="inlineStr">
-        <is>
-          <t>pos 41
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K89" s="7" t="inlineStr"/>
-      <c r="L89" s="7" t="inlineStr"/>
-      <c r="M89" s="7" t="inlineStr"/>
-      <c r="N89" s="7" t="inlineStr">
-        <is>
-          <t>pos 42
-&amp;none</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="8" t="inlineStr">
-        <is>
-          <t>タップ</t>
-        </is>
-      </c>
-      <c r="B90" s="9" t="inlineStr"/>
-      <c r="C90" s="9" t="inlineStr"/>
-      <c r="D90" s="9" t="inlineStr"/>
-      <c r="E90" s="9" t="inlineStr"/>
-      <c r="F90" s="9" t="inlineStr"/>
-      <c r="G90" s="9" t="inlineStr"/>
-      <c r="H90" s="9" t="inlineStr"/>
-      <c r="I90" s="9" t="inlineStr"/>
-      <c r="J90" s="9" t="inlineStr"/>
-      <c r="K90" s="9" t="inlineStr"/>
-      <c r="L90" s="9" t="inlineStr"/>
-      <c r="M90" s="9" t="inlineStr"/>
-      <c r="N90" s="9" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>VIM_VISUAL_BASE レイヤー</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="n"/>
-      <c r="C91" s="4" t="n"/>
-      <c r="D91" s="4" t="n"/>
-      <c r="E91" s="4" t="n"/>
-      <c r="F91" s="4" t="n"/>
-      <c r="G91" s="4" t="n"/>
-      <c r="H91" s="4" t="n"/>
-      <c r="I91" s="4" t="n"/>
-      <c r="J91" s="4" t="n"/>
-      <c r="K91" s="4" t="n"/>
-      <c r="L91" s="4" t="n"/>
-      <c r="M91" s="4" t="n"/>
-      <c r="N91" s="5" t="n"/>
+      <c r="G91" s="9" t="inlineStr"/>
+      <c r="H91" s="9" t="inlineStr"/>
+      <c r="I91" s="9" t="inlineStr"/>
+      <c r="J91" s="9" t="inlineStr"/>
+      <c r="K91" s="9" t="inlineStr"/>
+      <c r="L91" s="9" t="inlineStr"/>
+      <c r="M91" s="9" t="inlineStr"/>
+      <c r="N91" s="9" t="inlineStr"/>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>Row 1</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>pos 0
+          <t>pos 34
 &amp;none</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>pos 1
-&amp;kp LS(LC(RIGHT))</t>
+          <t>pos 35
+&amp;none</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>pos 2
-&amp;kp LS(LC(RIGHT))</t>
+          <t>pos 36
+&amp;none</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>pos 3
+          <t>pos 37
 &amp;none</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>pos 4
-&amp;none</t>
-        </is>
-      </c>
-      <c r="G92" s="7" t="inlineStr"/>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
       <c r="H92" s="7" t="inlineStr"/>
-      <c r="I92" s="7" t="inlineStr"/>
+      <c r="I92" s="7" t="inlineStr">
+        <is>
+          <t>pos 40
+&amp;none</t>
+        </is>
+      </c>
       <c r="J92" s="7" t="inlineStr">
         <is>
-          <t>pos 5
-&amp;macro_vim_visual_y</t>
-        </is>
-      </c>
-      <c r="K92" s="7" t="inlineStr">
-        <is>
-          <t>pos 6
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L92" s="7" t="inlineStr">
-        <is>
-          <t>pos 7
-&amp;none</t>
-        </is>
-      </c>
-      <c r="M92" s="7" t="inlineStr">
-        <is>
-          <t>pos 8
-&amp;none</t>
-        </is>
-      </c>
+          <t>pos 41
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K92" s="7" t="inlineStr"/>
+      <c r="L92" s="7" t="inlineStr"/>
+      <c r="M92" s="7" t="inlineStr"/>
       <c r="N92" s="7" t="inlineStr">
         <is>
-          <t>pos 9
-&amp;macro_vim_visual_p</t>
+          <t>pos 42
+&amp;none</t>
         </is>
       </c>
     </row>
@@ -10745,650 +10872,527 @@
         </is>
       </c>
       <c r="B93" s="9" t="inlineStr"/>
-      <c r="C93" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LS(LC(RIGHT))</t>
-        </is>
-      </c>
-      <c r="D93" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LS(LC(RIGHT))</t>
-        </is>
-      </c>
+      <c r="C93" s="9" t="inlineStr"/>
+      <c r="D93" s="9" t="inlineStr"/>
       <c r="E93" s="9" t="inlineStr"/>
       <c r="F93" s="9" t="inlineStr"/>
       <c r="G93" s="9" t="inlineStr"/>
       <c r="H93" s="9" t="inlineStr"/>
       <c r="I93" s="9" t="inlineStr"/>
-      <c r="J93" s="9" t="inlineStr">
-        <is>
-          <t>macro_vim_visual_y</t>
-        </is>
-      </c>
+      <c r="J93" s="9" t="inlineStr"/>
       <c r="K93" s="9" t="inlineStr"/>
       <c r="L93" s="9" t="inlineStr"/>
       <c r="M93" s="9" t="inlineStr"/>
-      <c r="N93" s="9" t="inlineStr">
-        <is>
-          <t>macro_vim_visual_p</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="30" customHeight="1">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>Row 2</t>
-        </is>
-      </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>pos 10
-&amp;kp LCTRL</t>
-        </is>
-      </c>
-      <c r="C94" s="7" t="inlineStr">
-        <is>
-          <t>pos 11
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>pos 12
-&amp;macro_vim_visual_cut</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t>pos 13
-&amp;none</t>
-        </is>
-      </c>
-      <c r="F94" s="7" t="inlineStr">
-        <is>
-          <t>pos 14
-&amp;mm_vim_visual_g</t>
-        </is>
-      </c>
-      <c r="G94" s="7" t="inlineStr">
-        <is>
-          <t>pos 15
-&amp;none</t>
-        </is>
-      </c>
-      <c r="H94" s="7" t="inlineStr"/>
-      <c r="I94" s="7" t="inlineStr">
-        <is>
-          <t>pos 16
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J94" s="7" t="inlineStr">
-        <is>
-          <t>pos 17
-&amp;kp LS(LEFT)</t>
-        </is>
-      </c>
-      <c r="K94" s="7" t="inlineStr">
-        <is>
-          <t>pos 18
-&amp;kp LS(DOWN)</t>
-        </is>
-      </c>
-      <c r="L94" s="7" t="inlineStr">
-        <is>
-          <t>pos 19
-&amp;kp LS(UP)</t>
-        </is>
-      </c>
-      <c r="M94" s="7" t="inlineStr">
-        <is>
-          <t>pos 20
-&amp;kp LS(RIGHT)</t>
-        </is>
-      </c>
-      <c r="N94" s="7" t="inlineStr">
-        <is>
-          <t>pos 21
-&amp;kp RCTRL</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="45" customHeight="1">
-      <c r="A95" s="8" t="inlineStr">
+      <c r="N93" s="9" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>MOUSE_MOVE レイヤー</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="n"/>
+      <c r="C94" s="4" t="n"/>
+      <c r="D94" s="4" t="n"/>
+      <c r="E94" s="4" t="n"/>
+      <c r="F94" s="4" t="n"/>
+      <c r="G94" s="4" t="n"/>
+      <c r="H94" s="4" t="n"/>
+      <c r="I94" s="4" t="n"/>
+      <c r="J94" s="4" t="n"/>
+      <c r="K94" s="4" t="n"/>
+      <c r="L94" s="4" t="n"/>
+      <c r="M94" s="4" t="n"/>
+      <c r="N94" s="5" t="n"/>
+    </row>
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>Row 1</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>pos 0
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>pos 1
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>pos 2
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>pos 3
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>pos 4
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr"/>
+      <c r="H95" s="7" t="inlineStr"/>
+      <c r="I95" s="7" t="inlineStr"/>
+      <c r="J95" s="7" t="inlineStr">
+        <is>
+          <t>pos 5
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K95" s="7" t="inlineStr">
+        <is>
+          <t>pos 6
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
+        <is>
+          <t>pos 7
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M95" s="7" t="inlineStr">
+        <is>
+          <t>pos 8
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N95" s="7" t="inlineStr">
+        <is>
+          <t>pos 9
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B95" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LCTRL</t>
-        </is>
-      </c>
-      <c r="C95" s="9" t="inlineStr"/>
-      <c r="D95" s="9" t="inlineStr">
-        <is>
-          <t>macro_vim_visual_cut</t>
-        </is>
-      </c>
-      <c r="E95" s="9" t="inlineStr"/>
-      <c r="F95" s="10" t="inlineStr">
-        <is>
-          <t>mm_vim_visual_g[0]
-▸ td_vim_visual_g[0]
-▸ &amp;none</t>
-        </is>
-      </c>
-      <c r="G95" s="9" t="inlineStr"/>
-      <c r="H95" s="9" t="inlineStr"/>
-      <c r="I95" s="9" t="inlineStr"/>
-      <c r="J95" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LS(LEFT)</t>
-        </is>
-      </c>
-      <c r="K95" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LS(DOWN)</t>
-        </is>
-      </c>
-      <c r="L95" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LS(UP)</t>
-        </is>
-      </c>
-      <c r="M95" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LS(RIGHT)</t>
-        </is>
-      </c>
-      <c r="N95" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp RCTRL</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="45" customHeight="1">
-      <c r="A96" s="8" t="inlineStr">
-        <is>
-          <t>ダブルタップ</t>
-        </is>
-      </c>
-      <c r="B96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="B96" s="9" t="inlineStr"/>
       <c r="C96" s="9" t="inlineStr"/>
-      <c r="D96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="D96" s="9" t="inlineStr"/>
       <c r="E96" s="9" t="inlineStr"/>
-      <c r="F96" s="10" t="inlineStr">
-        <is>
-          <t>mm_vim_visual_g[0]
-▸ td_vim_visual_g[1]
-▸ &amp;kp LS(LC(HOME))</t>
-        </is>
-      </c>
+      <c r="F96" s="9" t="inlineStr"/>
       <c r="G96" s="9" t="inlineStr"/>
       <c r="H96" s="9" t="inlineStr"/>
       <c r="I96" s="9" t="inlineStr"/>
-      <c r="J96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="K96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="L96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="M96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N96" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="J96" s="9" t="inlineStr"/>
+      <c r="K96" s="9" t="inlineStr"/>
+      <c r="L96" s="9" t="inlineStr"/>
+      <c r="M96" s="9" t="inlineStr"/>
+      <c r="N96" s="9" t="inlineStr"/>
     </row>
     <row r="97" ht="30" customHeight="1">
-      <c r="A97" s="8" t="inlineStr">
-        <is>
-          <t>Shift+</t>
-        </is>
-      </c>
-      <c r="B97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="C97" s="9" t="inlineStr"/>
-      <c r="D97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="E97" s="9" t="inlineStr"/>
-      <c r="F97" s="10" t="inlineStr">
-        <is>
-          <t>mm_vim_visual_g[1]
-▸ &amp;kp LS(LC(END))</t>
-        </is>
-      </c>
-      <c r="G97" s="9" t="inlineStr"/>
-      <c r="H97" s="9" t="inlineStr"/>
-      <c r="I97" s="9" t="inlineStr"/>
-      <c r="J97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="K97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="L97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="M97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="N97" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="30" customHeight="1">
-      <c r="A98" s="6" t="inlineStr">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>Row 2</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>pos 10
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>pos 11
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>pos 12
+&amp;none</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>pos 13
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>pos 14
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>pos 15
+&amp;none</t>
+        </is>
+      </c>
+      <c r="H97" s="7" t="inlineStr"/>
+      <c r="I97" s="7" t="inlineStr">
+        <is>
+          <t>pos 16
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J97" s="7" t="inlineStr">
+        <is>
+          <t>pos 17
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K97" s="7" t="inlineStr">
+        <is>
+          <t>pos 18
+&amp;none</t>
+        </is>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>pos 19
+&amp;mo MOUSE_SCROLL</t>
+        </is>
+      </c>
+      <c r="M97" s="7" t="inlineStr">
+        <is>
+          <t>pos 20
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N97" s="7" t="inlineStr">
+        <is>
+          <t>pos 21
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>タップ</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="inlineStr"/>
+      <c r="C98" s="9" t="inlineStr"/>
+      <c r="D98" s="9" t="inlineStr"/>
+      <c r="E98" s="9" t="inlineStr"/>
+      <c r="F98" s="9" t="inlineStr"/>
+      <c r="G98" s="9" t="inlineStr"/>
+      <c r="H98" s="9" t="inlineStr"/>
+      <c r="I98" s="9" t="inlineStr"/>
+      <c r="J98" s="9" t="inlineStr"/>
+      <c r="K98" s="9" t="inlineStr"/>
+      <c r="L98" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mo MOUSE_SCROLL</t>
+        </is>
+      </c>
+      <c r="M98" s="9" t="inlineStr"/>
+      <c r="N98" s="9" t="inlineStr"/>
+    </row>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>Row 3</t>
         </is>
       </c>
-      <c r="B98" s="7" t="inlineStr">
+      <c r="B99" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;kp LEFT_SHIFT</t>
-        </is>
-      </c>
-      <c r="C98" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
         <is>
           <t>pos 23
-&amp;macro_vim_visual_cut</t>
-        </is>
-      </c>
-      <c r="D98" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
         <is>
           <t>pos 24
 &amp;none</t>
         </is>
       </c>
-      <c r="E98" s="7" t="inlineStr">
+      <c r="E99" s="7" t="inlineStr">
         <is>
           <t>pos 25
-&amp;macro_vim_visual_exit</t>
-        </is>
-      </c>
-      <c r="F98" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
         <is>
           <t>pos 26
-&amp;kp LS(LC(LEFT))</t>
-        </is>
-      </c>
-      <c r="G98" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="H98" s="7" t="inlineStr"/>
-      <c r="I98" s="7" t="inlineStr">
+      <c r="H99" s="7" t="inlineStr"/>
+      <c r="I99" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="J98" s="7" t="inlineStr">
+      <c r="J99" s="7" t="inlineStr">
         <is>
           <t>pos 29
-&amp;kp F3</t>
-        </is>
-      </c>
-      <c r="K98" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K99" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;none</t>
         </is>
       </c>
-      <c r="L98" s="7" t="inlineStr">
+      <c r="L99" s="7" t="inlineStr">
         <is>
           <t>pos 31
 &amp;none</t>
         </is>
       </c>
-      <c r="M98" s="7" t="inlineStr">
+      <c r="M99" s="7" t="inlineStr">
         <is>
           <t>pos 32
 &amp;none</t>
         </is>
       </c>
-      <c r="N98" s="7" t="inlineStr">
+      <c r="N99" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;kp RIGHT_SHIFT</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="8" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B99" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LEFT_SHIFT</t>
-        </is>
-      </c>
-      <c r="C99" s="9" t="inlineStr">
-        <is>
-          <t>macro_vim_visual_cut</t>
-        </is>
-      </c>
-      <c r="D99" s="9" t="inlineStr"/>
-      <c r="E99" s="9" t="inlineStr">
-        <is>
-          <t>macro_vim_visual_exit</t>
-        </is>
-      </c>
-      <c r="F99" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LS(LC(LEFT))</t>
-        </is>
-      </c>
-      <c r="G99" s="9" t="inlineStr"/>
-      <c r="H99" s="9" t="inlineStr"/>
-      <c r="I99" s="9" t="inlineStr"/>
-      <c r="J99" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp F3</t>
-        </is>
-      </c>
-      <c r="K99" s="9" t="inlineStr"/>
-      <c r="L99" s="9" t="inlineStr"/>
-      <c r="M99" s="9" t="inlineStr"/>
-      <c r="N99" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp RIGHT_SHIFT</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="30" customHeight="1">
-      <c r="A100" s="6" t="inlineStr">
+      <c r="B100" s="9" t="inlineStr"/>
+      <c r="C100" s="9" t="inlineStr"/>
+      <c r="D100" s="9" t="inlineStr"/>
+      <c r="E100" s="9" t="inlineStr"/>
+      <c r="F100" s="9" t="inlineStr"/>
+      <c r="G100" s="9" t="inlineStr"/>
+      <c r="H100" s="9" t="inlineStr"/>
+      <c r="I100" s="9" t="inlineStr"/>
+      <c r="J100" s="9" t="inlineStr"/>
+      <c r="K100" s="9" t="inlineStr"/>
+      <c r="L100" s="9" t="inlineStr"/>
+      <c r="M100" s="9" t="inlineStr"/>
+      <c r="N100" s="9" t="inlineStr"/>
+    </row>
+    <row r="101" ht="30" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>Row 4</t>
         </is>
       </c>
-      <c r="B100" s="7" t="inlineStr">
+      <c r="B101" s="7" t="inlineStr">
         <is>
           <t>pos 34
 &amp;none</t>
         </is>
       </c>
-      <c r="C100" s="7" t="inlineStr">
+      <c r="C101" s="7" t="inlineStr">
         <is>
           <t>pos 35
 &amp;none</t>
         </is>
       </c>
-      <c r="D100" s="7" t="inlineStr">
+      <c r="D101" s="7" t="inlineStr">
         <is>
           <t>pos 36
 &amp;none</t>
         </is>
       </c>
-      <c r="E100" s="7" t="inlineStr">
+      <c r="E101" s="7" t="inlineStr">
         <is>
           <t>pos 37
 &amp;none</t>
         </is>
       </c>
-      <c r="F100" s="7" t="inlineStr">
+      <c r="F101" s="7" t="inlineStr">
         <is>
           <t>pos 38
 &amp;none</t>
         </is>
       </c>
-      <c r="G100" s="7" t="inlineStr">
+      <c r="G101" s="7" t="inlineStr">
         <is>
           <t>pos 39
-&amp;mo VIM_VISUAL_SYM</t>
-        </is>
-      </c>
-      <c r="H100" s="7" t="inlineStr"/>
-      <c r="I100" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="inlineStr"/>
+      <c r="I101" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;none</t>
         </is>
       </c>
-      <c r="J100" s="7" t="inlineStr">
+      <c r="J101" s="7" t="inlineStr">
         <is>
           <t>pos 41
-&amp;mo VIM_VISUAL_SYM</t>
-        </is>
-      </c>
-      <c r="K100" s="7" t="inlineStr"/>
-      <c r="L100" s="7" t="inlineStr"/>
-      <c r="M100" s="7" t="inlineStr"/>
-      <c r="N100" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K101" s="7" t="inlineStr"/>
+      <c r="L101" s="7" t="inlineStr"/>
+      <c r="M101" s="7" t="inlineStr"/>
+      <c r="N101" s="7" t="inlineStr">
         <is>
           <t>pos 42
 &amp;none</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="8" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
         </is>
       </c>
-      <c r="B101" s="9" t="inlineStr"/>
-      <c r="C101" s="9" t="inlineStr"/>
-      <c r="D101" s="9" t="inlineStr"/>
-      <c r="E101" s="9" t="inlineStr"/>
-      <c r="F101" s="9" t="inlineStr"/>
-      <c r="G101" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mo VIM_VISUAL_SYM</t>
-        </is>
-      </c>
-      <c r="H101" s="9" t="inlineStr"/>
-      <c r="I101" s="9" t="inlineStr"/>
-      <c r="J101" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mo VIM_VISUAL_SYM</t>
-        </is>
-      </c>
-      <c r="K101" s="9" t="inlineStr"/>
-      <c r="L101" s="9" t="inlineStr"/>
-      <c r="M101" s="9" t="inlineStr"/>
-      <c r="N101" s="9" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="inlineStr">
-        <is>
-          <t>VIM_VISUAL_SYM レイヤー</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="n"/>
-      <c r="C102" s="4" t="n"/>
-      <c r="D102" s="4" t="n"/>
-      <c r="E102" s="4" t="n"/>
-      <c r="F102" s="4" t="n"/>
-      <c r="G102" s="4" t="n"/>
-      <c r="H102" s="4" t="n"/>
-      <c r="I102" s="4" t="n"/>
-      <c r="J102" s="4" t="n"/>
-      <c r="K102" s="4" t="n"/>
-      <c r="L102" s="4" t="n"/>
-      <c r="M102" s="4" t="n"/>
-      <c r="N102" s="5" t="n"/>
-    </row>
-    <row r="103" ht="30" customHeight="1">
-      <c r="A103" s="6" t="inlineStr">
+      <c r="B102" s="9" t="inlineStr"/>
+      <c r="C102" s="9" t="inlineStr"/>
+      <c r="D102" s="9" t="inlineStr"/>
+      <c r="E102" s="9" t="inlineStr"/>
+      <c r="F102" s="9" t="inlineStr"/>
+      <c r="G102" s="9" t="inlineStr"/>
+      <c r="H102" s="9" t="inlineStr"/>
+      <c r="I102" s="9" t="inlineStr"/>
+      <c r="J102" s="9" t="inlineStr"/>
+      <c r="K102" s="9" t="inlineStr"/>
+      <c r="L102" s="9" t="inlineStr"/>
+      <c r="M102" s="9" t="inlineStr"/>
+      <c r="N102" s="9" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>MOUSE_SCROLL レイヤー</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="n"/>
+      <c r="C103" s="4" t="n"/>
+      <c r="D103" s="4" t="n"/>
+      <c r="E103" s="4" t="n"/>
+      <c r="F103" s="4" t="n"/>
+      <c r="G103" s="4" t="n"/>
+      <c r="H103" s="4" t="n"/>
+      <c r="I103" s="4" t="n"/>
+      <c r="J103" s="4" t="n"/>
+      <c r="K103" s="4" t="n"/>
+      <c r="L103" s="4" t="n"/>
+      <c r="M103" s="4" t="n"/>
+      <c r="N103" s="5" t="n"/>
+    </row>
+    <row r="104" ht="30" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
         <is>
           <t>Row 1</t>
         </is>
       </c>
-      <c r="B103" s="7" t="inlineStr">
+      <c r="B104" s="7" t="inlineStr">
         <is>
           <t>pos 0
 &amp;none</t>
         </is>
       </c>
-      <c r="C103" s="7" t="inlineStr">
+      <c r="C104" s="7" t="inlineStr">
         <is>
           <t>pos 1
 &amp;none</t>
         </is>
       </c>
-      <c r="D103" s="7" t="inlineStr">
+      <c r="D104" s="7" t="inlineStr">
         <is>
           <t>pos 2
 &amp;none</t>
         </is>
       </c>
-      <c r="E103" s="7" t="inlineStr">
+      <c r="E104" s="7" t="inlineStr">
         <is>
           <t>pos 3
-&amp;mm_vim_visual_shift_4</t>
-        </is>
-      </c>
-      <c r="F103" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr">
         <is>
           <t>pos 4
 &amp;none</t>
         </is>
       </c>
-      <c r="G103" s="7" t="inlineStr"/>
-      <c r="H103" s="7" t="inlineStr"/>
-      <c r="I103" s="7" t="inlineStr"/>
-      <c r="J103" s="7" t="inlineStr">
+      <c r="G104" s="7" t="inlineStr"/>
+      <c r="H104" s="7" t="inlineStr"/>
+      <c r="I104" s="7" t="inlineStr"/>
+      <c r="J104" s="7" t="inlineStr">
         <is>
           <t>pos 5
-&amp;mm_vim_visual_shift_6</t>
-        </is>
-      </c>
-      <c r="K103" s="7" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K104" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;none</t>
         </is>
       </c>
-      <c r="L103" s="7" t="inlineStr">
+      <c r="L104" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="M103" s="7" t="inlineStr">
+      <c r="M104" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;none</t>
         </is>
       </c>
-      <c r="N103" s="7" t="inlineStr">
+      <c r="N104" s="7" t="inlineStr">
         <is>
           <t>pos 9
-&amp;kp LS(HOME)</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="30" customHeight="1">
-      <c r="A104" s="8" t="inlineStr">
+&amp;none</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="8" t="inlineStr">
         <is>
           <t>タップ</t>
-        </is>
-      </c>
-      <c r="B104" s="9" t="inlineStr"/>
-      <c r="C104" s="9" t="inlineStr"/>
-      <c r="D104" s="9" t="inlineStr"/>
-      <c r="E104" s="10" t="inlineStr">
-        <is>
-          <t>mm_vim_visual_shift_4[0]
-▸ &amp;none</t>
-        </is>
-      </c>
-      <c r="F104" s="9" t="inlineStr"/>
-      <c r="G104" s="9" t="inlineStr"/>
-      <c r="H104" s="9" t="inlineStr"/>
-      <c r="I104" s="9" t="inlineStr"/>
-      <c r="J104" s="10" t="inlineStr">
-        <is>
-          <t>mm_vim_visual_shift_6[0]
-▸ &amp;none</t>
-        </is>
-      </c>
-      <c r="K104" s="9" t="inlineStr"/>
-      <c r="L104" s="9" t="inlineStr"/>
-      <c r="M104" s="9" t="inlineStr"/>
-      <c r="N104" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LS(HOME)</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="30" customHeight="1">
-      <c r="A105" s="8" t="inlineStr">
-        <is>
-          <t>Shift+</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr"/>
       <c r="C105" s="9" t="inlineStr"/>
       <c r="D105" s="9" t="inlineStr"/>
-      <c r="E105" s="10" t="inlineStr">
-        <is>
-          <t>mm_vim_visual_shift_4[1]
-▸ &amp;kp LS(END)</t>
-        </is>
-      </c>
+      <c r="E105" s="9" t="inlineStr"/>
       <c r="F105" s="9" t="inlineStr"/>
       <c r="G105" s="9" t="inlineStr"/>
       <c r="H105" s="9" t="inlineStr"/>
       <c r="I105" s="9" t="inlineStr"/>
-      <c r="J105" s="10" t="inlineStr">
-        <is>
-          <t>mm_vim_visual_shift_6[1]
-▸ &amp;kp LS(HOME)</t>
-        </is>
-      </c>
+      <c r="J105" s="9" t="inlineStr"/>
       <c r="K105" s="9" t="inlineStr"/>
       <c r="L105" s="9" t="inlineStr"/>
       <c r="M105" s="9" t="inlineStr"/>
-      <c r="N105" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="N105" s="9" t="inlineStr"/>
     </row>
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="6" t="inlineStr">
@@ -11399,7 +11403,7 @@
       <c r="B106" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;kp LCTRL</t>
+&amp;none</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
@@ -11442,13 +11446,13 @@
       <c r="J106" s="7" t="inlineStr">
         <is>
           <t>pos 17
-&amp;kp LS(LEFT)</t>
+&amp;none</t>
         </is>
       </c>
       <c r="K106" s="7" t="inlineStr">
         <is>
           <t>pos 18
-&amp;none</t>
+&amp;mkp MB1</t>
         </is>
       </c>
       <c r="L106" s="7" t="inlineStr">
@@ -11460,13 +11464,13 @@
       <c r="M106" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
+&amp;mkp MB2</t>
         </is>
       </c>
       <c r="N106" s="7" t="inlineStr">
         <is>
           <t>pos 21
-&amp;kp RCTRL</t>
+&amp;none</t>
         </is>
       </c>
     </row>
@@ -11476,11 +11480,7 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B107" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LCTRL</t>
-        </is>
-      </c>
+      <c r="B107" s="9" t="inlineStr"/>
       <c r="C107" s="9" t="inlineStr"/>
       <c r="D107" s="9" t="inlineStr"/>
       <c r="E107" s="9" t="inlineStr"/>
@@ -11488,19 +11488,19 @@
       <c r="G107" s="9" t="inlineStr"/>
       <c r="H107" s="9" t="inlineStr"/>
       <c r="I107" s="9" t="inlineStr"/>
-      <c r="J107" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LS(LEFT)</t>
-        </is>
-      </c>
-      <c r="K107" s="9" t="inlineStr"/>
+      <c r="J107" s="9" t="inlineStr"/>
+      <c r="K107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB1</t>
+        </is>
+      </c>
       <c r="L107" s="9" t="inlineStr"/>
-      <c r="M107" s="9" t="inlineStr"/>
-      <c r="N107" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp RCTRL</t>
-        </is>
-      </c>
+      <c r="M107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB2</t>
+        </is>
+      </c>
+      <c r="N107" s="9" t="inlineStr"/>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
@@ -11511,7 +11511,7 @@
       <c r="B108" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;kp LEFT_SHIFT</t>
+&amp;none</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
@@ -11560,7 +11560,7 @@
       <c r="K108" s="7" t="inlineStr">
         <is>
           <t>pos 30
-&amp;none</t>
+&amp;mkp MB4</t>
         </is>
       </c>
       <c r="L108" s="7" t="inlineStr">
@@ -11572,13 +11572,13 @@
       <c r="M108" s="7" t="inlineStr">
         <is>
           <t>pos 32
-&amp;none</t>
+&amp;mkp MB5</t>
         </is>
       </c>
       <c r="N108" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;kp RIGHT_SHIFT</t>
+&amp;none</t>
         </is>
       </c>
     </row>
@@ -11588,11 +11588,7 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B109" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LEFT_SHIFT</t>
-        </is>
-      </c>
+      <c r="B109" s="9" t="inlineStr"/>
       <c r="C109" s="9" t="inlineStr"/>
       <c r="D109" s="9" t="inlineStr"/>
       <c r="E109" s="9" t="inlineStr"/>
@@ -11601,14 +11597,18 @@
       <c r="H109" s="9" t="inlineStr"/>
       <c r="I109" s="9" t="inlineStr"/>
       <c r="J109" s="9" t="inlineStr"/>
-      <c r="K109" s="9" t="inlineStr"/>
+      <c r="K109" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB4</t>
+        </is>
+      </c>
       <c r="L109" s="9" t="inlineStr"/>
-      <c r="M109" s="9" t="inlineStr"/>
-      <c r="N109" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp RIGHT_SHIFT</t>
-        </is>
-      </c>
+      <c r="M109" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB5</t>
+        </is>
+      </c>
+      <c r="N109" s="9" t="inlineStr"/>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
@@ -11697,16 +11697,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A91:N91"/>
     <mergeCell ref="A55:N55"/>
     <mergeCell ref="A4:N4"/>
     <mergeCell ref="A45:N45"/>
     <mergeCell ref="A16:N16"/>
-    <mergeCell ref="A64:N64"/>
-    <mergeCell ref="A82:N82"/>
-    <mergeCell ref="A73:N73"/>
+    <mergeCell ref="A76:N76"/>
+    <mergeCell ref="A85:N85"/>
     <mergeCell ref="A28:N28"/>
-    <mergeCell ref="A102:N102"/>
+    <mergeCell ref="A103:N103"/>
+    <mergeCell ref="A66:N66"/>
+    <mergeCell ref="A94:N94"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
